--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{378452D2-8AA1-4607-8A51-4D8610BE5293}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15071429-99B2-4404-89B8-E6B48C00D46F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1002">
   <si>
     <t>UV</t>
   </si>
@@ -3965,6 +3965,650 @@
   </si>
   <si>
     <t>D’en faire la déclaration au Préfet de région au moins un an avant</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vous intervenez sur une armoire électrique, quelle précaution devez-vous prendre ?|Contacter préalablement le fournisseur d’électricité|Vérifier que l’extincteur utilisé est plein|Mettre un appareil respiratoire isolant|Couper ou veiller à ce que l’électricité soit coupée|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Quelle est la bonne correspondance de classe de feu ?|B : Feu de gaz|C : Feu de solide|A : Feu de liquide|A : Feu de solide|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vous découvrez une fuite importante sur une canalisation d’un R.I.A. Que faites-vous immédiatement après voir prévenu le P.C.S. ?|Je ferme la vanne de barrage du R.I.A.|Je fais appel au service de nettoyage|J’appelle les pompiers|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Le triangle du feu regroupe trois paramètres ?|Le carburant, le combustible et l’inhibition|Le comburant, le combustible, l’énergie d’activation|Le refroidissement|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>De quelle couleur peut être un extincteur ?|Rouge|Vert|Les deux|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dans quel cas doit-on rédiger un permis de feu ?|Lors de la mise en route des groupes électrogènes|A la mise en place d’une zone fumeur|A l’occasion des travaux par points chauds|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vous êtes en poste au PC Sécurité, une alarme incendie retentit :|Vous arrêtez immédiatement le signal sonore et réarmez la zone|Vous appuyez sur l’évacuation générale|Vous finissez votre ronde et vous la prenez en compte|Vous contactez immédiatement votre collègue afin qu’il effectue immédiatement une levée de doute sur site|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Où trouve-t-on les consignes générales de sécurité|A proximité des sorties de secours|Dans les sanitaires|Dans les locaux techniques|Dans votre local|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Indiquez le message d’alerte le plus efficace :|Nom de l’établissement, N° de téléphone, Nature du sinistre, Action menée|Nom, Prénom, adresse, action menée|Nom de l’établissement, N° de téléphone, Nature du sinistre, Adresse|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Qu’indique un voyant rouge sur le SSI ?|Un défaut|Un feu|Un dérangement|Un défaut de position de sécurité|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <t>Vous intervenez sur une armoire électrique, quelle précaution devez-vous prendre ?</t>
+  </si>
+  <si>
+    <t>Vérifier que l’extincteur utilisé est plein</t>
+  </si>
+  <si>
+    <t>Quelle est la bonne correspondance de classe de feu ?</t>
+  </si>
+  <si>
+    <t>B : Feu de gaz</t>
+  </si>
+  <si>
+    <t>C : Feu de solide</t>
+  </si>
+  <si>
+    <t>A : Feu de liquide</t>
+  </si>
+  <si>
+    <t>A : Feu de solide</t>
+  </si>
+  <si>
+    <t>Vous découvrez une fuite importante sur une canalisation d’un R.I.A. Que faites-vous immédiatement après voir prévenu le P.C.S. ?</t>
+  </si>
+  <si>
+    <t>Je ferme la vanne de barrage du R.I.A.</t>
+  </si>
+  <si>
+    <t>Je fais appel au service de nettoyage</t>
+  </si>
+  <si>
+    <t>J’appelle les pompiers</t>
+  </si>
+  <si>
+    <t>Le triangle du feu regroupe trois paramètres ?</t>
+  </si>
+  <si>
+    <t>Le carburant, le combustible et l’inhibition</t>
+  </si>
+  <si>
+    <t>De quelle couleur peut être un extincteur ?</t>
+  </si>
+  <si>
+    <t>Les deux</t>
+  </si>
+  <si>
+    <t>Dans quel cas doit-on rédiger un permis de feu ?</t>
+  </si>
+  <si>
+    <t>Lors de la mise en route des groupes électrogènes</t>
+  </si>
+  <si>
+    <t>A la mise en place d’une zone fumeur</t>
+  </si>
+  <si>
+    <t>A l’occasion des travaux par points chauds</t>
+  </si>
+  <si>
+    <t>Vous êtes en poste au PC Sécurité, une alarme incendie retentit :</t>
+  </si>
+  <si>
+    <t>Vous arrêtez immédiatement le signal sonore et réarmez la zone</t>
+  </si>
+  <si>
+    <t>Vous appuyez sur l’évacuation générale</t>
+  </si>
+  <si>
+    <t>Vous finissez votre ronde et vous la prenez en compte</t>
+  </si>
+  <si>
+    <t>Vous contactez immédiatement votre collègue afin qu’il effectue immédiatement une levée de doute sur site</t>
+  </si>
+  <si>
+    <t>Où trouve-t-on les consignes générales de sécurité</t>
+  </si>
+  <si>
+    <t>A proximité des sorties de secours</t>
+  </si>
+  <si>
+    <t>Dans les sanitaires</t>
+  </si>
+  <si>
+    <t>Dans les locaux techniques</t>
+  </si>
+  <si>
+    <t>Dans votre local</t>
+  </si>
+  <si>
+    <t>Indiquez le message d’alerte le plus efficace :</t>
+  </si>
+  <si>
+    <t>Nom de l’établissement, N° de téléphone, Nature du sinistre, Action menée</t>
+  </si>
+  <si>
+    <t>Nom, Prénom, adresse, action menée</t>
+  </si>
+  <si>
+    <t>Nom de l’établissement, N° de téléphone, Nature du sinistre, Adresse</t>
+  </si>
+  <si>
+    <t>Qu’indique un voyant rouge sur le SSI ?</t>
+  </si>
+  <si>
+    <t>Un défaut</t>
+  </si>
+  <si>
+    <t>Un feu</t>
+  </si>
+  <si>
+    <t>Un dérangement</t>
+  </si>
+  <si>
+    <t>Un défaut de position de sécurité</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
 </sst>
 </file>
@@ -4489,13 +5133,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>228962</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>181008</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4533,13 +5177,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>581840</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>171518</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4577,13 +5221,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>155</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>238570</xdr:colOff>
-      <xdr:row>146</xdr:row>
+      <xdr:row>156</xdr:row>
       <xdr:rowOff>181019</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4609,6 +5253,50 @@
         <a:xfrm>
           <a:off x="15935325" y="27679650"/>
           <a:ext cx="3191320" cy="314369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>229052</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>57183</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Image 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{546AC271-ABFE-C90F-4EB1-899883BDD109}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15878175" y="22107525"/>
+          <a:ext cx="3238952" cy="238158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4905,7 +5593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
@@ -8390,57 +9078,57 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>11</v>
+        <v>992</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>723</v>
+        <v>954</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>724</v>
+        <v>554</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>725</v>
+        <v>955</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>726</v>
+        <v>556</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>727</v>
+        <v>555</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>13</v>
+        <v>993</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>728</v>
+        <v>956</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>729</v>
+        <v>957</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>730</v>
+        <v>958</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>731</v>
+        <v>959</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>732</v>
+        <v>960</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J118" s="10" t="s">
         <v>18</v>
@@ -8448,28 +9136,25 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>15</v>
+        <v>994</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>733</v>
+        <v>961</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>734</v>
+        <v>962</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>735</v>
+        <v>963</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>736</v>
+        <v>964</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J119" s="10" t="s">
         <v>14</v>
@@ -8477,144 +9162,135 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>16</v>
+        <v>995</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>738</v>
+        <v>965</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>739</v>
+        <v>966</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>740</v>
+        <v>534</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>741</v>
+        <v>660</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>17</v>
+        <v>996</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>743</v>
+        <v>967</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>744</v>
+        <v>563</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>745</v>
+        <v>564</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>746</v>
+        <v>968</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>19</v>
+        <v>997</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>748</v>
+        <v>969</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>749</v>
+        <v>970</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>750</v>
+        <v>971</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>751</v>
+        <v>972</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>20</v>
+        <v>998</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>753</v>
+        <v>973</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>754</v>
+        <v>974</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>755</v>
+        <v>975</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>756</v>
+        <v>976</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>757</v>
+        <v>977</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>22</v>
+        <v>999</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>758</v>
+        <v>978</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>759</v>
+        <v>979</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>760</v>
+        <v>980</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>761</v>
+        <v>981</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>762</v>
+        <v>982</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J124" s="10" t="s">
         <v>14</v>
@@ -8622,141 +9298,138 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>784</v>
+        <v>983</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>785</v>
+        <v>984</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>786</v>
+        <v>985</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>787</v>
+        <v>986</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>13</v>
+        <v>1001</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>789</v>
+        <v>987</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>790</v>
+        <v>988</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>791</v>
+        <v>989</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>792</v>
+        <v>990</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>793</v>
+        <v>991</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>90</v>
+        <v>541</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>794</v>
+        <v>723</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>795</v>
+        <v>724</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>796</v>
+        <v>725</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>797</v>
+        <v>726</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>798</v>
+        <v>727</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>799</v>
+        <v>728</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>800</v>
+        <v>729</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>801</v>
+        <v>730</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>803</v>
+        <v>732</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>804</v>
+        <v>733</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>805</v>
+        <v>734</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>806</v>
+        <v>735</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>807</v>
+        <v>736</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>90</v>
@@ -8767,83 +9440,83 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>809</v>
+        <v>738</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>811</v>
+        <v>740</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>812</v>
+        <v>741</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>813</v>
+        <v>742</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>814</v>
+        <v>743</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>815</v>
+        <v>744</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>816</v>
+        <v>745</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>817</v>
+        <v>746</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>818</v>
+        <v>747</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>819</v>
+        <v>748</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>820</v>
+        <v>749</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>821</v>
+        <v>750</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>822</v>
+        <v>751</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>823</v>
+        <v>752</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>90</v>
@@ -8854,60 +9527,60 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>824</v>
+        <v>753</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>825</v>
+        <v>754</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>826</v>
+        <v>755</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>827</v>
+        <v>756</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>828</v>
+        <v>757</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>829</v>
+        <v>758</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>830</v>
+        <v>759</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>831</v>
+        <v>760</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>832</v>
+        <v>761</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>833</v>
+        <v>762</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8915,22 +9588,22 @@
         <v>258</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>834</v>
+        <v>784</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>835</v>
+        <v>785</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>836</v>
+        <v>786</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>837</v>
+        <v>787</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>838</v>
+        <v>788</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>90</v>
@@ -8944,28 +9617,28 @@
         <v>258</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>839</v>
+        <v>789</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>840</v>
+        <v>790</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>841</v>
+        <v>791</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>842</v>
+        <v>792</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>843</v>
+        <v>793</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -8973,28 +9646,28 @@
         <v>258</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>844</v>
+        <v>794</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>845</v>
+        <v>795</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>846</v>
+        <v>796</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>847</v>
+        <v>797</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>848</v>
+        <v>798</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -9002,28 +9675,28 @@
         <v>258</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>849</v>
+        <v>799</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>851</v>
+        <v>801</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>852</v>
+        <v>802</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>853</v>
+        <v>803</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -9031,28 +9704,28 @@
         <v>258</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>854</v>
+        <v>804</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>855</v>
+        <v>805</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>856</v>
+        <v>806</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>857</v>
+        <v>807</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>858</v>
+        <v>808</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -9060,22 +9733,22 @@
         <v>258</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>860</v>
+        <v>810</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>861</v>
+        <v>811</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>863</v>
+        <v>813</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>90</v>
@@ -9089,22 +9762,22 @@
         <v>258</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>864</v>
+        <v>814</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>865</v>
+        <v>815</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>866</v>
+        <v>816</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>867</v>
+        <v>817</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>868</v>
+        <v>818</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>90</v>
@@ -9118,28 +9791,28 @@
         <v>258</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>869</v>
+        <v>819</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>871</v>
+        <v>821</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>872</v>
+        <v>822</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>873</v>
+        <v>823</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -9147,28 +9820,28 @@
         <v>258</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>875</v>
+        <v>825</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>876</v>
+        <v>826</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>877</v>
+        <v>827</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>878</v>
+        <v>828</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -9176,109 +9849,109 @@
         <v>258</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>879</v>
+        <v>829</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>881</v>
+        <v>831</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>882</v>
+        <v>832</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>883</v>
+        <v>833</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>894</v>
+        <v>834</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>895</v>
+        <v>835</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>896</v>
+        <v>836</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>897</v>
+        <v>837</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>898</v>
+        <v>838</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>899</v>
+        <v>839</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>901</v>
+        <v>841</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>902</v>
+        <v>842</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>903</v>
+        <v>843</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>904</v>
+        <v>844</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>905</v>
+        <v>845</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>906</v>
+        <v>846</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>907</v>
+        <v>847</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>908</v>
+        <v>848</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>90</v>
@@ -9289,112 +9962,112 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>909</v>
+        <v>849</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>910</v>
+        <v>850</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>911</v>
+        <v>851</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>912</v>
+        <v>852</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>913</v>
+        <v>853</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>914</v>
+        <v>854</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>915</v>
+        <v>855</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>916</v>
+        <v>856</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>918</v>
+        <v>858</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J149" s="10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>919</v>
+        <v>859</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>920</v>
+        <v>860</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>921</v>
+        <v>861</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>922</v>
+        <v>862</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>923</v>
+        <v>863</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>924</v>
+        <v>864</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>925</v>
+        <v>865</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>926</v>
+        <v>866</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>927</v>
+        <v>867</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>928</v>
+        <v>868</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>90</v>
@@ -9405,25 +10078,25 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>929</v>
+        <v>869</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>930</v>
+        <v>870</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>931</v>
+        <v>871</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>932</v>
+        <v>872</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>933</v>
+        <v>873</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>90</v>
@@ -9434,59 +10107,349 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>934</v>
+        <v>874</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>935</v>
+        <v>875</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>936</v>
+        <v>876</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>937</v>
+        <v>877</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>938</v>
+        <v>878</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>939</v>
+        <v>879</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>940</v>
+        <v>880</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>941</v>
+        <v>881</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>942</v>
+        <v>882</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>943</v>
+        <v>883</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J154" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J155" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J157" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J159" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J161" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J162" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J163" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J164" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -10627,7 +11590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18582157-25E0-434E-AB6B-01FE38A60B37}">
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
@@ -14403,6 +15366,311 @@
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="15"/>
     </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="B125" s="17">
+        <f t="shared" ref="B125:B134" si="16">FIND(" – ",A125)</f>
+        <v>10</v>
+      </c>
+      <c r="C125" s="17" t="str">
+        <f t="shared" ref="C125:C134" si="17">RIGHT(A125, LEN(A125)-(B125+2))</f>
+        <v>Vous intervenez sur une armoire électrique, quelle précaution devez-vous prendre ?|Contacter préalablement le fournisseur d’électricité|Vérifier que l’extincteur utilisé est plein|Mettre un appareil respiratoire isolant|Couper ou veiller à ce que l’électricité soit coupée|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D125" t="str" cm="1">
+        <f t="array" ref="D125:I125">_xlfn.TEXTSPLIT(C125,"|")</f>
+        <v>Vous intervenez sur une armoire électrique, quelle précaution devez-vous prendre ?</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Contacter préalablement le fournisseur d’électricité</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Vérifier que l’extincteur utilisé est plein</v>
+      </c>
+      <c r="G125" t="str">
+        <v>Mettre un appareil respiratoire isolant</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Couper ou veiller à ce que l’électricité soit coupée</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="B126" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C126" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Quelle est la bonne correspondance de classe de feu ?|B : Feu de gaz|C : Feu de solide|A : Feu de liquide|A : Feu de solide|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D126" t="str" cm="1">
+        <f t="array" ref="D126:I126">_xlfn.TEXTSPLIT(C126,"|")</f>
+        <v>Quelle est la bonne correspondance de classe de feu ?</v>
+      </c>
+      <c r="E126" t="str">
+        <v>B : Feu de gaz</v>
+      </c>
+      <c r="F126" t="str">
+        <v>C : Feu de solide</v>
+      </c>
+      <c r="G126" t="str">
+        <v>A : Feu de liquide</v>
+      </c>
+      <c r="H126" t="str">
+        <v>A : Feu de solide</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="B127" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C127" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Vous découvrez une fuite importante sur une canalisation d’un R.I.A. Que faites-vous immédiatement après voir prévenu le P.C.S. ?|Je ferme la vanne de barrage du R.I.A.|Je fais appel au service de nettoyage|J’appelle les pompiers|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D127" t="str" cm="1">
+        <f t="array" ref="D127:H127">_xlfn.TEXTSPLIT(C127,"|")</f>
+        <v>Vous découvrez une fuite importante sur une canalisation d’un R.I.A. Que faites-vous immédiatement après voir prévenu le P.C.S. ?</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Je ferme la vanne de barrage du R.I.A.</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Je fais appel au service de nettoyage</v>
+      </c>
+      <c r="G127" t="str">
+        <v>J’appelle les pompiers</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="B128" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C128" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Le triangle du feu regroupe trois paramètres ?|Le carburant, le combustible et l’inhibition|Le comburant, le combustible, l’énergie d’activation|Le refroidissement|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D128" t="str" cm="1">
+        <f t="array" ref="D128:H128">_xlfn.TEXTSPLIT(C128,"|")</f>
+        <v>Le triangle du feu regroupe trois paramètres ?</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Le carburant, le combustible et l’inhibition</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Le comburant, le combustible, l’énergie d’activation</v>
+      </c>
+      <c r="G128" t="str">
+        <v>Le refroidissement</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B129" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C129" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>De quelle couleur peut être un extincteur ?|Rouge|Vert|Les deux|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D129" t="str" cm="1">
+        <f t="array" ref="D129:H129">_xlfn.TEXTSPLIT(C129,"|")</f>
+        <v>De quelle couleur peut être un extincteur ?</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Rouge</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Vert</v>
+      </c>
+      <c r="G129" t="str">
+        <v>Les deux</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="B130" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C130" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Dans quel cas doit-on rédiger un permis de feu ?|Lors de la mise en route des groupes électrogènes|A la mise en place d’une zone fumeur|A l’occasion des travaux par points chauds|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D130" t="str" cm="1">
+        <f t="array" ref="D130:H130">_xlfn.TEXTSPLIT(C130,"|")</f>
+        <v>Dans quel cas doit-on rédiger un permis de feu ?</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Lors de la mise en route des groupes électrogènes</v>
+      </c>
+      <c r="F130" t="str">
+        <v>A la mise en place d’une zone fumeur</v>
+      </c>
+      <c r="G130" t="str">
+        <v>A l’occasion des travaux par points chauds</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="B131" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C131" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Vous êtes en poste au PC Sécurité, une alarme incendie retentit :|Vous arrêtez immédiatement le signal sonore et réarmez la zone|Vous appuyez sur l’évacuation générale|Vous finissez votre ronde et vous la prenez en compte|Vous contactez immédiatement votre collègue afin qu’il effectue immédiatement une levée de doute sur site|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D131" t="str" cm="1">
+        <f t="array" ref="D131:I131">_xlfn.TEXTSPLIT(C131,"|")</f>
+        <v>Vous êtes en poste au PC Sécurité, une alarme incendie retentit :</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Vous arrêtez immédiatement le signal sonore et réarmez la zone</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Vous appuyez sur l’évacuation générale</v>
+      </c>
+      <c r="G131" t="str">
+        <v>Vous finissez votre ronde et vous la prenez en compte</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Vous contactez immédiatement votre collègue afin qu’il effectue immédiatement une levée de doute sur site</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="B132" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C132" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Où trouve-t-on les consignes générales de sécurité|A proximité des sorties de secours|Dans les sanitaires|Dans les locaux techniques|Dans votre local|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D132" t="str" cm="1">
+        <f t="array" ref="D132:I132">_xlfn.TEXTSPLIT(C132,"|")</f>
+        <v>Où trouve-t-on les consignes générales de sécurité</v>
+      </c>
+      <c r="E132" t="str">
+        <v>A proximité des sorties de secours</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Dans les sanitaires</v>
+      </c>
+      <c r="G132" t="str">
+        <v>Dans les locaux techniques</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Dans votre local</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="B133" s="17">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="C133" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Indiquez le message d’alerte le plus efficace :|Nom de l’établissement, N° de téléphone, Nature du sinistre, Action menée|Nom, Prénom, adresse, action menée|Nom de l’établissement, N° de téléphone, Nature du sinistre, Adresse|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D133" t="str" cm="1">
+        <f t="array" ref="D133:H133">_xlfn.TEXTSPLIT(C133,"|")</f>
+        <v>Indiquez le message d’alerte le plus efficace :</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Nom de l’établissement, N° de téléphone, Nature du sinistre, Action menée</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Nom, Prénom, adresse, action menée</v>
+      </c>
+      <c r="G133" t="str">
+        <v>Nom de l’établissement, N° de téléphone, Nature du sinistre, Adresse</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="B134" s="17">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="C134" s="17" t="str">
+        <f t="shared" si="17"/>
+        <v>Qu’indique un voyant rouge sur le SSI ?|Un défaut|Un feu|Un dérangement|Un défaut de position de sécurité|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D134" t="str" cm="1">
+        <f t="array" ref="D134:I134">_xlfn.TEXTSPLIT(C134,"|")</f>
+        <v>Qu’indique un voyant rouge sur le SSI ?</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Un défaut</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Un feu</v>
+      </c>
+      <c r="G134" t="str">
+        <v>Un dérangement</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Un défaut de position de sécurité</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15071429-99B2-4404-89B8-E6B48C00D46F}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E37C4B-C686-48C3-B7B7-E495B62B59C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1124">
   <si>
     <t>UV</t>
   </si>
@@ -4609,6 +4609,625 @@
   </si>
   <si>
     <t>50</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1 – En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?|Le CMSI, Centralisateur de Mise en Sécurité Incendie|Le SMSI, Système de Mise en Sécurité Incendie|Le DAS, Dispositif Actionné de Sécurité|Le SDI, Système de Détection Incendie|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 – Quelle type d’alarme existe-il dans le fonctionnement d’un DATI ?|L’alarme semi-automatique|Aucune des réponses précédentes|La perte de verticalité|L’alarme aléatoire|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3 – Quel est le signe distinctif réglementaire qui permet d’identifier un local électrique ?|Un symbole avec une tête de mort|Un triangle rouge|Un triangle jaune|Un panneau défense d’entrer|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4 – Votre équipement de protection du travailleur isolé est utile :|Uniquement au PC|Uniquement durant le circuit de vérification|Au poste de sécurité (PC) et en dehors du PC|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5 – Quelle habilitation minimum doit avoir un APS pour entrer dans un local avec TGBT (Tableau Général Basse Tension) ?|L’habilitation H1 / B1|L’habilitation H0 / B0|L’habilitation BR ou BC|L’habilitation BS ou BE manœuvre|Aucune habilitation n’est nécessaire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6 – Quel est l’un des modes de déclenchement dans le fonctionnement d’un DATI ?|En cas d’arrachement et/ou d’agression morale|En cas d’arrachement et/ou d’agression psychique|En cas d’arrachement et/ou d’agression physique|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7 – Quel est l’un des éléments qui permet le déclenchement du dispositif DATI ?|Le dispositif détecte une position anormale prolongée du travailleur|Le dispositif se déclenche en cas d’intrusion|Le dispositif se déclenche en cas de ronde réalisée partiellement|Le dispositif se déclenche en cas de détonation|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8 – Que signifie le sigle DATI ?|Dispositif d’Alarme du Travailleur Isolé|Détecteur Automatique Temporisé d’Intrusion|Dispositif d’Alerte du Travailleur Isolé|Dispositif d’Alarme Travail Intérieur|Dispositif d’Alarme Technique Individuel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9 – Pour vous, quelle réponse justifierait le port du DATI ?|J’effectue seul(e) une ronde sur un site|Je suis en surveillance de nuit avec 3 autres APS|Je suis affecté au contrôle d’accès d’un site face à l’accueil en activité|Je suis en surveillance derrière la ligne de caisse avec 3 autres APS|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10 – Quelles sont les limites de la basse tension en courant alternatif ?|De 500 V à 800 V|De 50 V à 1000 V|De 500 V à 1000 V|De 50 V à 750 V|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11 – En cas de déclenchement du dispositif d’alarme d’un DATI, peut-on localiser avec précision une victime ?|Oui|Non</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12 – Lors d’un appel du PC de télésurveillance pour une alarme intrusion sur votre site, vous devez en premier lieu :|Noter l’appel sur la main courante ou le cahier de poste|Confirmer votre identité par un mot de passe|Confirmer qu’il n’existe aucune anomalie avant d’avoir fait effectuer une levée de doute|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13 – Quelles sont les principales qualités d’un système d’alarme ?|Inviolabilité, compatibilité, pluralité, fiabilité, sécurité négative|Inviolabilité, compatibilité, pluralité, fébrilité, sécurité négative|Inviolabilité, compatibilité, pluralité, fiabilité, sécurité positive|Inviolabilité, comptabilité, pluralité, fiabilité, sécurité positive|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14 – Vous êtes en poste au PC sécurité et une Alarme Incendie retentit|Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue|Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude|Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde|Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>15 – Votre collègue est en ronde, vous êtes en poste au PC et recevez une alarme intrusion, que faites-vous ?|Vous rejoignez au plus vite votre collègue pour intervenir plus efficacement|Vous effectuez vous-même la levée de doute|Vous demandez à votre collègue de se rendre sur le lieu précis de déclenchement de l’alarme pour effectuer la levée de doute|Vous attendez que votre collègue finisse sa ronde pour intervenir|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>16 – Vous êtes en poste au PC sécurité et une Alarme Incendie retentit|Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde|Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue|Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude|Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17 – Vous êtes en poste, les pompiers arrivent sur le site sinistré. Vous êtes informé que la voie d’accès principale est bloquée par un camion stationné. Que faites-vous en priorité ?|Je propose aux pompiers d’emprunter un autre accès qui est bien libre|J’autorise les pompiers à pousser le camion, ils en ont l’obligation|J’appelle les personnels de l’usine, au point de rassemblement, pour déplacer le véhicule|J’appelle la Fourrière|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>18 – Lors d’un orage, une coupure de courant intervient, que faites-vous ?|Rien|Réarmer le disjoncteur principal|Vous cherchez les bougies|J’applique les consignes|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>19 – Vous êtes seul sur site lors d’une ronde, vous constatez un incendie, que faites-vous en premier ?|J’appelle les pompiers|Je compose le 17|Je rends compte au PCS et je tente l’extinction|J’ai obligation de prendre un extincteur pour éteindre l’incendie|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20 – Le courant est dangereux à partir de :|700 V en courant alternatif|500 V en courant alternatif|50 V en courant alternatif|25 V en courant continu|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>21 – Qui délivre l’habilitation électrique ?|L’employeur|Le formateur|Le chargé de travaux|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>22 – Qu’est-ce qu’une alarme restreinte ?|C’est un signal sonore qui alerte une partie du personnel pour évacuer|C’est un signal visuel et sonore qui informe le PC pour effectuer une levée de doute|C’est un signal sonore qui alerte l’ensemble des occupants pour évacuer|C’est un signal horizontal et vertical qui guide les occupants vers la sortie|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>23 – Dans une usine en activité, suite à un incendie, une évacuation générale es déclenchée, les pompiers arrivent, agent au PC, que faites-vous en priorité ?|Je remets les plans d’évacuation parfaitement à jour aux pompiers qui savent où aller|Je vérifie rapidement les cartes professionnelles des pompiers|Je dépêche un agent pour les accueillir et les guider|Je demande aux agents d’utiliser les extincteurs pour maîtriser l’incendie|Aucune des réponses précédentes</t>
+    </r>
+  </si>
+  <si>
+    <t>En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?</t>
+  </si>
+  <si>
+    <t>Le CMSI, Centralisateur de Mise en Sécurité Incendie</t>
+  </si>
+  <si>
+    <t>Le SMSI, Système de Mise en Sécurité Incendie</t>
+  </si>
+  <si>
+    <t>Le DAS, Dispositif Actionné de Sécurité</t>
+  </si>
+  <si>
+    <t>Le SDI, Système de Détection Incendie</t>
+  </si>
+  <si>
+    <t>Quelle type d’alarme existe-il dans le fonctionnement d’un DATI ?</t>
+  </si>
+  <si>
+    <t>L’alarme semi-automatique</t>
+  </si>
+  <si>
+    <t>La perte de verticalité</t>
+  </si>
+  <si>
+    <t>L’alarme aléatoire</t>
+  </si>
+  <si>
+    <t>Quel est le signe distinctif réglementaire qui permet d’identifier un local électrique ?</t>
+  </si>
+  <si>
+    <t>Un symbole avec une tête de mort</t>
+  </si>
+  <si>
+    <t>Un triangle rouge</t>
+  </si>
+  <si>
+    <t>Un triangle jaune</t>
+  </si>
+  <si>
+    <t>Un panneau défense d’entrer</t>
+  </si>
+  <si>
+    <t>Votre équipement de protection du travailleur isolé est utile :</t>
+  </si>
+  <si>
+    <t>Uniquement au PC</t>
+  </si>
+  <si>
+    <t>Uniquement durant le circuit de vérification</t>
+  </si>
+  <si>
+    <t>Au poste de sécurité (PC) et en dehors du PC</t>
+  </si>
+  <si>
+    <t>Quelle habilitation minimum doit avoir un APS pour entrer dans un local avec TGBT (Tableau Général Basse Tension) ?</t>
+  </si>
+  <si>
+    <t>L’habilitation H1 / B1</t>
+  </si>
+  <si>
+    <t>L’habilitation H0 / B0</t>
+  </si>
+  <si>
+    <t>L’habilitation BR ou BC</t>
+  </si>
+  <si>
+    <t>L’habilitation BS ou BE manœuvre</t>
+  </si>
+  <si>
+    <t>Aucune habilitation n’est nécessaire</t>
+  </si>
+  <si>
+    <t>Quel est l’un des modes de déclenchement dans le fonctionnement d’un DATI ?</t>
+  </si>
+  <si>
+    <t>En cas d’arrachement et/ou d’agression morale</t>
+  </si>
+  <si>
+    <t>En cas d’arrachement et/ou d’agression psychique</t>
+  </si>
+  <si>
+    <t>En cas d’arrachement et/ou d’agression physique</t>
+  </si>
+  <si>
+    <t>Quel est l’un des éléments qui permet le déclenchement du dispositif DATI ?</t>
+  </si>
+  <si>
+    <t>Le dispositif détecte une position anormale prolongée du travailleur</t>
+  </si>
+  <si>
+    <t>Le dispositif se déclenche en cas d’intrusion</t>
+  </si>
+  <si>
+    <t>Le dispositif se déclenche en cas de ronde réalisée partiellement</t>
+  </si>
+  <si>
+    <t>Le dispositif se déclenche en cas de détonation</t>
+  </si>
+  <si>
+    <t>Que signifie le sigle DATI ?</t>
+  </si>
+  <si>
+    <t>Dispositif d’Alarme du Travailleur Isolé</t>
+  </si>
+  <si>
+    <t>Détecteur Automatique Temporisé d’Intrusion</t>
+  </si>
+  <si>
+    <t>Dispositif d’Alerte du Travailleur Isolé</t>
+  </si>
+  <si>
+    <t>Dispositif d’Alarme Travail Intérieur</t>
+  </si>
+  <si>
+    <t>Dispositif d’Alarme Technique Individuel</t>
+  </si>
+  <si>
+    <t>Pour vous, quelle réponse justifierait le port du DATI ?</t>
+  </si>
+  <si>
+    <t>J’effectue seul(e) une ronde sur un site</t>
+  </si>
+  <si>
+    <t>Je suis en surveillance de nuit avec 3 autres APS</t>
+  </si>
+  <si>
+    <t>Je suis affecté au contrôle d’accès d’un site face à l’accueil en activité</t>
+  </si>
+  <si>
+    <t>Je suis en surveillance derrière la ligne de caisse avec 3 autres APS</t>
+  </si>
+  <si>
+    <t>Quelles sont les limites de la basse tension en courant alternatif ?</t>
+  </si>
+  <si>
+    <t>De 500 V à 800 V</t>
+  </si>
+  <si>
+    <t>De 50 V à 1000 V</t>
+  </si>
+  <si>
+    <t>De 500 V à 1000 V</t>
+  </si>
+  <si>
+    <t>De 50 V à 750 V</t>
+  </si>
+  <si>
+    <t>En cas de déclenchement du dispositif d’alarme d’un DATI, peut-on localiser avec précision une victime ?</t>
+  </si>
+  <si>
+    <t>Lors d’un appel du PC de télésurveillance pour une alarme intrusion sur votre site, vous devez en premier lieu :</t>
+  </si>
+  <si>
+    <t>Noter l’appel sur la main courante ou le cahier de poste</t>
+  </si>
+  <si>
+    <t>Confirmer votre identité par un mot de passe</t>
+  </si>
+  <si>
+    <t>Confirmer qu’il n’existe aucune anomalie avant d’avoir fait effectuer une levée de doute</t>
+  </si>
+  <si>
+    <t>Quelles sont les principales qualités d’un système d’alarme ?</t>
+  </si>
+  <si>
+    <t>Inviolabilité, compatibilité, pluralité, fiabilité, sécurité négative</t>
+  </si>
+  <si>
+    <t>Inviolabilité, compatibilité, pluralité, fébrilité, sécurité négative</t>
+  </si>
+  <si>
+    <t>Inviolabilité, compatibilité, pluralité, fiabilité, sécurité positive</t>
+  </si>
+  <si>
+    <t>Inviolabilité, comptabilité, pluralité, fiabilité, sécurité positive</t>
+  </si>
+  <si>
+    <t>Vous êtes en poste au PC sécurité et une Alarme Incendie retentit</t>
+  </si>
+  <si>
+    <t>Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue</t>
+  </si>
+  <si>
+    <t>Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude</t>
+  </si>
+  <si>
+    <t>Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde</t>
+  </si>
+  <si>
+    <t>Votre collègue est en ronde, vous êtes en poste au PC et recevez une alarme intrusion, que faites-vous ?</t>
+  </si>
+  <si>
+    <t>Vous rejoignez au plus vite votre collègue pour intervenir plus efficacement</t>
+  </si>
+  <si>
+    <t>Vous effectuez vous-même la levée de doute</t>
+  </si>
+  <si>
+    <t>Vous demandez à votre collègue de se rendre sur le lieu précis de déclenchement de l’alarme pour effectuer la levée de doute</t>
+  </si>
+  <si>
+    <t>Vous attendez que votre collègue finisse sa ronde pour intervenir</t>
+  </si>
+  <si>
+    <t>Vous êtes en poste, les pompiers arrivent sur le site sinistré. Vous êtes informé que la voie d’accès principale est bloquée par un camion stationné. Que faites-vous en priorité ?</t>
+  </si>
+  <si>
+    <t>Je propose aux pompiers d’emprunter un autre accès qui est bien libre</t>
+  </si>
+  <si>
+    <t>J’appelle la Fourrière</t>
+  </si>
+  <si>
+    <t>Lors d’un orage, une coupure de courant intervient, que faites-vous ?</t>
+  </si>
+  <si>
+    <t>Rien</t>
+  </si>
+  <si>
+    <t>Réarmer le disjoncteur principal</t>
+  </si>
+  <si>
+    <t>Vous cherchez les bougies</t>
+  </si>
+  <si>
+    <t>J’applique les consignes</t>
+  </si>
+  <si>
+    <t>Vous êtes seul sur site lors d’une ronde, vous constatez un incendie, que faites-vous en premier ?</t>
+  </si>
+  <si>
+    <t>Je compose le 17</t>
+  </si>
+  <si>
+    <t>Je rends compte au PCS et je tente l’extinction</t>
+  </si>
+  <si>
+    <t>J’ai obligation de prendre un extincteur pour éteindre l’incendie</t>
+  </si>
+  <si>
+    <t>Le courant est dangereux à partir de :</t>
+  </si>
+  <si>
+    <t>700 V en courant alternatif</t>
+  </si>
+  <si>
+    <t>500 V en courant alternatif</t>
+  </si>
+  <si>
+    <t>50 V en courant alternatif</t>
+  </si>
+  <si>
+    <t>25 V en courant continu</t>
+  </si>
+  <si>
+    <t>Qui délivre l’habilitation électrique ?</t>
+  </si>
+  <si>
+    <t>L’employeur</t>
+  </si>
+  <si>
+    <t>Le formateur</t>
+  </si>
+  <si>
+    <t>Le chargé de travaux</t>
+  </si>
+  <si>
+    <t>Qu’est-ce qu’une alarme restreinte ?</t>
+  </si>
+  <si>
+    <t>C’est un signal sonore qui alerte une partie du personnel pour évacuer</t>
+  </si>
+  <si>
+    <t>C’est un signal visuel et sonore qui informe le PC pour effectuer une levée de doute</t>
+  </si>
+  <si>
+    <t>C’est un signal sonore qui alerte l’ensemble des occupants pour évacuer</t>
+  </si>
+  <si>
+    <t>C’est un signal horizontal et vertical qui guide les occupants vers la sortie</t>
+  </si>
+  <si>
+    <t>Dans une usine en activité, suite à un incendie, une évacuation générale es déclenchée, les pompiers arrivent, agent au PC, que faites-vous en priorité ?</t>
+  </si>
+  <si>
+    <t>Je remets les plans d’évacuation parfaitement à jour aux pompiers qui savent où aller</t>
+  </si>
+  <si>
+    <t>Je vérifie rapidement les cartes professionnelles des pompiers</t>
+  </si>
+  <si>
+    <t>Je dépêche un agent pour les accueillir et les guider</t>
+  </si>
+  <si>
+    <t>Je demande aux agents d’utiliser les extincteurs pour maîtriser l’incendie</t>
   </si>
 </sst>
 </file>
@@ -5305,6 +5924,49 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>333903</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>142972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Image 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7AE77D4-12B9-036F-4FB1-3B175C870297}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:srcRect t="12161"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16049625" y="31337249"/>
+          <a:ext cx="3781953" cy="619223"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5593,7 +6255,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J164"/>
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
@@ -10453,6 +11118,652 @@
         <v>21</v>
       </c>
     </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J165" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J166" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J167" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J168" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J169" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J170" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J171" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J172" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J173" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B174" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J174" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J175" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J176" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J177" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J178" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J179" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J180" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J181" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J182" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J183" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J184" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J185" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J186" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J187" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J76" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -10464,7 +11775,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D364EFAA-EF75-46AB-9449-DE504B7E1DE0}">
   <sheetPr>
-    <tabColor rgb="FF999999"/>
+    <tabColor rgb="FF00B0F0"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B1000"/>
@@ -11590,7 +12901,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18582157-25E0-434E-AB6B-01FE38A60B37}">
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
@@ -15671,6 +16982,721 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B136" s="17">
+        <f t="shared" ref="B136:B158" si="18">FIND(" – ",A136)</f>
+        <v>10</v>
+      </c>
+      <c r="C136" s="17" t="str">
+        <f t="shared" ref="C136:C158" si="19">RIGHT(A136, LEN(A136)-(B136+2))</f>
+        <v>En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?|Le CMSI, Centralisateur de Mise en Sécurité Incendie|Le SMSI, Système de Mise en Sécurité Incendie|Le DAS, Dispositif Actionné de Sécurité|Le SDI, Système de Détection Incendie|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D136" t="str" cm="1">
+        <f t="array" ref="D136:I136">_xlfn.TEXTSPLIT(C136,"|")</f>
+        <v>En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Le CMSI, Centralisateur de Mise en Sécurité Incendie</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Le SMSI, Système de Mise en Sécurité Incendie</v>
+      </c>
+      <c r="G136" t="str">
+        <v>Le DAS, Dispositif Actionné de Sécurité</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Le SDI, Système de Détection Incendie</v>
+      </c>
+      <c r="I136" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B137" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C137" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quelle type d’alarme existe-il dans le fonctionnement d’un DATI ?|L’alarme semi-automatique|Aucune des réponses précédentes|La perte de verticalité|L’alarme aléatoire|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D137" t="str" cm="1">
+        <f t="array" ref="D137:I137">_xlfn.TEXTSPLIT(C137,"|")</f>
+        <v>Quelle type d’alarme existe-il dans le fonctionnement d’un DATI ?</v>
+      </c>
+      <c r="E137" t="str">
+        <v>L’alarme semi-automatique</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+      <c r="G137" t="str">
+        <v>La perte de verticalité</v>
+      </c>
+      <c r="H137" t="str">
+        <v>L’alarme aléatoire</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B138" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C138" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quel est le signe distinctif réglementaire qui permet d’identifier un local électrique ?|Un symbole avec une tête de mort|Un triangle rouge|Un triangle jaune|Un panneau défense d’entrer|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D138" t="str" cm="1">
+        <f t="array" ref="D138:I138">_xlfn.TEXTSPLIT(C138,"|")</f>
+        <v>Quel est le signe distinctif réglementaire qui permet d’identifier un local électrique ?</v>
+      </c>
+      <c r="E138" t="str">
+        <v>Un symbole avec une tête de mort</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Un triangle rouge</v>
+      </c>
+      <c r="G138" t="str">
+        <v>Un triangle jaune</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Un panneau défense d’entrer</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B139" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C139" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Votre équipement de protection du travailleur isolé est utile :|Uniquement au PC|Uniquement durant le circuit de vérification|Au poste de sécurité (PC) et en dehors du PC|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D139" t="str" cm="1">
+        <f t="array" ref="D139:H139">_xlfn.TEXTSPLIT(C139,"|")</f>
+        <v>Votre équipement de protection du travailleur isolé est utile :</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Uniquement au PC</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Uniquement durant le circuit de vérification</v>
+      </c>
+      <c r="G139" t="str">
+        <v>Au poste de sécurité (PC) et en dehors du PC</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B140" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C140" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quelle habilitation minimum doit avoir un APS pour entrer dans un local avec TGBT (Tableau Général Basse Tension) ?|L’habilitation H1 / B1|L’habilitation H0 / B0|L’habilitation BR ou BC|L’habilitation BS ou BE manœuvre|Aucune habilitation n’est nécessaire</v>
+      </c>
+      <c r="D140" t="str" cm="1">
+        <f t="array" ref="D140:I140">_xlfn.TEXTSPLIT(C140,"|")</f>
+        <v>Quelle habilitation minimum doit avoir un APS pour entrer dans un local avec TGBT (Tableau Général Basse Tension) ?</v>
+      </c>
+      <c r="E140" t="str">
+        <v>L’habilitation H1 / B1</v>
+      </c>
+      <c r="F140" t="str">
+        <v>L’habilitation H0 / B0</v>
+      </c>
+      <c r="G140" t="str">
+        <v>L’habilitation BR ou BC</v>
+      </c>
+      <c r="H140" t="str">
+        <v>L’habilitation BS ou BE manœuvre</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Aucune habilitation n’est nécessaire</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B141" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C141" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quel est l’un des modes de déclenchement dans le fonctionnement d’un DATI ?|En cas d’arrachement et/ou d’agression morale|En cas d’arrachement et/ou d’agression psychique|En cas d’arrachement et/ou d’agression physique|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D141" t="str" cm="1">
+        <f t="array" ref="D141:H141">_xlfn.TEXTSPLIT(C141,"|")</f>
+        <v>Quel est l’un des modes de déclenchement dans le fonctionnement d’un DATI ?</v>
+      </c>
+      <c r="E141" t="str">
+        <v>En cas d’arrachement et/ou d’agression morale</v>
+      </c>
+      <c r="F141" t="str">
+        <v>En cas d’arrachement et/ou d’agression psychique</v>
+      </c>
+      <c r="G141" t="str">
+        <v>En cas d’arrachement et/ou d’agression physique</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B142" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C142" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quel est l’un des éléments qui permet le déclenchement du dispositif DATI ?|Le dispositif détecte une position anormale prolongée du travailleur|Le dispositif se déclenche en cas d’intrusion|Le dispositif se déclenche en cas de ronde réalisée partiellement|Le dispositif se déclenche en cas de détonation|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D142" t="str" cm="1">
+        <f t="array" ref="D142:I142">_xlfn.TEXTSPLIT(C142,"|")</f>
+        <v>Quel est l’un des éléments qui permet le déclenchement du dispositif DATI ?</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Le dispositif détecte une position anormale prolongée du travailleur</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Le dispositif se déclenche en cas d’intrusion</v>
+      </c>
+      <c r="G142" t="str">
+        <v>Le dispositif se déclenche en cas de ronde réalisée partiellement</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Le dispositif se déclenche en cas de détonation</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B143" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C143" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Que signifie le sigle DATI ?|Dispositif d’Alarme du Travailleur Isolé|Détecteur Automatique Temporisé d’Intrusion|Dispositif d’Alerte du Travailleur Isolé|Dispositif d’Alarme Travail Intérieur|Dispositif d’Alarme Technique Individuel</v>
+      </c>
+      <c r="D143" t="str" cm="1">
+        <f t="array" ref="D143:I143">_xlfn.TEXTSPLIT(C143,"|")</f>
+        <v>Que signifie le sigle DATI ?</v>
+      </c>
+      <c r="E143" t="str">
+        <v>Dispositif d’Alarme du Travailleur Isolé</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Détecteur Automatique Temporisé d’Intrusion</v>
+      </c>
+      <c r="G143" t="str">
+        <v>Dispositif d’Alerte du Travailleur Isolé</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Dispositif d’Alarme Travail Intérieur</v>
+      </c>
+      <c r="I143" t="str">
+        <v>Dispositif d’Alarme Technique Individuel</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B144" s="17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="C144" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Pour vous, quelle réponse justifierait le port du DATI ?|J’effectue seul(e) une ronde sur un site|Je suis en surveillance de nuit avec 3 autres APS|Je suis affecté au contrôle d’accès d’un site face à l’accueil en activité|Je suis en surveillance derrière la ligne de caisse avec 3 autres APS|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D144" t="str" cm="1">
+        <f t="array" ref="D144:I144">_xlfn.TEXTSPLIT(C144,"|")</f>
+        <v>Pour vous, quelle réponse justifierait le port du DATI ?</v>
+      </c>
+      <c r="E144" t="str">
+        <v>J’effectue seul(e) une ronde sur un site</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Je suis en surveillance de nuit avec 3 autres APS</v>
+      </c>
+      <c r="G144" t="str">
+        <v>Je suis affecté au contrôle d’accès d’un site face à l’accueil en activité</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Je suis en surveillance derrière la ligne de caisse avec 3 autres APS</v>
+      </c>
+      <c r="I144" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B145" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C145" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quelles sont les limites de la basse tension en courant alternatif ?|De 500 V à 800 V|De 50 V à 1000 V|De 500 V à 1000 V|De 50 V à 750 V|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D145" t="str" cm="1">
+        <f t="array" ref="D145:I145">_xlfn.TEXTSPLIT(C145,"|")</f>
+        <v>Quelles sont les limites de la basse tension en courant alternatif ?</v>
+      </c>
+      <c r="E145" t="str">
+        <v>De 500 V à 800 V</v>
+      </c>
+      <c r="F145" t="str">
+        <v>De 50 V à 1000 V</v>
+      </c>
+      <c r="G145" t="str">
+        <v>De 500 V à 1000 V</v>
+      </c>
+      <c r="H145" t="str">
+        <v>De 50 V à 750 V</v>
+      </c>
+      <c r="I145" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B146" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C146" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>En cas de déclenchement du dispositif d’alarme d’un DATI, peut-on localiser avec précision une victime ?|Oui|Non</v>
+      </c>
+      <c r="D146" t="str" cm="1">
+        <f t="array" ref="D146:F146">_xlfn.TEXTSPLIT(C146,"|")</f>
+        <v>En cas de déclenchement du dispositif d’alarme d’un DATI, peut-on localiser avec précision une victime ?</v>
+      </c>
+      <c r="E146" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B147" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C147" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Lors d’un appel du PC de télésurveillance pour une alarme intrusion sur votre site, vous devez en premier lieu :|Noter l’appel sur la main courante ou le cahier de poste|Confirmer votre identité par un mot de passe|Confirmer qu’il n’existe aucune anomalie avant d’avoir fait effectuer une levée de doute|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D147" t="str" cm="1">
+        <f t="array" ref="D147:H147">_xlfn.TEXTSPLIT(C147,"|")</f>
+        <v>Lors d’un appel du PC de télésurveillance pour une alarme intrusion sur votre site, vous devez en premier lieu :</v>
+      </c>
+      <c r="E147" t="str">
+        <v>Noter l’appel sur la main courante ou le cahier de poste</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Confirmer votre identité par un mot de passe</v>
+      </c>
+      <c r="G147" t="str">
+        <v>Confirmer qu’il n’existe aucune anomalie avant d’avoir fait effectuer une levée de doute</v>
+      </c>
+      <c r="H147" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B148" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C148" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Quelles sont les principales qualités d’un système d’alarme ?|Inviolabilité, compatibilité, pluralité, fiabilité, sécurité négative|Inviolabilité, compatibilité, pluralité, fébrilité, sécurité négative|Inviolabilité, compatibilité, pluralité, fiabilité, sécurité positive|Inviolabilité, comptabilité, pluralité, fiabilité, sécurité positive|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D148" t="str" cm="1">
+        <f t="array" ref="D148:I148">_xlfn.TEXTSPLIT(C148,"|")</f>
+        <v>Quelles sont les principales qualités d’un système d’alarme ?</v>
+      </c>
+      <c r="E148" t="str">
+        <v>Inviolabilité, compatibilité, pluralité, fiabilité, sécurité négative</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Inviolabilité, compatibilité, pluralité, fébrilité, sécurité négative</v>
+      </c>
+      <c r="G148" t="str">
+        <v>Inviolabilité, compatibilité, pluralité, fiabilité, sécurité positive</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Inviolabilité, comptabilité, pluralité, fiabilité, sécurité positive</v>
+      </c>
+      <c r="I148" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B149" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C149" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Vous êtes en poste au PC sécurité et une Alarme Incendie retentit|Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue|Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude|Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde|Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D149" t="str" cm="1">
+        <f t="array" ref="D149:I149">_xlfn.TEXTSPLIT(C149,"|")</f>
+        <v>Vous êtes en poste au PC sécurité et une Alarme Incendie retentit</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude</v>
+      </c>
+      <c r="G149" t="str">
+        <v>Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde</v>
+      </c>
+      <c r="H149" t="str">
+        <v>Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone</v>
+      </c>
+      <c r="I149" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B150" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C150" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Votre collègue est en ronde, vous êtes en poste au PC et recevez une alarme intrusion, que faites-vous ?|Vous rejoignez au plus vite votre collègue pour intervenir plus efficacement|Vous effectuez vous-même la levée de doute|Vous demandez à votre collègue de se rendre sur le lieu précis de déclenchement de l’alarme pour effectuer la levée de doute|Vous attendez que votre collègue finisse sa ronde pour intervenir|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D150" t="str" cm="1">
+        <f t="array" ref="D150:I150">_xlfn.TEXTSPLIT(C150,"|")</f>
+        <v>Votre collègue est en ronde, vous êtes en poste au PC et recevez une alarme intrusion, que faites-vous ?</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Vous rejoignez au plus vite votre collègue pour intervenir plus efficacement</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Vous effectuez vous-même la levée de doute</v>
+      </c>
+      <c r="G150" t="str">
+        <v>Vous demandez à votre collègue de se rendre sur le lieu précis de déclenchement de l’alarme pour effectuer la levée de doute</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Vous attendez que votre collègue finisse sa ronde pour intervenir</v>
+      </c>
+      <c r="I150" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B151" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C151" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Vous êtes en poste au PC sécurité et une Alarme Incendie retentit|Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde|Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue|Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude|Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D151" t="str" cm="1">
+        <f t="array" ref="D151:I151">_xlfn.TEXTSPLIT(C151,"|")</f>
+        <v>Vous êtes en poste au PC sécurité et une Alarme Incendie retentit</v>
+      </c>
+      <c r="E151" t="str">
+        <v>Vous finissez ce que vous faisiez vous serez toujours à temps d’envoyer le rondier à son retour de ronde</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Vous appuyez sur l’évacuation générale pour être certain que tout le monde évacue</v>
+      </c>
+      <c r="G151" t="str">
+        <v>Vous arrêtez immédiatement le signal sonore et réarmez la zone, c’est sûrement rien comme d’habitude</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Vous contactez sur le champ votre collègue pour qu’il effectue immédiatement une levée de doute sur zone</v>
+      </c>
+      <c r="I151" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B152" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C152" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Vous êtes en poste, les pompiers arrivent sur le site sinistré. Vous êtes informé que la voie d’accès principale est bloquée par un camion stationné. Que faites-vous en priorité ?|Je propose aux pompiers d’emprunter un autre accès qui est bien libre|J’autorise les pompiers à pousser le camion, ils en ont l’obligation|J’appelle les personnels de l’usine, au point de rassemblement, pour déplacer le véhicule|J’appelle la Fourrière|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D152" t="str" cm="1">
+        <f t="array" ref="D152:I152">_xlfn.TEXTSPLIT(C152,"|")</f>
+        <v>Vous êtes en poste, les pompiers arrivent sur le site sinistré. Vous êtes informé que la voie d’accès principale est bloquée par un camion stationné. Que faites-vous en priorité ?</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Je propose aux pompiers d’emprunter un autre accès qui est bien libre</v>
+      </c>
+      <c r="F152" t="str">
+        <v>J’autorise les pompiers à pousser le camion, ils en ont l’obligation</v>
+      </c>
+      <c r="G152" t="str">
+        <v>J’appelle les personnels de l’usine, au point de rassemblement, pour déplacer le véhicule</v>
+      </c>
+      <c r="H152" t="str">
+        <v>J’appelle la Fourrière</v>
+      </c>
+      <c r="I152" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B153" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C153" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Lors d’un orage, une coupure de courant intervient, que faites-vous ?|Rien|Réarmer le disjoncteur principal|Vous cherchez les bougies|J’applique les consignes|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D153" t="str" cm="1">
+        <f t="array" ref="D153:I153">_xlfn.TEXTSPLIT(C153,"|")</f>
+        <v>Lors d’un orage, une coupure de courant intervient, que faites-vous ?</v>
+      </c>
+      <c r="E153" t="str">
+        <v>Rien</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Réarmer le disjoncteur principal</v>
+      </c>
+      <c r="G153" t="str">
+        <v>Vous cherchez les bougies</v>
+      </c>
+      <c r="H153" t="str">
+        <v>J’applique les consignes</v>
+      </c>
+      <c r="I153" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B154" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C154" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Vous êtes seul sur site lors d’une ronde, vous constatez un incendie, que faites-vous en premier ?|J’appelle les pompiers|Je compose le 17|Je rends compte au PCS et je tente l’extinction|J’ai obligation de prendre un extincteur pour éteindre l’incendie|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D154" t="str" cm="1">
+        <f t="array" ref="D154:I154">_xlfn.TEXTSPLIT(C154,"|")</f>
+        <v>Vous êtes seul sur site lors d’une ronde, vous constatez un incendie, que faites-vous en premier ?</v>
+      </c>
+      <c r="E154" t="str">
+        <v>J’appelle les pompiers</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Je compose le 17</v>
+      </c>
+      <c r="G154" t="str">
+        <v>Je rends compte au PCS et je tente l’extinction</v>
+      </c>
+      <c r="H154" t="str">
+        <v>J’ai obligation de prendre un extincteur pour éteindre l’incendie</v>
+      </c>
+      <c r="I154" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B155" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C155" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Le courant est dangereux à partir de :|700 V en courant alternatif|500 V en courant alternatif|50 V en courant alternatif|25 V en courant continu|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D155" t="str" cm="1">
+        <f t="array" ref="D155:I155">_xlfn.TEXTSPLIT(C155,"|")</f>
+        <v>Le courant est dangereux à partir de :</v>
+      </c>
+      <c r="E155" t="str">
+        <v>700 V en courant alternatif</v>
+      </c>
+      <c r="F155" t="str">
+        <v>500 V en courant alternatif</v>
+      </c>
+      <c r="G155" t="str">
+        <v>50 V en courant alternatif</v>
+      </c>
+      <c r="H155" t="str">
+        <v>25 V en courant continu</v>
+      </c>
+      <c r="I155" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B156" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C156" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Qui délivre l’habilitation électrique ?|L’employeur|Le formateur|Le chargé de travaux|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D156" t="str" cm="1">
+        <f t="array" ref="D156:H156">_xlfn.TEXTSPLIT(C156,"|")</f>
+        <v>Qui délivre l’habilitation électrique ?</v>
+      </c>
+      <c r="E156" t="str">
+        <v>L’employeur</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Le formateur</v>
+      </c>
+      <c r="G156" t="str">
+        <v>Le chargé de travaux</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B157" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C157" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Qu’est-ce qu’une alarme restreinte ?|C’est un signal sonore qui alerte une partie du personnel pour évacuer|C’est un signal visuel et sonore qui informe le PC pour effectuer une levée de doute|C’est un signal sonore qui alerte l’ensemble des occupants pour évacuer|C’est un signal horizontal et vertical qui guide les occupants vers la sortie|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D157" t="str" cm="1">
+        <f t="array" ref="D157:I157">_xlfn.TEXTSPLIT(C157,"|")</f>
+        <v>Qu’est-ce qu’une alarme restreinte ?</v>
+      </c>
+      <c r="E157" t="str">
+        <v>C’est un signal sonore qui alerte une partie du personnel pour évacuer</v>
+      </c>
+      <c r="F157" t="str">
+        <v>C’est un signal visuel et sonore qui informe le PC pour effectuer une levée de doute</v>
+      </c>
+      <c r="G157" t="str">
+        <v>C’est un signal sonore qui alerte l’ensemble des occupants pour évacuer</v>
+      </c>
+      <c r="H157" t="str">
+        <v>C’est un signal horizontal et vertical qui guide les occupants vers la sortie</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B158" s="17">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="C158" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>Dans une usine en activité, suite à un incendie, une évacuation générale es déclenchée, les pompiers arrivent, agent au PC, que faites-vous en priorité ?|Je remets les plans d’évacuation parfaitement à jour aux pompiers qui savent où aller|Je vérifie rapidement les cartes professionnelles des pompiers|Je dépêche un agent pour les accueillir et les guider|Je demande aux agents d’utiliser les extincteurs pour maîtriser l’incendie|Aucune des réponses précédentes</v>
+      </c>
+      <c r="D158" t="str" cm="1">
+        <f t="array" ref="D158:I158">_xlfn.TEXTSPLIT(C158,"|")</f>
+        <v>Dans une usine en activité, suite à un incendie, une évacuation générale es déclenchée, les pompiers arrivent, agent au PC, que faites-vous en priorité ?</v>
+      </c>
+      <c r="E158" t="str">
+        <v>Je remets les plans d’évacuation parfaitement à jour aux pompiers qui savent où aller</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Je vérifie rapidement les cartes professionnelles des pompiers</v>
+      </c>
+      <c r="G158" t="str">
+        <v>Je dépêche un agent pour les accueillir et les guider</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Je demande aux agents d’utiliser les extincteurs pour maîtriser l’incendie</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E37C4B-C686-48C3-B7B7-E495B62B59C4}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB602DE5-6FEA-43CD-A844-B98B58E475E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5425,8 +5425,119 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{739EAF5D-6DEC-4933-BEAA-58326FF9FE6A}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -5924,49 +6035,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>164</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>333903</xdr:colOff>
-      <xdr:row>167</xdr:row>
-      <xdr:rowOff>142972</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7AE77D4-12B9-036F-4FB1-3B175C870297}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:srcRect t="12161"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16049625" y="31337249"/>
-          <a:ext cx="3781953" cy="619223"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6263,8 +6331,8 @@
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="9"/>
-    <col min="3" max="8" width="32.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" style="2" customWidth="1"/>
+    <col min="4" max="9" width="26.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10"/>
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -7389,7 +7457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>10</v>
       </c>
@@ -7402,26 +7470,26 @@
       <c r="D36" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="11" t="s">
         <v>119</v>
       </c>
       <c r="J36" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>10</v>
       </c>
@@ -7434,19 +7502,19 @@
       <c r="D37" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="11" t="s">
         <v>119</v>
       </c>
       <c r="J37" s="10" t="s">
@@ -11144,7 +11212,7 @@
         <v>541</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -11228,7 +11296,7 @@
         <v>541</v>
       </c>
       <c r="J168" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -11677,7 +11745,7 @@
         <v>541</v>
       </c>
       <c r="J184" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -11767,6 +11835,36 @@
   </sheetData>
   <autoFilter ref="A1:J76" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>$J1="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="expression" dxfId="10" priority="5">
+      <formula>$J1="B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="expression" dxfId="9" priority="4">
+      <formula>$J1="C"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>$J1="D"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>$J1="E"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>$J1="F"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB602DE5-6FEA-43CD-A844-B98B58E475E2}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E1CE67B-5322-4F24-BC8F-EF545A960142}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="1124">
   <si>
     <t>UV</t>
   </si>
@@ -5425,70 +5425,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{739EAF5D-6DEC-4933-BEAA-58326FF9FE6A}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -11229,19 +11166,16 @@
         <v>1031</v>
       </c>
       <c r="E166" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G166" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F166" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="J166" s="10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -11836,32 +11770,32 @@
   <autoFilter ref="A1:J76" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J1="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J1="B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J1="C"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$J1="D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$J1="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$J1="F"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E1CE67B-5322-4F24-BC8F-EF545A960142}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15325C94-57E1-4052-A22A-E3F975B2DFE0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste_Questions" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="1200">
   <si>
     <t>UV</t>
   </si>
@@ -5228,6 +5228,234 @@
   </si>
   <si>
     <t>Je demande aux agents d’utiliser les extincteurs pour maîtriser l’incendie</t>
+  </si>
+  <si>
+    <t>A quel moment est rédigé le Plan de Prévention ?</t>
+  </si>
+  <si>
+    <t>Avant la prestation</t>
+  </si>
+  <si>
+    <t>Pendant la prestation</t>
+  </si>
+  <si>
+    <t>Après la prestation</t>
+  </si>
+  <si>
+    <t>Vous les réorientez vers le point de rassemblement</t>
+  </si>
+  <si>
+    <t>Vous ne faites rien car il s’agit d’un exercice</t>
+  </si>
+  <si>
+    <t>Aucune des réponse précédentes</t>
+  </si>
+  <si>
+    <t>Que signifie POI ?</t>
+  </si>
+  <si>
+    <t>Processus d’Organisation Interne</t>
+  </si>
+  <si>
+    <t>Plan d’Opération Interne</t>
+  </si>
+  <si>
+    <t>Processus Optimisé Industriel</t>
+  </si>
+  <si>
+    <t>Plan Obligatoire d’Intervention</t>
+  </si>
+  <si>
+    <t>Le pictogramme sur fond vert indique :</t>
+  </si>
+  <si>
+    <t>Un panneau d’avertissement de danger</t>
+  </si>
+  <si>
+    <t>Un panneau concernant le matériel ou l’équipement de lutte contre l’incendie</t>
+  </si>
+  <si>
+    <t>Un panneau d’interdiction</t>
+  </si>
+  <si>
+    <t>Un panneau de sauvetage et de secours</t>
+  </si>
+  <si>
+    <t>Quel est le rôle du Document Unique (DU) ?</t>
+  </si>
+  <si>
+    <t>Analyser les dangers et la gestion des risques</t>
+  </si>
+  <si>
+    <t>N’est pas obligatoire</t>
+  </si>
+  <si>
+    <t>Identifier les dangers et évaluer les risques</t>
+  </si>
+  <si>
+    <t>Identifier les risques et les conditions de travail</t>
+  </si>
+  <si>
+    <t>L’inspecteur du travail</t>
+  </si>
+  <si>
+    <t>Le médecin du travail</t>
+  </si>
+  <si>
+    <t>Les salariés</t>
+  </si>
+  <si>
+    <t>Les entreprises extérieures</t>
+  </si>
+  <si>
+    <t>Vous rappelez l’interdiction de fumer</t>
+  </si>
+  <si>
+    <t>Vous interdisez immédiatement à la personne de fumer</t>
+  </si>
+  <si>
+    <t>Du droit de retrait en cas de danger potentiel et dangereux</t>
+  </si>
+  <si>
+    <t>Du droit d’alerte en cas de danger grave et imminent</t>
+  </si>
+  <si>
+    <t>Du droit d’alerte en cas de danger potentiel et dangereux</t>
+  </si>
+  <si>
+    <t>Du droit de retrait en cas de danger grave et imminent</t>
+  </si>
+  <si>
+    <t>Que signifie l’abrégé P.P.I. ?</t>
+  </si>
+  <si>
+    <t>Plan Particulier d’Intervention</t>
+  </si>
+  <si>
+    <t>Plan Particulier d’Investigation</t>
+  </si>
+  <si>
+    <t>Plan Particulier d’inter population</t>
+  </si>
+  <si>
+    <t>La directive SEVESO est applicable pour ?</t>
+  </si>
+  <si>
+    <t>Les établissement recevant du public (EPR)</t>
+  </si>
+  <si>
+    <t>Certaines installations classées pour la protection de l’environnement</t>
+  </si>
+  <si>
+    <t>Les immeubles de grande hauteur (IGH)</t>
+  </si>
+  <si>
+    <t>Quelle protection doit avoir un appareil électrique dans une zone ATEX ?</t>
+  </si>
+  <si>
+    <t>Protection de classe 2</t>
+  </si>
+  <si>
+    <t>Protection anti-explosion</t>
+  </si>
+  <si>
+    <t>Les risques professionnels comprennent :</t>
+  </si>
+  <si>
+    <t>Les maladies personnelles</t>
+  </si>
+  <si>
+    <t>Les dommages incorporels des accidents domestiques</t>
+  </si>
+  <si>
+    <t>Les maladies professionnelles</t>
+  </si>
+  <si>
+    <t>Les dommages matériels liés aux accidents du travail</t>
+  </si>
+  <si>
+    <t>Comment sera classée une centrale nucléaire ?</t>
+  </si>
+  <si>
+    <t>Les établissements recevant du public (EPR)</t>
+  </si>
+  <si>
+    <t>Un véhicule transportant des matières dangereuses est-il classé comme ICPE ?</t>
+  </si>
+  <si>
+    <t>Oui, dans tous les cas</t>
+  </si>
+  <si>
+    <t>Oui, mais seulement lorsdqu’il transporte une quantité importante de produit</t>
+  </si>
+  <si>
+    <t>Que est le rôle du CHSCT (avant la réforme du Code du Travail au 31/08/2017)</t>
+  </si>
+  <si>
+    <t>Participe à protéger la santé et la sécurité des directeurs de l’entreprise</t>
+  </si>
+  <si>
+    <t>Participe à protéger la santé et la sécurité des salariés de l’entreprise</t>
+  </si>
+  <si>
+    <t>Participe à financer la retraite des salariés de l’entreprise</t>
+  </si>
+  <si>
+    <t>Quel type de risque n’est pas considéré comme un risque majeur ?</t>
+  </si>
+  <si>
+    <t>Risque naturel</t>
+  </si>
+  <si>
+    <t>Risque technologique</t>
+  </si>
+  <si>
+    <t>Risque lié aux transports collectifs</t>
+  </si>
+  <si>
+    <t>Risque lié aux conflits</t>
+  </si>
+  <si>
+    <t>Un plan de prévention doit être obligatoirement écrit lorsque :</t>
+  </si>
+  <si>
+    <t>Les travaux sont d’une durée totale d’au moins 400 heurs sur 12 mois</t>
+  </si>
+  <si>
+    <t>Les travaux présentent des risques particuliers</t>
+  </si>
+  <si>
+    <t>Lors d’un exercice d’évacuation, vous constatez que les personnels ne respectent pas le point de rassemblement mentionné sur les plans d'évacuation. Que faites-vous ?</t>
+  </si>
+  <si>
+    <t>Vous laissez faire car les personnels sont à l’extérieur de l’immeuble, ce qui est le plus important</t>
+  </si>
+  <si>
+    <t>Vous leur indiquez le point de rassemblement, mais vous laissez faire</t>
+  </si>
+  <si>
+    <t>Pouvez vous utiliser votre téléphone portable personnel sur une zone présentant un pictogramme orange portant l'inscription "EX" ?</t>
+  </si>
+  <si>
+    <t>Le Document Unique (DU) est tenu à la disposition de certains acteurs. Lequel n'y a pas accès ?</t>
+  </si>
+  <si>
+    <t>Sur un site, une personne fume à proximité d’un pictogramme indiquant la présence de matières inflammables : quelle est votre réaction ?</t>
+  </si>
+  <si>
+    <t>Vous prévenez votre PC de sécurité</t>
+  </si>
+  <si>
+    <t>En cas d’absence de prévention ou d’échec de celle-ci, de quels moyens dispose le salarié pour alerter son employeur ou se prémunir d'une situation dangereuse ?</t>
+  </si>
+  <si>
+    <t>Les installations classées pour la protection de l’environnement</t>
+  </si>
+  <si>
+    <t>Participe à protéger exclusivement la santé et la sécurité des clients de l'entreprise</t>
+  </si>
+  <si>
+    <t>Les travaux concernent la coactivité sur les chantiers de bâtiment et de génie civil</t>
   </si>
 </sst>
 </file>
@@ -6263,7 +6491,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
@@ -9801,7 +10029,7 @@
         <v>541</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -9989,7 +10217,7 @@
         <v>541</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -11764,6 +11992,489 @@
       </c>
       <c r="J187" s="10" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J188" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J189" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J190" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J191" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J192" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J193" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J194" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J195" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J196" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J197" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J198" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J199" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J200" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J201" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J202" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="J203" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J204" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J205" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -11800,7 +12511,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="355" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15325C94-57E1-4052-A22A-E3F975B2DFE0}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CBEB89E-8F5C-4FAC-96A6-1B70A9A4549D}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste_Questions" sheetId="1" r:id="rId1"/>
@@ -18,31 +18,85 @@
     <sheet name="Feuil1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_1h997plu2r3q" localSheetId="2">Feuil1!$A$169</definedName>
     <definedName name="_1x11d5k5io24" localSheetId="2">Feuil1!$A$26</definedName>
     <definedName name="_25b71xk2i301" localSheetId="2">Feuil1!$A$109</definedName>
     <definedName name="_2k99lr79hl9i" localSheetId="2">Feuil1!$A$5</definedName>
     <definedName name="_2utln1nfnqsx" localSheetId="2">Feuil1!$A$2</definedName>
+    <definedName name="_3bxdsxq7p8gw" localSheetId="2">Feuil1!$A$165</definedName>
+    <definedName name="_5ocrwot4q9or" localSheetId="2">Feuil1!$A$210</definedName>
     <definedName name="_62p8mewzupdh" localSheetId="2">Feuil1!$A$9</definedName>
+    <definedName name="_63ehbuvcc3tw" localSheetId="2">Feuil1!$A$174</definedName>
+    <definedName name="_6g3puvkrrskn" localSheetId="2">Feuil1!$A$173</definedName>
     <definedName name="_6sxpqe84lwy" localSheetId="2">Feuil1!$A$27</definedName>
+    <definedName name="_76u3b285zost" localSheetId="2">Feuil1!$A$191</definedName>
+    <definedName name="_76x8livz92e3" localSheetId="2">Feuil1!$A$207</definedName>
+    <definedName name="_7npq3rapq3b5" localSheetId="2">Feuil1!$A$211</definedName>
     <definedName name="_847vco2er5vx" localSheetId="2">Feuil1!#REF!</definedName>
+    <definedName name="_8i1gdydhdqo8" localSheetId="2">Feuil1!$A$206</definedName>
     <definedName name="_8vd2wc5v9auo" localSheetId="2">Feuil1!$A$12</definedName>
+    <definedName name="_92rzspumfy17" localSheetId="2">Feuil1!$A$204</definedName>
+    <definedName name="_9hexdyk5v0wx" localSheetId="2">Feuil1!$A$167</definedName>
+    <definedName name="_9jeesbxf4272" localSheetId="2">Feuil1!$A$193</definedName>
+    <definedName name="_9o8iqnw0882k" localSheetId="2">Feuil1!$A$181</definedName>
+    <definedName name="_a1blj5gc9j8j" localSheetId="2">Feuil1!$A$163</definedName>
+    <definedName name="_a20iajxrewtn" localSheetId="2">Feuil1!$A$212</definedName>
+    <definedName name="_a75ul79bzp21" localSheetId="2">Feuil1!$A$179</definedName>
     <definedName name="_atn6jtpgu1zu" localSheetId="2">Feuil1!$A$6</definedName>
+    <definedName name="_b77wlvmmh9wq" localSheetId="2">Feuil1!$A$176</definedName>
     <definedName name="_be1fc6ea00hk" localSheetId="2">Feuil1!$A$24</definedName>
+    <definedName name="_byzztlualq0q" localSheetId="2">Feuil1!$A$198</definedName>
+    <definedName name="_ccy2pemctn8p" localSheetId="2">Feuil1!$A$178</definedName>
+    <definedName name="_chgzqrac0okr" localSheetId="2">Feuil1!$A$161</definedName>
+    <definedName name="_dwwrsfcgojso" localSheetId="2">Feuil1!$A$171</definedName>
     <definedName name="_e8p5frs5ytai" localSheetId="2">Feuil1!$A$3</definedName>
     <definedName name="_eltq1ml39i8g" localSheetId="2">Feuil1!$A$110</definedName>
+    <definedName name="_f4und4vdlss2" localSheetId="2">Feuil1!$A$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste_Questions!$A$1:$J$76</definedName>
+    <definedName name="_g0y5qe76r34g" localSheetId="2">Feuil1!$A$195</definedName>
     <definedName name="_g70xgby2qf4" localSheetId="2">Feuil1!$A$4</definedName>
+    <definedName name="_g8ek9utgccwp" localSheetId="2">Feuil1!$A$209</definedName>
     <definedName name="_g9qmie434sne" localSheetId="2">Feuil1!$A$10</definedName>
+    <definedName name="_gawbf46ma6oj" localSheetId="2">Feuil1!$A$201</definedName>
+    <definedName name="_gelkcw7y8ynz" localSheetId="2">Feuil1!$A$199</definedName>
+    <definedName name="_hdt4xnw2zsex" localSheetId="2">Feuil1!$A$197</definedName>
+    <definedName name="_hm9eh7d297ex" localSheetId="2">Feuil1!$A$186</definedName>
     <definedName name="_hplm79wzz7gn" localSheetId="2">Feuil1!#REF!</definedName>
+    <definedName name="_i1nfs8unu8of" localSheetId="2">Feuil1!$A$185</definedName>
     <definedName name="_i84ik2pub0j3" localSheetId="2">Feuil1!$A$23</definedName>
+    <definedName name="_ieozcmlv3r2" localSheetId="2">Feuil1!$A$184</definedName>
+    <definedName name="_iqeveq8of09t" localSheetId="2">Feuil1!$A$168</definedName>
+    <definedName name="_j9lo7fkxjlb" localSheetId="2">Feuil1!$A$160</definedName>
+    <definedName name="_kc00q4gy8hb8" localSheetId="2">Feuil1!$A$183</definedName>
+    <definedName name="_kg2jlon5v06" localSheetId="2">Feuil1!$A$192</definedName>
+    <definedName name="_kor4i06yw3hg" localSheetId="2">Feuil1!$A$190</definedName>
+    <definedName name="_kwnngch1lt48" localSheetId="2">Feuil1!$A$196</definedName>
+    <definedName name="_lx174ek5g80a" localSheetId="2">Feuil1!$A$200</definedName>
     <definedName name="_nyqwx0jkl5qi" localSheetId="2">Feuil1!$A$33</definedName>
+    <definedName name="_nz347gkbav67" localSheetId="2">Feuil1!$A$180</definedName>
+    <definedName name="_odb06e873shv" localSheetId="2">Feuil1!$A$182</definedName>
     <definedName name="_p9wiu4shs9hc" localSheetId="2">Feuil1!$A$112</definedName>
+    <definedName name="_pzw7706yg5ao" localSheetId="2">Feuil1!$A$162</definedName>
+    <definedName name="_qf459c9a8pp1" localSheetId="2">Feuil1!$A$194</definedName>
+    <definedName name="_qxb3o5v8mgjr" localSheetId="2">Feuil1!$A$172</definedName>
+    <definedName name="_r9s9ghg1e3hf" localSheetId="2">Feuil1!$A$189</definedName>
+    <definedName name="_sicn53eiffia" localSheetId="2">Feuil1!$A$166</definedName>
     <definedName name="_tt764b9auzq8" localSheetId="2">Feuil1!$A$8</definedName>
+    <definedName name="_u74njex1xmue" localSheetId="2">Feuil1!$A$202</definedName>
     <definedName name="_u9haniwxsi9j" localSheetId="2">Feuil1!$A$16</definedName>
+    <definedName name="_utuurwq44qbd" localSheetId="2">Feuil1!$A$214</definedName>
+    <definedName name="_v2a1uzdymhjv" localSheetId="2">Feuil1!$A$205</definedName>
+    <definedName name="_vdgtxnft4z9o" localSheetId="2">Feuil1!$A$164</definedName>
     <definedName name="_vk618iff2ee1" localSheetId="2">Feuil1!$A$111</definedName>
+    <definedName name="_vs7np853i52g" localSheetId="2">Feuil1!$A$177</definedName>
+    <definedName name="_vyvwb23eh5z1" localSheetId="2">Feuil1!$A$208</definedName>
+    <definedName name="_w3sb88kffkq" localSheetId="2">Feuil1!$A$213</definedName>
     <definedName name="_wpn81467iw0b" localSheetId="2">Feuil1!$A$7</definedName>
+    <definedName name="_x6nck1a900y" localSheetId="2">Feuil1!$A$187</definedName>
     <definedName name="_xgrsy6hezdp9" localSheetId="2">Feuil1!$A$25</definedName>
+    <definedName name="_y4xt3quxwyvi" localSheetId="2">Feuil1!$A$175</definedName>
     <definedName name="_yj4hh6ff2wx9" localSheetId="2">Feuil1!$A$28</definedName>
+    <definedName name="_yyxysi2ip7um" localSheetId="2">Feuil1!$A$203</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="1507">
   <si>
     <t>UV</t>
   </si>
@@ -5457,12 +5511,933 @@
   <si>
     <t>Les travaux concernent la coactivité sur les chantiers de bâtiment et de génie civil</t>
   </si>
+  <si>
+    <t>1 - [UV7] Que signifie le R de N.R.B.C-E ?|Radiologique|Radicalisé|Radioactif|Aucune des autres réponses|Rayonnant|A</t>
+  </si>
+  <si>
+    <t>2 - [UV7] Le Pneumothorax peut être occasionné par :|Toutes les réponses sont bonnes|Une explosion (Blast primaire)|Une perforation par une côte|Une plaie pénétrante par arme blanche|Une plaie pénétrante par balle|A</t>
+  </si>
+  <si>
+    <t>3 - [UV7] Parmi ces infractions, laquelle porte atteinte aux intérêts fondamentaux de la nation ?|La délation|L’abus de droit public|La rébellion|Le sabotage|La violation de domicile|D</t>
+  </si>
+  <si>
+    <t>4 - [UV7] Dans le cadre d’un risque d’attentat, que peut faire le Préfet ?|Décréter l’état d’urgence, mais seulement au niveau “vigilance”|Faire procéder à des fouilles à corps par des ASP|Accroître les contrôles aux frontières|Aucune des autres réponses|Interdire la circulation, instaurer un couvre-feu et limiter les allées/venues des personnes|E</t>
+  </si>
+  <si>
+    <t>5 - [UV7] Témoin direct d’un attentat en cours sur votre site, quelles consignes à suivre sont les plus appropriées ?|Alerter les personnes autour de vous|Si possible, aider les autres personnes à s’échapper|Laisser vos affaires derrière vous|Si vous ne pouvez pas courir, se confiner, éteindre la lumière et couper le son des appareils à proximité|Toutes les réponses précédentes sont exactes|E</t>
+  </si>
+  <si>
+    <t>6 - [UV11] Un groupe d’individus cagoulés et armés pénètre dans votre établissement et vous êtes seul : que faites-vous ?|J’appelle la relève pour me venir en aide le plus tôt possible|Je m’enfuis et je fais appel aux forces de l’ordre le plus rapidement possible|Je m’enfuis si je peux ou sinon je me confine, et je contacte le 114 par sms|Aucune des autres réponses|Je dois agir physiquement pour les expulser de l’établissement|C</t>
+  </si>
+  <si>
+    <t>7 - [UV9] Un agent de prévention et de sécurité a-t-il le droit de pratiquer des palpations de sécurité lors de manifestations sportives, récréatives ou culturelles ?|Oui, en toutes circonstances|Oui, s’il est habilité par son entreprise|Non, sauf s’il est habilité par son employeur|Aucune des autres réponses|Oui, si la manifestation dépasse 300 personnes et sous le contrôle d’un OPJ et que la personne palpée soit du même sexe que l’agent de sécurité|E</t>
+  </si>
+  <si>
+    <t>8 - [UV9] Je suis agent dans un établissement : sous quelles conditions ai-je le droit d’inspecter des sacs ?|Je peux faire une inspection visuelle même si ce n’est pas dans les consignes|Aucune des autres réponses|Si c’est prévu dans les consignes, je peux fouiller les sacs sans avoir besoin du consentement du propriétaire|J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille|Je peux vérifier visuellement et fouiller tous les sacs|D</t>
+  </si>
+  <si>
+    <t>9 - [UV11] En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?|D.A.S.|C.M.S.I.|S.M.S.I.|S.D.I.|Aucune des réponses précédentes|D</t>
+  </si>
+  <si>
+    <t>10 - [UV7] Que dois-je regarder pour détecter un potentiel terroriste ?|Son comportement|La pratique de sa religion|Aucune des autres réponses|Ses antécédents judiciaires|Son apparence physique|A</t>
+  </si>
+  <si>
+    <t>11 - [UV7] Qu’est-ce que la zone d’exclusion dans un périmètre de sécurité immédiat ?|La zone de prise en charge par les secours|La zone de danger et d’intervention|La zone de commandement des forces de l’ordre|Aucune des autres réponses|La zone d’accueil des force de l’ordre et des secours|B</t>
+  </si>
+  <si>
+    <t>12 - [UV2] Un revolver chambré pour le calibre 38 spécial est une arme de catégorie :|C|D|A|Aucune des autres réponses|B|B</t>
+  </si>
+  <si>
+    <t>13 - [UV2] Le vol avec arme est qualifié de :|Crime terroriste|Aucune des autres réponses|Délit qualifié|Délit aggravé|Crime|E</t>
+  </si>
+  <si>
+    <t>14 - [UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein de périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :|Sans le consentement de son conducteur, par un agent de prévention et de sécurité|Sans le consentement de son conducteur, par un agent de prévention et de sécurité mais sous le contrôle d’un OPJ|Avec le consentement de son conducteur, par un agent de prévention et de sécurité|Avec le consentement de son conducteur, par un agent de prévention et de sécurité placé sous l’autorité d’un OPJ|Aucune des autres réponses|E</t>
+  </si>
+  <si>
+    <t>15 - [UV12] Le fait d’accéder frauduleusement à des données informatiques issues d’images de vidéosurveillance constitue l’infraction de :|Atteinte au système de traitement automatisé de données|Entrave à la libre circulation des données|Dégradation ou détérioration d’un système de traitement de données informatiques |Aucune des autres réponses|Vol de données informatiques|A</t>
+  </si>
+  <si>
+    <t>16 - [UV12] Que signifie l’acronyme P.I.F. dans le cadre d’un système de sécurité lors d’un événement ?|Point ou Poste d’Inspection Filtrage|Poste Itinérant de Filtrage|Passage Interdit à la Foule|Aucune des autres réponses|Permis d’Inspection et de Fouille|A</t>
+  </si>
+  <si>
+    <t>17 - [UV12] Le plan ORSEC est :|Aucune des autres réponses|Un plan de limitation des déplacements dans le cadre du plan Vigipirates “Urgence Attentat”|Un plan d’Organisation de la Réponses de la Sécurité Civile|Un plan de circulation des riverains lors des événement culturels ou festifs|Un plan d’intervention coordonné des forces de l’ordre publiques et privées|C</t>
+  </si>
+  <si>
+    <t>18 - [UV8] Suite à un vol dans un magasin, le chef de poste du PCS reçoit les forces de l’ordre et il peut déposer plainte :|Non, car c’est du ressort exclusif d’un responsable du magasin habilité|Oui, seulement en l’absence du responsable du magasin|Aucune des autres réponses|Oui, car il est le chef de poste et il est donc habilité à déposer plainte|Oui, s’il a l’accord du responsable du magasin|A</t>
+  </si>
+  <si>
+    <t>19 - [UV8] Une zone de protection périphérique concerne :|Un objet précis|Aucune des autres réponses|Un local|Une vitrine|Une clôture|E</t>
+  </si>
+  <si>
+    <t>20 - [UV8] Une zone de protection ponctuelle concerne :|Un local|Aucune des autres réponses|Une vitrine|Une clôture|Un objet précis|E</t>
+  </si>
+  <si>
+    <t>21 - [UV8] Les convoyeurs de fonds peuvent-ils être armés lorsqu’ils effectuent en véhicule banalisé un transport de fonds, bijoux ou métaux précieux ?|Oui, avec l’autorisation du Préfet|Non, ils ne peuvent pas être armés|Oui, si la valeur des biens est supérieure à 1,3 millions d’euros|Aucune des autres réponses|Oui sur ordre de la société|B</t>
+  </si>
+  <si>
+    <t>22 - [UV7] Que signifie NRBC-E ?|Nationaliste-Radiologique-Bactériologique-Cyberterrorisme et Explosive|Nucléaire-Radiologique-Biologique-Chimique et Explosive|Nucléaire-Radiotechnologique-Bactériologique-Catastrophique et Explosive|Nationaliste-Régionaliste-Bracage-Contrôle et Enlèvement|Aucune des autres réponses|B</t>
+  </si>
+  <si>
+    <t>23 - [UV7] En cas de plan Vigipirate, l’accès à n’importe quel établissement peut être soumis à une palpation de sécurité : qui peut en décider ?|Le Préfet par un arrêté spécifique|L’agent de sécurité si les consignes spéciales le prévoyants|Le chef d’établissement dans son règlement intérieur|Le CNAPS par une circulaire ministérielle|Aucune des autres réponses|A</t>
+  </si>
+  <si>
+    <t>24 - [UV7] Qu’est-ce que l’état d’urgence ?|Un régime exceptionnel qui permet à l’Etat français de gérer une crise|Un régime qui donne des pouvoirs supplémentaires aux agents de prévention et de sécurité|Un régime continu servant à instaurer un climat de sécurité au peuple|Un régime totalitaire qui octroie les pleins pouvoirs au Président de la République|Aucune des autres réponses|A</t>
+  </si>
+  <si>
+    <t>25 - [UV7] Suite à une blessure par balle sur le torse d’une victime, comment puis-je la secourir sans provoquer un pneumothorax ?|Aucune des autres réponses|En posant dès que possible un garrot|En réalisant un pansement 3 côtés|En bouchant le trou formé par l’impact avec ma main|En mettant en place la réanimation cardio-pulmonaire|C</t>
+  </si>
+  <si>
+    <t>26 - [UV7] Quelles sont les grandes priorités de réaction que je dois adopter face à une attaque terroriste ?|Courir, m'enfermer, appeler, attaquer si nécessaire|M’échapper, me cacher, secourir, combattre systématiquement|Alerter, éteindre, méloigner, boxer|Aucune des autres réponses|A</t>
+  </si>
+  <si>
+    <t>27 - [UV7] Qu’est-ce que le terrorisme d’Etat ?|Aucune des autres réponses|Lorsqu’un peuple terrorise son gouvernement|Lorsqu’un Etat terrorise son peuple|Lorsqu’un Etat combat de le terrorisme à l’intérieur de ses frontières|Lorsqu’une organisation terroriste veut prendre le pouvoir d’un Etat|C</t>
+  </si>
+  <si>
+    <t>28 - [UV2] Un agent de sécurité exerçant ses fonctions dans un parc d’attraction peut-il appréhender un individu qui y entre avec une matraque et tente d’agresser un salarié du parc ?|Il peut juste l’aborder mais il ne peut pas l’appréhender en vertu de l’art. 73 du CPP|Aucune des autres réponses|Oui, car il sera dans le cadre de l’état de nécessité prévu dans l’art. 121-2 du Code Pénal|Non, car il n’y a pas d’infraction prévue pour ce type de fait|Le port d’une matraque constituant un délit, il peut appréhender l’individu au titre de l’art. 73 du CPP|E</t>
+  </si>
+  <si>
+    <t>29 - [UV2] Un agent de sécurité privé peut être sanctionné par le CNAPS :|À une pénalité financière mais sans limite prise en charge par l’entreprise|À aucune pénalité financière|À une pénalité financière allant jusqu’à 10 000 euros|À une pénalité financière allant jusqu’à 7 500 euros|À une pénalité financière inférieure à 1 500 euros|D</t>
+  </si>
+  <si>
+    <t>30 - [UV12] À quoi peut servir un PPI/POI/PER ?|Aucune des autres réponses|À coordonner les moyens internes des installations classées|À prévoir la mobilisation des services de secours publics|À protéger les installations recevant du public|À planifier les opérations de maintien de l’ordre|C</t>
+  </si>
+  <si>
+    <t>31 - [UV12] Il est puni par le code du sport (L332-3) dans une enceinte sportive, lors du déroulement ou de la retransmission en public d’une manifestation sportive :|Le fait d’introduire ou de tenter d’introduire, par force ou par fraude, des boissons alcoolisées|Toutes les réponses sont exactes|Le fait d’avoir, en état d’ivresse, pénétré ou tenté de pénétrer par force ou par fraude|D’un an d’emprisonnement ou d’amende|Le fait d’accéder en état d’ivresse|A</t>
+  </si>
+  <si>
+    <t>32 - [UV12] Les organisateurs de manifestations sportives, récréatives ou culturelles sont tenus (R211-22 du CSI) :|D’en faire la déclaration uniquement si elles sont sur la liste des événements exposés|D’en faire la déclaration au Préfet de région au moins un an avant l’événement|D’en faire la déclaration aux maires ou aux Préfets de police, si la manifestation peut atteindre plus de 1500 personnes|Aucune des autres réponses|D’en faire la déclaration aux maires si la manifestation peut atteindre plus de 300 personnes et aux Préfets si elle dépasse plus de 1500 personnes|C</t>
+  </si>
+  <si>
+    <t>33 - [UV9] Je suis agent dans un magasin : sous quelles conditions ai-je le droit d’inspecter des sacs ?|Je peux faire une inspection visuelle, dès lors que j’ai un doute|Je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaire|Aucune des autres réponses|J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille|Si c’est prévu dans les consignes, je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaires|D</t>
+  </si>
+  <si>
+    <t>34 - [UV8] Qu’est-ce qu’une zone de protection ?|Lieu protégé par des filets empêchant l’introduction de pigeons dans le site|Lieu protégé par des paroies possédant une isolation phonique|Aucune des autres réponses|Lieu protégé contre les intempéries|Lieu protégé par un obstacle s’opposant à pénétration d’intrus dans le site|E</t>
+  </si>
+  <si>
+    <t>35 - [UV8] Un point dit vulnérable lors d’une ronde est :|Un point comportant un danger permanent|Un point qui en cas d’atteinte pourrait handicaper le bon fonctionnement de l’entreprise|Un point régulièrement mis en défaut|Aucune des autres réponses|Un point sensible convoité par les voleurs|B</t>
+  </si>
+  <si>
+    <t>36 - [UV8] Pendant votre ronde, vous découvrez un local en désordre avec un pied de biche au sol. Que faites-vous ?|Vous ramassez le pied de biche afin d’avoir un objet pour vous défendre|Vous prévenez immédiatement le PCS et inspecter prudemment les locaux voisins|Aucune des autres réponses|Vous ne faites rien et continuez votre rondre, c’est sûrement le bureau d’un salarié désordonné|Vous refermez la porte et prévenez le PCS|B</t>
+  </si>
+  <si>
+    <t>37 - [UV6] Un agent de sécurité privé masculin doit appréhender un voleur en sortie de caisse, mais il s’agit d’une femme :|Il doit appeler une collègue du même sexe|Il agit normalement, néanmoins il est conseillé d’appeler un témoin féminin|Aucune des autres réponses|Il doit demander l’autorisation de la personne|Il ne peut rien faire sur une personne de sexe opposé|B</t>
+  </si>
+  <si>
+    <t>38 - [UV2] Les agents de sécurité employés par un bailleur d’immeuble à usage d’habitations peuvent être armés :|D’un bâton de défense de type TONFA|D’un fusil à pompe|D’une grenade lacrymogène ayant une capacité inférieure à 100 ml|Aucune des autres réponses|D’un pistolet mitrailleur|A</t>
+  </si>
+  <si>
+    <t>39 - [UV12] Le schéma d’installation de la vidéoprotection permet :|D’installer, de maintenir et de mettre à disposition des prestataires des images|De capter, de transmettre, de stocker, de visionner les images|Aucune des autres réponses|De garantir aux forces de l’ordre la bonne réalisation de la mission de sûreté|De compléter le système de surveillance incendie|B</t>
+  </si>
+  <si>
+    <t>40 - [UV12] À quoi correspond une crash barrière ?|Aucune des autres réponses|Un système de barrière type passage à niveau pour bloquer les accès|Des barrières de sécurité équipés de pieds empêchant le renversement|Un test en laboratoire de la résistance des barrières|L’action de lancer des barrières sur des véhicules voulant forcer l’accès|C</t>
+  </si>
+  <si>
+    <t>41 - [UV12] Un APS effectue une ronde dans la chaufferie gaz, il peut y entrer si :|Il dispose d’une radio fabriquée après le 1er juillet 2017|Il dispose d’un matériel anti-déflagrant|Il dispose d’un émetteur multi-fréquences|Il dispose d’une pastille de détection de gaz homologuée|Aucune des autres réponses|B</t>
+  </si>
+  <si>
+    <t>42 - [UV11] Sur votre GTB/GTC vous recevez une alarme SURCHAUFF au niveau de la chaufferie. Que devez-vous faire en premier ?|Aucune des autres réponses|Arrêter le signal sonore de l’alarme|Appeler les services de secours|Couper la chaudière|Appeler le technicien compétent|B</t>
+  </si>
+  <si>
+    <t>43 - [UV11] En vous rendant sur une levée de doute intrusion, votre PC vous appelle car une détection incendie vient d’avoir lieu. Que faites-vous ?|Je termine la levée de doute intrusion sans effectuer les contrôles de rigueur pour aller sur la levée de doute incendie|Je fais demi-tour et priorise la détection incendie dont la gravité peut être supérieure|Aucune des autres réponses|Je poursuis la levée de doute intrusion, étant presque arrivé|Je demande au chef de poste d’effectuer lui-même la levée de doute incendie|B</t>
+  </si>
+  <si>
+    <t>44 - [UV11] En cas d’alarme observée sur la centrale incendie, quelle est généralement la procédure à suivre ?|Appel de l’astreinte incendie, attente des secours, intervention éventuelle sur le feu|Acquittement du signal sonore, lecture de l’information, levée de doute, plan d’action conforme aux consignes du site|Aucune des autres réponses|Levée de doute, appel des secours, retour au PCS|Intervention immédiate sur feu, appel des secours, réinitialisation central incendie|B</t>
+  </si>
+  <si>
+    <t>45 - [UV9] Quelles sont les méthodes pour les agents masculins pour effectuer des vérifications de sécurité sur des femmes qui sont au contrôle d’accès :|Les palpations de sécurité|La fouille à corps uniquement avec le consentement de la personne|La fouille au corps|Aucune des autres réponses|Le contrôle visuel des bagages|E</t>
+  </si>
+  <si>
+    <t>46 - [UV9] Dans quelle situation puis-je effectuer des palpations de sécurité ?|Dans tout le magasin sur des personnes soupçonnées de vouloir fumer|À l’intérieur d’une salle de concert à la demande du chef de poste|Dans tout lieu visé par un arrêté préfectoral|À la sortie du magasin sur un individu connu pour des actes de vol|Aucune des autres réponses|C</t>
+  </si>
+  <si>
+    <t>47 - [UV8] Certaines circonstances peuvent aggraver le vol. Par exemple quand le vol est commis :|Par plusieurs personnes|Chez une personne dépositaire de l’autorité publique|Sur une personne dans la journée|Aucune des autres réponses|Dans un local sous surveillance électronique|A</t>
+  </si>
+  <si>
+    <t>48 - [UV7] Dès l’arrivée des forces de l’ordre, dans une zone d’attentat, vous devez en premier :|Leur parler de la situation|Courir vers eux|Leur indiquer l’emplacement des victimes|Suivre leurs instructions|Aucune des autres réponses|D</t>
+  </si>
+  <si>
+    <t>49 - [UV7] Parmi les types de “BLAST” suivants, lequel ou lesquels existent ?|BLAST primaire|BLAST tertiaire|BLAST quaternaire|Toutes les réponses précédentes sont exactes|BLAST secondaire|D</t>
+  </si>
+  <si>
+    <t>50 - [UV2] Agent de sécurité, je dispose d’un véhicule d’entreprise équipé d’un gyrophare orange :|Aucune des autres réponses|C’est absolument interdit|C’est autorisé uniquement à l’intérieur des sites surveillés, si les consignes le prévoient|Seuls les gyrophares bleus sont autorisés pour les agents de sécurité|C’est interdit, sauf en situation d’urgence attentat|C</t>
+  </si>
+  <si>
+    <t>51 - [UV2] Selon la loi, est une arme par destination :|Tout objet conçu pour usage professionnel|Tout objet conçu pour tuer ou blesser|Aucune des autres réponses|Tout objet susceptible de présenter un danger pour des personnes, dès lors qu’il est utilisé pour menacer|Tout objet pouvant causer des dommages|D</t>
+  </si>
+  <si>
+    <t>52 - [UV11] Le report d’alarme d’une centrale intrusion est un dispositif :|Uniquement destiné aux équipes de sûreté en cas d’intrusion|De secours en cas de défaillance du clavier principal|Qui permet aux agents d’accéder à certaines informations hors du PCS|De cloisonnement anti-intrusion indépendant du système central|Aucune des autres réponses|C</t>
+  </si>
+  <si>
+    <t>53 - [UV14] Dans quel document l’APS peut trouver les mesures opératoires des secours extérieurs lors d’un sinistre majeur ?|Le Plan des Opérations Externes (P.O.E.)|Le Plan Particulier d’Intervention (P.P.I. ou équivalent)|Le Plan de Secours Extérieurs (P.S.E.)|Le Plan Particulier des Risques Majeurs (P.P.R.M.)|Aucune des autres réponses|B</t>
+  </si>
+  <si>
+    <t>54 - [UV14] Quand doit-on rédiger notamment impérativement un Plan de Prévention ?|En cas de travaux dangereux listés dans l’arrêté du 19 mars 1993|Uniquement lorsque les consignes de sûreté le prévoient|Si vous estimez que l’importance des travaux le nécessitent|Uniquement sur demande explicite du client|Aucune des autres réponses|A</t>
+  </si>
+  <si>
+    <t>55 - [UV14] Quel est l’objectif général de la prévention ?|Définir les mesures de sûreté|Protéger l’employeur du risque pénal|Améliorer les statistiques concernant les taux d’accidents|Éviter ou limiter les dommages|Aucune des autres réponses|D</t>
+  </si>
+  <si>
+    <t>Radiologique</t>
+  </si>
+  <si>
+    <t>Radicalisé</t>
+  </si>
+  <si>
+    <t>Radioactif</t>
+  </si>
+  <si>
+    <t>Rayonnant</t>
+  </si>
+  <si>
+    <t>[UV7] Le Pneumothorax peut être occasionné par :</t>
+  </si>
+  <si>
+    <t>Une explosion (Blast primaire)</t>
+  </si>
+  <si>
+    <t>Une perforation par une côte</t>
+  </si>
+  <si>
+    <t>Une plaie pénétrante par arme blanche</t>
+  </si>
+  <si>
+    <t>Une plaie pénétrante par balle</t>
+  </si>
+  <si>
+    <t>[UV7] Parmi ces infractions, laquelle porte atteinte aux intérêts fondamentaux de la nation ?</t>
+  </si>
+  <si>
+    <t>La délation</t>
+  </si>
+  <si>
+    <t>L’abus de droit public</t>
+  </si>
+  <si>
+    <t>La rébellion</t>
+  </si>
+  <si>
+    <t>Le sabotage</t>
+  </si>
+  <si>
+    <t>La violation de domicile</t>
+  </si>
+  <si>
+    <t>[UV7] Dans le cadre d’un risque d’attentat, que peut faire le Préfet ?</t>
+  </si>
+  <si>
+    <t>Décréter l’état d’urgence, mais seulement au niveau “vigilance”</t>
+  </si>
+  <si>
+    <t>Faire procéder à des fouilles à corps par des ASP</t>
+  </si>
+  <si>
+    <t>Accroître les contrôles aux frontières</t>
+  </si>
+  <si>
+    <t>Interdire la circulation, instaurer un couvre-feu et limiter les allées/venues des personnes</t>
+  </si>
+  <si>
+    <t>[UV7] Témoin direct d’un attentat en cours sur votre site, quelles consignes à suivre sont les plus appropriées ?</t>
+  </si>
+  <si>
+    <t>Alerter les personnes autour de vous</t>
+  </si>
+  <si>
+    <t>Si possible, aider les autres personnes à s’échapper</t>
+  </si>
+  <si>
+    <t>Laisser vos affaires derrière vous</t>
+  </si>
+  <si>
+    <t>Si vous ne pouvez pas courir, se confiner, éteindre la lumière et couper le son des appareils à proximité</t>
+  </si>
+  <si>
+    <t>[UV11] Un groupe d’individus cagoulés et armés pénètre dans votre établissement et vous êtes seul : que faites-vous ?</t>
+  </si>
+  <si>
+    <t>J’appelle la relève pour me venir en aide le plus tôt possible</t>
+  </si>
+  <si>
+    <t>Je m’enfuis et je fais appel aux forces de l’ordre le plus rapidement possible</t>
+  </si>
+  <si>
+    <t>Je m’enfuis si je peux ou sinon je me confine, et je contacte le 114 par sms</t>
+  </si>
+  <si>
+    <t>Je dois agir physiquement pour les expulser de l’établissement</t>
+  </si>
+  <si>
+    <t>[UV9] Un agent de prévention et de sécurité a-t-il le droit de pratiquer des palpations de sécurité lors de manifestations sportives, récréatives ou culturelles ?</t>
+  </si>
+  <si>
+    <t>Oui, en toutes circonstances</t>
+  </si>
+  <si>
+    <t>Oui, s’il est habilité par son entreprise</t>
+  </si>
+  <si>
+    <t>Non, sauf s’il est habilité par son employeur</t>
+  </si>
+  <si>
+    <t>Oui, si la manifestation dépasse 300 personnes et sous le contrôle d’un OPJ et que la personne palpée soit du même sexe que l’agent de sécurité</t>
+  </si>
+  <si>
+    <t>[UV9] Je suis agent dans un établissement : sous quelles conditions ai-je le droit d’inspecter des sacs ?</t>
+  </si>
+  <si>
+    <t>Je peux faire une inspection visuelle même si ce n’est pas dans les consignes</t>
+  </si>
+  <si>
+    <t>Si c’est prévu dans les consignes, je peux fouiller les sacs sans avoir besoin du consentement du propriétaire</t>
+  </si>
+  <si>
+    <t>J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille</t>
+  </si>
+  <si>
+    <t>Je peux vérifier visuellement et fouiller tous les sacs</t>
+  </si>
+  <si>
+    <t>[UV11] En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?</t>
+  </si>
+  <si>
+    <t>D.A.S.</t>
+  </si>
+  <si>
+    <t>C.M.S.I.</t>
+  </si>
+  <si>
+    <t>S.M.S.I.</t>
+  </si>
+  <si>
+    <t>S.D.I.</t>
+  </si>
+  <si>
+    <t>[UV7] Que dois-je regarder pour détecter un potentiel terroriste ?</t>
+  </si>
+  <si>
+    <t>Son comportement</t>
+  </si>
+  <si>
+    <t>La pratique de sa religion</t>
+  </si>
+  <si>
+    <t>Ses antécédents judiciaires</t>
+  </si>
+  <si>
+    <t>Son apparence physique</t>
+  </si>
+  <si>
+    <t>[UV7] Qu’est-ce que la zone d’exclusion dans un périmètre de sécurité immédiat ?</t>
+  </si>
+  <si>
+    <t>La zone de prise en charge par les secours</t>
+  </si>
+  <si>
+    <t>La zone de danger et d’intervention</t>
+  </si>
+  <si>
+    <t>La zone de commandement des forces de l’ordre</t>
+  </si>
+  <si>
+    <t>La zone d’accueil des force de l’ordre et des secours</t>
+  </si>
+  <si>
+    <t>[UV2] Un revolver chambré pour le calibre 38 spécial est une arme de catégorie :</t>
+  </si>
+  <si>
+    <t>[UV2] Le vol avec arme est qualifié de :</t>
+  </si>
+  <si>
+    <t>Crime terroriste</t>
+  </si>
+  <si>
+    <t>Délit qualifié</t>
+  </si>
+  <si>
+    <t>Délit aggravé</t>
+  </si>
+  <si>
+    <t>Crime</t>
+  </si>
+  <si>
+    <t>[UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein de périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :</t>
+  </si>
+  <si>
+    <t>Avec le consentement de son conducteur, par un agent de prévention et de sécurité placé sous l’autorité d’un OPJ</t>
+  </si>
+  <si>
+    <t>[UV12] Le fait d’accéder frauduleusement à des données informatiques issues d’images de vidéosurveillance constitue l’infraction de :</t>
+  </si>
+  <si>
+    <t>Atteinte au système de traitement automatisé de données</t>
+  </si>
+  <si>
+    <t>Entrave à la libre circulation des données</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dégradation ou détérioration d’un système de traitement de données informatiques </t>
+  </si>
+  <si>
+    <t>[UV12] Que signifie l’acronyme P.I.F. dans le cadre d’un système de sécurité lors d’un événement ?</t>
+  </si>
+  <si>
+    <t>Point ou Poste d’Inspection Filtrage</t>
+  </si>
+  <si>
+    <t>Poste Itinérant de Filtrage</t>
+  </si>
+  <si>
+    <t>Passage Interdit à la Foule</t>
+  </si>
+  <si>
+    <t>Permis d’Inspection et de Fouille</t>
+  </si>
+  <si>
+    <t>[UV12] Le plan ORSEC est :</t>
+  </si>
+  <si>
+    <t>Un plan de limitation des déplacements dans le cadre du plan Vigipirates “Urgence Attentat”</t>
+  </si>
+  <si>
+    <t>Un plan d’Organisation de la Réponses de la Sécurité Civile</t>
+  </si>
+  <si>
+    <t>Un plan de circulation des riverains lors des événement culturels ou festifs</t>
+  </si>
+  <si>
+    <t>Un plan d’intervention coordonné des forces de l’ordre publiques et privées</t>
+  </si>
+  <si>
+    <t>[UV8] Suite à un vol dans un magasin, le chef de poste du PCS reçoit les forces de l’ordre et il peut déposer plainte :</t>
+  </si>
+  <si>
+    <t>Non, car c’est du ressort exclusif d’un responsable du magasin habilité</t>
+  </si>
+  <si>
+    <t>Oui, seulement en l’absence du responsable du magasin</t>
+  </si>
+  <si>
+    <t>Oui, car il est le chef de poste et il est donc habilité à déposer plainte</t>
+  </si>
+  <si>
+    <t>Oui, s’il a l’accord du responsable du magasin</t>
+  </si>
+  <si>
+    <t>[UV8] Une zone de protection périphérique concerne :</t>
+  </si>
+  <si>
+    <t>[UV8] Une zone de protection ponctuelle concerne :</t>
+  </si>
+  <si>
+    <t>[UV8] Les convoyeurs de fonds peuvent-ils être armés lorsqu’ils effectuent en véhicule banalisé un transport de fonds, bijoux ou métaux précieux ?</t>
+  </si>
+  <si>
+    <t>Oui, avec l’autorisation du Préfet</t>
+  </si>
+  <si>
+    <t>Non, ils ne peuvent pas être armés</t>
+  </si>
+  <si>
+    <t>Oui, si la valeur des biens est supérieure à 1,3 millions d’euros</t>
+  </si>
+  <si>
+    <t>Oui sur ordre de la société</t>
+  </si>
+  <si>
+    <t>[UV7] Que signifie NRBC-E ?</t>
+  </si>
+  <si>
+    <t>Nationaliste-Radiologique-Bactériologique-Cyberterrorisme et Explosive</t>
+  </si>
+  <si>
+    <t>Nucléaire-Radiologique-Biologique-Chimique et Explosive</t>
+  </si>
+  <si>
+    <t>Nucléaire-Radiotechnologique-Bactériologique-Catastrophique et Explosive</t>
+  </si>
+  <si>
+    <t>Nationaliste-Régionaliste-Bracage-Contrôle et Enlèvement</t>
+  </si>
+  <si>
+    <t>[UV7] En cas de plan Vigipirate, l’accès à n’importe quel établissement peut être soumis à une palpation de sécurité : qui peut en décider ?</t>
+  </si>
+  <si>
+    <t>Le Préfet par un arrêté spécifique</t>
+  </si>
+  <si>
+    <t>L’agent de sécurité si les consignes spéciales le prévoyants</t>
+  </si>
+  <si>
+    <t>Le chef d’établissement dans son règlement intérieur</t>
+  </si>
+  <si>
+    <t>Le CNAPS par une circulaire ministérielle</t>
+  </si>
+  <si>
+    <t>[UV7] Qu’est-ce que l’état d’urgence ?</t>
+  </si>
+  <si>
+    <t>Un régime exceptionnel qui permet à l’Etat français de gérer une crise</t>
+  </si>
+  <si>
+    <t>Un régime qui donne des pouvoirs supplémentaires aux agents de prévention et de sécurité</t>
+  </si>
+  <si>
+    <t>Un régime continu servant à instaurer un climat de sécurité au peuple</t>
+  </si>
+  <si>
+    <t>Un régime totalitaire qui octroie les pleins pouvoirs au Président de la République</t>
+  </si>
+  <si>
+    <t>[UV7] Suite à une blessure par balle sur le torse d’une victime, comment puis-je la secourir sans provoquer un pneumothorax ?</t>
+  </si>
+  <si>
+    <t>En posant dès que possible un garrot</t>
+  </si>
+  <si>
+    <t>En réalisant un pansement 3 côtés</t>
+  </si>
+  <si>
+    <t>En bouchant le trou formé par l’impact avec ma main</t>
+  </si>
+  <si>
+    <t>En mettant en place la réanimation cardio-pulmonaire</t>
+  </si>
+  <si>
+    <t>[UV7] Quelles sont les grandes priorités de réaction que je dois adopter face à une attaque terroriste ?</t>
+  </si>
+  <si>
+    <t>Courir, m'enfermer, appeler, attaquer si nécessaire</t>
+  </si>
+  <si>
+    <t>M’échapper, me cacher, secourir, combattre systématiquement</t>
+  </si>
+  <si>
+    <t>Alerter, éteindre, méloigner, boxer</t>
+  </si>
+  <si>
+    <t>[UV7] Qu’est-ce que le terrorisme d’Etat ?</t>
+  </si>
+  <si>
+    <t>Lorsqu’un peuple terrorise son gouvernement</t>
+  </si>
+  <si>
+    <t>Lorsqu’un Etat terrorise son peuple</t>
+  </si>
+  <si>
+    <t>Lorsqu’un Etat combat de le terrorisme à l’intérieur de ses frontières</t>
+  </si>
+  <si>
+    <t>Lorsqu’une organisation terroriste veut prendre le pouvoir d’un Etat</t>
+  </si>
+  <si>
+    <t>[UV2] Un agent de sécurité exerçant ses fonctions dans un parc d’attraction peut-il appréhender un individu qui y entre avec une matraque et tente d’agresser un salarié du parc ?</t>
+  </si>
+  <si>
+    <t>Il peut juste l’aborder mais il ne peut pas l’appréhender en vertu de l’art. 73 du CPP</t>
+  </si>
+  <si>
+    <t>Oui, car il sera dans le cadre de l’état de nécessité prévu dans l’art. 121-2 du Code Pénal</t>
+  </si>
+  <si>
+    <t>Non, car il n’y a pas d’infraction prévue pour ce type de fait</t>
+  </si>
+  <si>
+    <t>Le port d’une matraque constituant un délit, il peut appréhender l’individu au titre de l’art. 73 du CPP</t>
+  </si>
+  <si>
+    <t>[UV2] Un agent de sécurité privé peut être sanctionné par le CNAPS :</t>
+  </si>
+  <si>
+    <t>À une pénalité financière mais sans limite prise en charge par l’entreprise</t>
+  </si>
+  <si>
+    <t>À aucune pénalité financière</t>
+  </si>
+  <si>
+    <t>À une pénalité financière allant jusqu’à 10 000 euros</t>
+  </si>
+  <si>
+    <t>À une pénalité financière allant jusqu’à 7 500 euros</t>
+  </si>
+  <si>
+    <t>À une pénalité financière inférieure à 1 500 euros</t>
+  </si>
+  <si>
+    <t>[UV12] À quoi peut servir un PPI/POI/PER ?</t>
+  </si>
+  <si>
+    <t>À coordonner les moyens internes des installations classées</t>
+  </si>
+  <si>
+    <t>À prévoir la mobilisation des services de secours publics</t>
+  </si>
+  <si>
+    <t>À protéger les installations recevant du public</t>
+  </si>
+  <si>
+    <t>À planifier les opérations de maintien de l’ordre</t>
+  </si>
+  <si>
+    <t>[UV12] Il est puni par le code du sport (L332-3) dans une enceinte sportive, lors du déroulement ou de la retransmission en public d’une manifestation sportive :</t>
+  </si>
+  <si>
+    <t>Le fait d’introduire ou de tenter d’introduire, par force ou par fraude, des boissons alcoolisées</t>
+  </si>
+  <si>
+    <t>Le fait d’avoir, en état d’ivresse, pénétré ou tenté de pénétrer par force ou par fraude</t>
+  </si>
+  <si>
+    <t>D’un an d’emprisonnement ou d’amende</t>
+  </si>
+  <si>
+    <t>Le fait d’accéder en état d’ivresse</t>
+  </si>
+  <si>
+    <t>[UV12] Les organisateurs de manifestations sportives, récréatives ou culturelles sont tenus (R211-22 du CSI) :</t>
+  </si>
+  <si>
+    <t>D’en faire la déclaration au Préfet de région au moins un an avant l’événement</t>
+  </si>
+  <si>
+    <t>D’en faire la déclaration aux maires ou aux Préfets de police, si la manifestation peut atteindre plus de 1500 personnes</t>
+  </si>
+  <si>
+    <t>D’en faire la déclaration aux maires si la manifestation peut atteindre plus de 300 personnes et aux Préfets si elle dépasse plus de 1500 personnes</t>
+  </si>
+  <si>
+    <t>[UV9] Je suis agent dans un magasin : sous quelles conditions ai-je le droit d’inspecter des sacs ?</t>
+  </si>
+  <si>
+    <t>Je peux faire une inspection visuelle, dès lors que j’ai un doute</t>
+  </si>
+  <si>
+    <t>Je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaire</t>
+  </si>
+  <si>
+    <t>Si c’est prévu dans les consignes, je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaires</t>
+  </si>
+  <si>
+    <t>[UV8] Qu’est-ce qu’une zone de protection ?</t>
+  </si>
+  <si>
+    <t>Lieu protégé par des filets empêchant l’introduction de pigeons dans le site</t>
+  </si>
+  <si>
+    <t>Lieu protégé par des paroies possédant une isolation phonique</t>
+  </si>
+  <si>
+    <t>Lieu protégé contre les intempéries</t>
+  </si>
+  <si>
+    <t>Lieu protégé par un obstacle s’opposant à pénétration d’intrus dans le site</t>
+  </si>
+  <si>
+    <t>[UV8] Un point dit vulnérable lors d’une ronde est :</t>
+  </si>
+  <si>
+    <t>Un point régulièrement mis en défaut</t>
+  </si>
+  <si>
+    <t>Un point sensible convoité par les voleurs</t>
+  </si>
+  <si>
+    <t>[UV8] Pendant votre ronde, vous découvrez un local en désordre avec un pied de biche au sol. Que faites-vous ?</t>
+  </si>
+  <si>
+    <t>Vous ramassez le pied de biche afin d’avoir un objet pour vous défendre</t>
+  </si>
+  <si>
+    <t>Vous prévenez immédiatement le PCS et inspecter prudemment les locaux voisins</t>
+  </si>
+  <si>
+    <t>Vous ne faites rien et continuez votre rondre, c’est sûrement le bureau d’un salarié désordonné</t>
+  </si>
+  <si>
+    <t>Vous refermez la porte et prévenez le PCS</t>
+  </si>
+  <si>
+    <t>[UV6] Un agent de sécurité privé masculin doit appréhender un voleur en sortie de caisse, mais il s’agit d’une femme :</t>
+  </si>
+  <si>
+    <t>Il doit appeler une collègue du même sexe</t>
+  </si>
+  <si>
+    <t>Il agit normalement, néanmoins il est conseillé d’appeler un témoin féminin</t>
+  </si>
+  <si>
+    <t>Il doit demander l’autorisation de la personne</t>
+  </si>
+  <si>
+    <t>Il ne peut rien faire sur une personne de sexe opposé</t>
+  </si>
+  <si>
+    <t>[UV2] Les agents de sécurité employés par un bailleur d’immeuble à usage d’habitations peuvent être armés :</t>
+  </si>
+  <si>
+    <t>D’un fusil à pompe</t>
+  </si>
+  <si>
+    <t>D’une grenade lacrymogène ayant une capacité inférieure à 100 ml</t>
+  </si>
+  <si>
+    <t>D’un pistolet mitrailleur</t>
+  </si>
+  <si>
+    <t>[UV12] Le schéma d’installation de la vidéoprotection permet :</t>
+  </si>
+  <si>
+    <t>[UV12] À quoi correspond une crash barrière ?</t>
+  </si>
+  <si>
+    <t>Un système de barrière type passage à niveau pour bloquer les accès</t>
+  </si>
+  <si>
+    <t>Des barrières de sécurité équipés de pieds empêchant le renversement</t>
+  </si>
+  <si>
+    <t>Un test en laboratoire de la résistance des barrières</t>
+  </si>
+  <si>
+    <t>L’action de lancer des barrières sur des véhicules voulant forcer l’accès</t>
+  </si>
+  <si>
+    <t>[UV12] Un APS effectue une ronde dans la chaufferie gaz, il peut y entrer si :</t>
+  </si>
+  <si>
+    <t>Il dispose d’une radio fabriquée après le 1er juillet 2017</t>
+  </si>
+  <si>
+    <t>Il dispose d’un matériel anti-déflagrant</t>
+  </si>
+  <si>
+    <t>Il dispose d’un émetteur multi-fréquences</t>
+  </si>
+  <si>
+    <t>Il dispose d’une pastille de détection de gaz homologuée</t>
+  </si>
+  <si>
+    <t>[UV11] Sur votre GTB/GTC vous recevez une alarme SURCHAUFF au niveau de la chaufferie. Que devez-vous faire en premier ?</t>
+  </si>
+  <si>
+    <t>Arrêter le signal sonore de l’alarme</t>
+  </si>
+  <si>
+    <t>Appeler les services de secours</t>
+  </si>
+  <si>
+    <t>Couper la chaudière</t>
+  </si>
+  <si>
+    <t>Appeler le technicien compétent</t>
+  </si>
+  <si>
+    <t>[UV11] En vous rendant sur une levée de doute intrusion, votre PC vous appelle car une détection incendie vient d’avoir lieu. Que faites-vous ?</t>
+  </si>
+  <si>
+    <t>Je termine la levée de doute intrusion sans effectuer les contrôles de rigueur pour aller sur la levée de doute incendie</t>
+  </si>
+  <si>
+    <t>Je fais demi-tour et priorise la détection incendie dont la gravité peut être supérieure</t>
+  </si>
+  <si>
+    <t>Je poursuis la levée de doute intrusion, étant presque arrivé</t>
+  </si>
+  <si>
+    <t>Je demande au chef de poste d’effectuer lui-même la levée de doute incendie</t>
+  </si>
+  <si>
+    <t>[UV11] En cas d’alarme observée sur la centrale incendie, quelle est généralement la procédure à suivre ?</t>
+  </si>
+  <si>
+    <t>Appel de l’astreinte incendie, attente des secours, intervention éventuelle sur le feu</t>
+  </si>
+  <si>
+    <t>Acquittement du signal sonore, lecture de l’information, levée de doute, plan d’action conforme aux consignes du site</t>
+  </si>
+  <si>
+    <t>Levée de doute, appel des secours, retour au PCS</t>
+  </si>
+  <si>
+    <t>Intervention immédiate sur feu, appel des secours, réinitialisation central incendie</t>
+  </si>
+  <si>
+    <t>[UV9] Quelles sont les méthodes pour les agents masculins pour effectuer des vérifications de sécurité sur des femmes qui sont au contrôle d’accès :</t>
+  </si>
+  <si>
+    <t>Le contrôle visuel des bagages</t>
+  </si>
+  <si>
+    <t>[UV9] Dans quelle situation puis-je effectuer des palpations de sécurité ?</t>
+  </si>
+  <si>
+    <t>Dans tout le magasin sur des personnes soupçonnées de vouloir fumer</t>
+  </si>
+  <si>
+    <t>À l’intérieur d’une salle de concert à la demande du chef de poste</t>
+  </si>
+  <si>
+    <t>Dans tout lieu visé par un arrêté préfectoral</t>
+  </si>
+  <si>
+    <t>À la sortie du magasin sur un individu connu pour des actes de vol</t>
+  </si>
+  <si>
+    <t>[UV8] Certaines circonstances peuvent aggraver le vol. Par exemple quand le vol est commis :</t>
+  </si>
+  <si>
+    <t>Par plusieurs personnes</t>
+  </si>
+  <si>
+    <t>Chez une personne dépositaire de l’autorité publique</t>
+  </si>
+  <si>
+    <t>Sur une personne dans la journée</t>
+  </si>
+  <si>
+    <t>Dans un local sous surveillance électronique</t>
+  </si>
+  <si>
+    <t>[UV7] Dès l’arrivée des forces de l’ordre, dans une zone d’attentat, vous devez en premier :</t>
+  </si>
+  <si>
+    <t>Leur parler de la situation</t>
+  </si>
+  <si>
+    <t>Courir vers eux</t>
+  </si>
+  <si>
+    <t>Leur indiquer l’emplacement des victimes</t>
+  </si>
+  <si>
+    <t>Suivre leurs instructions</t>
+  </si>
+  <si>
+    <t>[UV7] Parmi les types de “BLAST” suivants, lequel ou lesquels existent ?</t>
+  </si>
+  <si>
+    <t>BLAST primaire</t>
+  </si>
+  <si>
+    <t>BLAST tertiaire</t>
+  </si>
+  <si>
+    <t>BLAST quaternaire</t>
+  </si>
+  <si>
+    <t>BLAST secondaire</t>
+  </si>
+  <si>
+    <t>[UV2] Agent de sécurité, je dispose d’un véhicule d’entreprise équipé d’un gyrophare orange :</t>
+  </si>
+  <si>
+    <t>C’est absolument interdit</t>
+  </si>
+  <si>
+    <t>C’est autorisé uniquement à l’intérieur des sites surveillés, si les consignes le prévoient</t>
+  </si>
+  <si>
+    <t>Seuls les gyrophares bleus sont autorisés pour les agents de sécurité</t>
+  </si>
+  <si>
+    <t>C’est interdit, sauf en situation d’urgence attentat</t>
+  </si>
+  <si>
+    <t>[UV2] Selon la loi, est une arme par destination :</t>
+  </si>
+  <si>
+    <t>Tout objet conçu pour usage professionnel</t>
+  </si>
+  <si>
+    <t>Tout objet conçu pour tuer ou blesser</t>
+  </si>
+  <si>
+    <t>Tout objet susceptible de présenter un danger pour des personnes, dès lors qu’il est utilisé pour menacer</t>
+  </si>
+  <si>
+    <t>Tout objet pouvant causer des dommages</t>
+  </si>
+  <si>
+    <t>[UV11] Le report d’alarme d’une centrale intrusion est un dispositif :</t>
+  </si>
+  <si>
+    <t>Uniquement destiné aux équipes de sûreté en cas d’intrusion</t>
+  </si>
+  <si>
+    <t>De secours en cas de défaillance du clavier principal</t>
+  </si>
+  <si>
+    <t>Qui permet aux agents d’accéder à certaines informations hors du PCS</t>
+  </si>
+  <si>
+    <t>De cloisonnement anti-intrusion indépendant du système central</t>
+  </si>
+  <si>
+    <t>[UV14] Dans quel document l’APS peut trouver les mesures opératoires des secours extérieurs lors d’un sinistre majeur ?</t>
+  </si>
+  <si>
+    <t>Le Plan des Opérations Externes (P.O.E.)</t>
+  </si>
+  <si>
+    <t>Le Plan Particulier d’Intervention (P.P.I. ou équivalent)</t>
+  </si>
+  <si>
+    <t>Le Plan de Secours Extérieurs (P.S.E.)</t>
+  </si>
+  <si>
+    <t>Le Plan Particulier des Risques Majeurs (P.P.R.M.)</t>
+  </si>
+  <si>
+    <t>[UV14] Quand doit-on rédiger notamment impérativement un Plan de Prévention ?</t>
+  </si>
+  <si>
+    <t>En cas de travaux dangereux listés dans l’arrêté du 19 mars 1993</t>
+  </si>
+  <si>
+    <t>Uniquement lorsque les consignes de sûreté le prévoient</t>
+  </si>
+  <si>
+    <t>Si vous estimez que l’importance des travaux le nécessitent</t>
+  </si>
+  <si>
+    <t>Uniquement sur demande explicite du client</t>
+  </si>
+  <si>
+    <t>[UV14] Quel est l’objectif général de la prévention ?</t>
+  </si>
+  <si>
+    <t>Définir les mesures de sûreté</t>
+  </si>
+  <si>
+    <t>Protéger l’employeur du risque pénal</t>
+  </si>
+  <si>
+    <t>Améliorer les statistiques concernant les taux d’accidents</t>
+  </si>
+  <si>
+    <t>Éviter ou limiter les dommages</t>
+  </si>
+  <si>
+    <t>VRAC 1</t>
+  </si>
+  <si>
+    <t>VRAC 2</t>
+  </si>
+  <si>
+    <t>VRAC 3</t>
+  </si>
+  <si>
+    <t>Questions vrac</t>
+  </si>
+  <si>
+    <t>[UV7] Que signifie le R de NRBC-E ?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5548,6 +6523,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -5603,7 +6591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5648,6 +6636,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6491,10 +7483,10 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" style="9" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="9"/>
     <col min="3" max="3" width="59.28515625" style="2" customWidth="1"/>
     <col min="4" max="9" width="26.7109375" style="2" customWidth="1"/>
@@ -12475,6 +13467,1598 @@
       </c>
       <c r="J205" s="10" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J206" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="J207" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="J208" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J209" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J210" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J211" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="J212" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="J213" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J214" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="J215" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J216" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J217" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J218" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J219" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="J220" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="J221" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="J222" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="J223" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J224" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="J225" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="J226" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J227" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J228" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J229" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J230" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J231" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A232" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J232" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J233" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J234" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J235" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A236" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="J236" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A237" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J237" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A238" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J238" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="J239" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J240" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J241" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="J242" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="J243" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="J244" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="9" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H245" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J245" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J246" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H247" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J247" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B248" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="J248" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H249" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J249" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H250" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="J250" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H251" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J251" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A252" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H252" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J252" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H253" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J253" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="H254" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J254" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H255" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="J255" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H256" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="J256" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A257" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H257" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J257" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A258" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J258" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A259" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H259" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J259" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A260" s="9" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B260" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J260" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12658,18 +15242,42 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13639,13 +16247,14 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18582157-25E0-434E-AB6B-01FE38A60B37}">
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
@@ -18008,7 +20617,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>1011</v>
       </c>
@@ -18040,7 +20649,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>1012</v>
       </c>
@@ -18063,7 +20672,7 @@
         <v>Non</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>1013</v>
       </c>
@@ -18092,7 +20701,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>1014</v>
       </c>
@@ -18124,7 +20733,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>1015</v>
       </c>
@@ -18156,7 +20765,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>1016</v>
       </c>
@@ -18188,7 +20797,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>1017</v>
       </c>
@@ -18220,7 +20829,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>1018</v>
       </c>
@@ -18252,7 +20861,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>1019</v>
       </c>
@@ -18284,7 +20893,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>1020</v>
       </c>
@@ -18316,7 +20925,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>1021</v>
       </c>
@@ -18348,7 +20957,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>1022</v>
       </c>
@@ -18377,7 +20986,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>1023</v>
       </c>
@@ -18409,7 +21018,7 @@
         <v>Aucune des réponses précédentes</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>1024</v>
       </c>
@@ -18439,6 +21048,1928 @@
       </c>
       <c r="I158" t="str">
         <v>Aucune des réponses précédentes</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="18" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B160" s="17">
+        <f t="shared" ref="B160" si="20">FIND(" - ",A160)</f>
+        <v>2</v>
+      </c>
+      <c r="C160" s="17" t="str">
+        <f t="shared" ref="C160" si="21">RIGHT(A160, LEN(A160)-(B160+2))</f>
+        <v>[UV7] Que signifie le R de N.R.B.C-E ?|Radiologique|Radicalisé|Radioactif|Aucune des autres réponses|Rayonnant|A</v>
+      </c>
+      <c r="D160" t="str" cm="1">
+        <f t="array" ref="D160:J160">_xlfn.TEXTSPLIT(C160,"|")</f>
+        <v>[UV7] Que signifie le R de N.R.B.C-E ?</v>
+      </c>
+      <c r="E160" t="str">
+        <v>Radiologique</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Radicalisé</v>
+      </c>
+      <c r="G160" t="str">
+        <v>Radioactif</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Rayonnant</v>
+      </c>
+      <c r="J160" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="18" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B161" s="17">
+        <f t="shared" ref="B161:B214" si="22">FIND(" - ",A161)</f>
+        <v>2</v>
+      </c>
+      <c r="C161" s="17" t="str">
+        <f t="shared" ref="C161:C214" si="23">RIGHT(A161, LEN(A161)-(B161+2))</f>
+        <v>[UV7] Le Pneumothorax peut être occasionné par :|Toutes les réponses sont bonnes|Une explosion (Blast primaire)|Une perforation par une côte|Une plaie pénétrante par arme blanche|Une plaie pénétrante par balle|A</v>
+      </c>
+      <c r="D161" t="str" cm="1">
+        <f t="array" ref="D161:J161">_xlfn.TEXTSPLIT(C161,"|")</f>
+        <v>[UV7] Le Pneumothorax peut être occasionné par :</v>
+      </c>
+      <c r="E161" t="str">
+        <v>Toutes les réponses sont bonnes</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Une explosion (Blast primaire)</v>
+      </c>
+      <c r="G161" t="str">
+        <v>Une perforation par une côte</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Une plaie pénétrante par arme blanche</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Une plaie pénétrante par balle</v>
+      </c>
+      <c r="J161" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="18" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B162" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C162" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Parmi ces infractions, laquelle porte atteinte aux intérêts fondamentaux de la nation ?|La délation|L’abus de droit public|La rébellion|Le sabotage|La violation de domicile|D</v>
+      </c>
+      <c r="D162" t="str" cm="1">
+        <f t="array" ref="D162:J162">_xlfn.TEXTSPLIT(C162,"|")</f>
+        <v>[UV7] Parmi ces infractions, laquelle porte atteinte aux intérêts fondamentaux de la nation ?</v>
+      </c>
+      <c r="E162" t="str">
+        <v>La délation</v>
+      </c>
+      <c r="F162" t="str">
+        <v>L’abus de droit public</v>
+      </c>
+      <c r="G162" t="str">
+        <v>La rébellion</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Le sabotage</v>
+      </c>
+      <c r="I162" t="str">
+        <v>La violation de domicile</v>
+      </c>
+      <c r="J162" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="18" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B163" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C163" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Dans le cadre d’un risque d’attentat, que peut faire le Préfet ?|Décréter l’état d’urgence, mais seulement au niveau “vigilance”|Faire procéder à des fouilles à corps par des ASP|Accroître les contrôles aux frontières|Aucune des autres réponses|Interdire la circulation, instaurer un couvre-feu et limiter les allées/venues des personnes|E</v>
+      </c>
+      <c r="D163" t="str" cm="1">
+        <f t="array" ref="D163:J163">_xlfn.TEXTSPLIT(C163,"|")</f>
+        <v>[UV7] Dans le cadre d’un risque d’attentat, que peut faire le Préfet ?</v>
+      </c>
+      <c r="E163" t="str">
+        <v>Décréter l’état d’urgence, mais seulement au niveau “vigilance”</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Faire procéder à des fouilles à corps par des ASP</v>
+      </c>
+      <c r="G163" t="str">
+        <v>Accroître les contrôles aux frontières</v>
+      </c>
+      <c r="H163" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Interdire la circulation, instaurer un couvre-feu et limiter les allées/venues des personnes</v>
+      </c>
+      <c r="J163" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="18" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B164" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C164" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Témoin direct d’un attentat en cours sur votre site, quelles consignes à suivre sont les plus appropriées ?|Alerter les personnes autour de vous|Si possible, aider les autres personnes à s’échapper|Laisser vos affaires derrière vous|Si vous ne pouvez pas courir, se confiner, éteindre la lumière et couper le son des appareils à proximité|Toutes les réponses précédentes sont exactes|E</v>
+      </c>
+      <c r="D164" t="str" cm="1">
+        <f t="array" ref="D164:J164">_xlfn.TEXTSPLIT(C164,"|")</f>
+        <v>[UV7] Témoin direct d’un attentat en cours sur votre site, quelles consignes à suivre sont les plus appropriées ?</v>
+      </c>
+      <c r="E164" t="str">
+        <v>Alerter les personnes autour de vous</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Si possible, aider les autres personnes à s’échapper</v>
+      </c>
+      <c r="G164" t="str">
+        <v>Laisser vos affaires derrière vous</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Si vous ne pouvez pas courir, se confiner, éteindre la lumière et couper le son des appareils à proximité</v>
+      </c>
+      <c r="I164" t="str">
+        <v>Toutes les réponses précédentes sont exactes</v>
+      </c>
+      <c r="J164" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="18" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B165" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C165" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] Un groupe d’individus cagoulés et armés pénètre dans votre établissement et vous êtes seul : que faites-vous ?|J’appelle la relève pour me venir en aide le plus tôt possible|Je m’enfuis et je fais appel aux forces de l’ordre le plus rapidement possible|Je m’enfuis si je peux ou sinon je me confine, et je contacte le 114 par sms|Aucune des autres réponses|Je dois agir physiquement pour les expulser de l’établissement|C</v>
+      </c>
+      <c r="D165" t="str" cm="1">
+        <f t="array" ref="D165:J165">_xlfn.TEXTSPLIT(C165,"|")</f>
+        <v>[UV11] Un groupe d’individus cagoulés et armés pénètre dans votre établissement et vous êtes seul : que faites-vous ?</v>
+      </c>
+      <c r="E165" t="str">
+        <v>J’appelle la relève pour me venir en aide le plus tôt possible</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Je m’enfuis et je fais appel aux forces de l’ordre le plus rapidement possible</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Je m’enfuis si je peux ou sinon je me confine, et je contacte le 114 par sms</v>
+      </c>
+      <c r="H165" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Je dois agir physiquement pour les expulser de l’établissement</v>
+      </c>
+      <c r="J165" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="18" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B166" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C166" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV9] Un agent de prévention et de sécurité a-t-il le droit de pratiquer des palpations de sécurité lors de manifestations sportives, récréatives ou culturelles ?|Oui, en toutes circonstances|Oui, s’il est habilité par son entreprise|Non, sauf s’il est habilité par son employeur|Aucune des autres réponses|Oui, si la manifestation dépasse 300 personnes et sous le contrôle d’un OPJ et que la personne palpée soit du même sexe que l’agent de sécurité|E</v>
+      </c>
+      <c r="D166" t="str" cm="1">
+        <f t="array" ref="D166:J166">_xlfn.TEXTSPLIT(C166,"|")</f>
+        <v>[UV9] Un agent de prévention et de sécurité a-t-il le droit de pratiquer des palpations de sécurité lors de manifestations sportives, récréatives ou culturelles ?</v>
+      </c>
+      <c r="E166" t="str">
+        <v>Oui, en toutes circonstances</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Oui, s’il est habilité par son entreprise</v>
+      </c>
+      <c r="G166" t="str">
+        <v>Non, sauf s’il est habilité par son employeur</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Oui, si la manifestation dépasse 300 personnes et sous le contrôle d’un OPJ et que la personne palpée soit du même sexe que l’agent de sécurité</v>
+      </c>
+      <c r="J166" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="18" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B167" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C167" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV9] Je suis agent dans un établissement : sous quelles conditions ai-je le droit d’inspecter des sacs ?|Je peux faire une inspection visuelle même si ce n’est pas dans les consignes|Aucune des autres réponses|Si c’est prévu dans les consignes, je peux fouiller les sacs sans avoir besoin du consentement du propriétaire|J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille|Je peux vérifier visuellement et fouiller tous les sacs|D</v>
+      </c>
+      <c r="D167" t="str" cm="1">
+        <f t="array" ref="D167:J167">_xlfn.TEXTSPLIT(C167,"|")</f>
+        <v>[UV9] Je suis agent dans un établissement : sous quelles conditions ai-je le droit d’inspecter des sacs ?</v>
+      </c>
+      <c r="E167" t="str">
+        <v>Je peux faire une inspection visuelle même si ce n’est pas dans les consignes</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="G167" t="str">
+        <v>Si c’est prévu dans les consignes, je peux fouiller les sacs sans avoir besoin du consentement du propriétaire</v>
+      </c>
+      <c r="H167" t="str">
+        <v>J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Je peux vérifier visuellement et fouiller tous les sacs</v>
+      </c>
+      <c r="J167" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="18" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B168" s="17">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="C168" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?|D.A.S.|C.M.S.I.|S.M.S.I.|S.D.I.|Aucune des réponses précédentes|D</v>
+      </c>
+      <c r="D168" t="str" cm="1">
+        <f t="array" ref="D168:J168">_xlfn.TEXTSPLIT(C168,"|")</f>
+        <v>[UV11] En cas de détection incendie, sur quelle unité le voyant est-il lumineux ?</v>
+      </c>
+      <c r="E168" t="str">
+        <v>D.A.S.</v>
+      </c>
+      <c r="F168" t="str">
+        <v>C.M.S.I.</v>
+      </c>
+      <c r="G168" t="str">
+        <v>S.M.S.I.</v>
+      </c>
+      <c r="H168" t="str">
+        <v>S.D.I.</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Aucune des réponses précédentes</v>
+      </c>
+      <c r="J168" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B169" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C169" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Que dois-je regarder pour détecter un potentiel terroriste ?|Son comportement|La pratique de sa religion|Aucune des autres réponses|Ses antécédents judiciaires|Son apparence physique|A</v>
+      </c>
+      <c r="D169" t="str" cm="1">
+        <f t="array" ref="D169:J169">_xlfn.TEXTSPLIT(C169,"|")</f>
+        <v>[UV7] Que dois-je regarder pour détecter un potentiel terroriste ?</v>
+      </c>
+      <c r="E169" t="str">
+        <v>Son comportement</v>
+      </c>
+      <c r="F169" t="str">
+        <v>La pratique de sa religion</v>
+      </c>
+      <c r="G169" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Ses antécédents judiciaires</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Son apparence physique</v>
+      </c>
+      <c r="J169" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B170" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C170" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Qu’est-ce que la zone d’exclusion dans un périmètre de sécurité immédiat ?|La zone de prise en charge par les secours|La zone de danger et d’intervention|La zone de commandement des forces de l’ordre|Aucune des autres réponses|La zone d’accueil des force de l’ordre et des secours|B</v>
+      </c>
+      <c r="D170" t="str" cm="1">
+        <f t="array" ref="D170:J170">_xlfn.TEXTSPLIT(C170,"|")</f>
+        <v>[UV7] Qu’est-ce que la zone d’exclusion dans un périmètre de sécurité immédiat ?</v>
+      </c>
+      <c r="E170" t="str">
+        <v>La zone de prise en charge par les secours</v>
+      </c>
+      <c r="F170" t="str">
+        <v>La zone de danger et d’intervention</v>
+      </c>
+      <c r="G170" t="str">
+        <v>La zone de commandement des forces de l’ordre</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I170" t="str">
+        <v>La zone d’accueil des force de l’ordre et des secours</v>
+      </c>
+      <c r="J170" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="18" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B171" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C171" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Un revolver chambré pour le calibre 38 spécial est une arme de catégorie :|C|D|A|Aucune des autres réponses|B|B</v>
+      </c>
+      <c r="D171" t="str" cm="1">
+        <f t="array" ref="D171:J171">_xlfn.TEXTSPLIT(C171,"|")</f>
+        <v>[UV2] Un revolver chambré pour le calibre 38 spécial est une arme de catégorie :</v>
+      </c>
+      <c r="E171" t="str">
+        <v>C</v>
+      </c>
+      <c r="F171" t="str">
+        <v>D</v>
+      </c>
+      <c r="G171" t="str">
+        <v>A</v>
+      </c>
+      <c r="H171" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I171" t="str">
+        <v>B</v>
+      </c>
+      <c r="J171" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="18" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B172" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C172" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Le vol avec arme est qualifié de :|Crime terroriste|Aucune des autres réponses|Délit qualifié|Délit aggravé|Crime|E</v>
+      </c>
+      <c r="D172" t="str" cm="1">
+        <f t="array" ref="D172:J172">_xlfn.TEXTSPLIT(C172,"|")</f>
+        <v>[UV2] Le vol avec arme est qualifié de :</v>
+      </c>
+      <c r="E172" t="str">
+        <v>Crime terroriste</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="G172" t="str">
+        <v>Délit qualifié</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Délit aggravé</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Crime</v>
+      </c>
+      <c r="J172" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B173" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C173" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein de périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :|Sans le consentement de son conducteur, par un agent de prévention et de sécurité|Sans le consentement de son conducteur, par un agent de prévention et de sécurité mais sous le contrôle d’un OPJ|Avec le consentement de son conducteur, par un agent de prévention et de sécurité|Avec le consentement de son conducteur, par un agent de prévention et de sécurité placé sous l’autorité d’un OPJ|Aucune des autres réponses|E</v>
+      </c>
+      <c r="D173" t="str" cm="1">
+        <f t="array" ref="D173:J173">_xlfn.TEXTSPLIT(C173,"|")</f>
+        <v>[UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein de périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :</v>
+      </c>
+      <c r="E173" t="str">
+        <v>Sans le consentement de son conducteur, par un agent de prévention et de sécurité</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Sans le consentement de son conducteur, par un agent de prévention et de sécurité mais sous le contrôle d’un OPJ</v>
+      </c>
+      <c r="G173" t="str">
+        <v>Avec le consentement de son conducteur, par un agent de prévention et de sécurité</v>
+      </c>
+      <c r="H173" t="str">
+        <v>Avec le consentement de son conducteur, par un agent de prévention et de sécurité placé sous l’autorité d’un OPJ</v>
+      </c>
+      <c r="I173" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J173" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="18" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B174" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C174" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Le fait d’accéder frauduleusement à des données informatiques issues d’images de vidéosurveillance constitue l’infraction de :|Atteinte au système de traitement automatisé de données|Entrave à la libre circulation des données|Dégradation ou détérioration d’un système de traitement de données informatiques |Aucune des autres réponses|Vol de données informatiques|A</v>
+      </c>
+      <c r="D174" t="str" cm="1">
+        <f t="array" ref="D174:J174">_xlfn.TEXTSPLIT(C174,"|")</f>
+        <v>[UV12] Le fait d’accéder frauduleusement à des données informatiques issues d’images de vidéosurveillance constitue l’infraction de :</v>
+      </c>
+      <c r="E174" t="str">
+        <v>Atteinte au système de traitement automatisé de données</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Entrave à la libre circulation des données</v>
+      </c>
+      <c r="G174" t="str">
+        <v xml:space="preserve">Dégradation ou détérioration d’un système de traitement de données informatiques </v>
+      </c>
+      <c r="H174" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I174" t="str">
+        <v>Vol de données informatiques</v>
+      </c>
+      <c r="J174" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B175" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C175" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Que signifie l’acronyme P.I.F. dans le cadre d’un système de sécurité lors d’un événement ?|Point ou Poste d’Inspection Filtrage|Poste Itinérant de Filtrage|Passage Interdit à la Foule|Aucune des autres réponses|Permis d’Inspection et de Fouille|A</v>
+      </c>
+      <c r="D175" t="str" cm="1">
+        <f t="array" ref="D175:J175">_xlfn.TEXTSPLIT(C175,"|")</f>
+        <v>[UV12] Que signifie l’acronyme P.I.F. dans le cadre d’un système de sécurité lors d’un événement ?</v>
+      </c>
+      <c r="E175" t="str">
+        <v>Point ou Poste d’Inspection Filtrage</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Poste Itinérant de Filtrage</v>
+      </c>
+      <c r="G175" t="str">
+        <v>Passage Interdit à la Foule</v>
+      </c>
+      <c r="H175" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I175" t="str">
+        <v>Permis d’Inspection et de Fouille</v>
+      </c>
+      <c r="J175" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="18" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B176" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C176" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Le plan ORSEC est :|Aucune des autres réponses|Un plan de limitation des déplacements dans le cadre du plan Vigipirates “Urgence Attentat”|Un plan d’Organisation de la Réponses de la Sécurité Civile|Un plan de circulation des riverains lors des événement culturels ou festifs|Un plan d’intervention coordonné des forces de l’ordre publiques et privées|C</v>
+      </c>
+      <c r="D176" t="str" cm="1">
+        <f t="array" ref="D176:J176">_xlfn.TEXTSPLIT(C176,"|")</f>
+        <v>[UV12] Le plan ORSEC est :</v>
+      </c>
+      <c r="E176" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Un plan de limitation des déplacements dans le cadre du plan Vigipirates “Urgence Attentat”</v>
+      </c>
+      <c r="G176" t="str">
+        <v>Un plan d’Organisation de la Réponses de la Sécurité Civile</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Un plan de circulation des riverains lors des événement culturels ou festifs</v>
+      </c>
+      <c r="I176" t="str">
+        <v>Un plan d’intervention coordonné des forces de l’ordre publiques et privées</v>
+      </c>
+      <c r="J176" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B177" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C177" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Suite à un vol dans un magasin, le chef de poste du PCS reçoit les forces de l’ordre et il peut déposer plainte :|Non, car c’est du ressort exclusif d’un responsable du magasin habilité|Oui, seulement en l’absence du responsable du magasin|Aucune des autres réponses|Oui, car il est le chef de poste et il est donc habilité à déposer plainte|Oui, s’il a l’accord du responsable du magasin|A</v>
+      </c>
+      <c r="D177" t="str" cm="1">
+        <f t="array" ref="D177:J177">_xlfn.TEXTSPLIT(C177,"|")</f>
+        <v>[UV8] Suite à un vol dans un magasin, le chef de poste du PCS reçoit les forces de l’ordre et il peut déposer plainte :</v>
+      </c>
+      <c r="E177" t="str">
+        <v>Non, car c’est du ressort exclusif d’un responsable du magasin habilité</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Oui, seulement en l’absence du responsable du magasin</v>
+      </c>
+      <c r="G177" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H177" t="str">
+        <v>Oui, car il est le chef de poste et il est donc habilité à déposer plainte</v>
+      </c>
+      <c r="I177" t="str">
+        <v>Oui, s’il a l’accord du responsable du magasin</v>
+      </c>
+      <c r="J177" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="18" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B178" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C178" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Une zone de protection périphérique concerne :|Un objet précis|Aucune des autres réponses|Un local|Une vitrine|Une clôture|E</v>
+      </c>
+      <c r="D178" t="str" cm="1">
+        <f t="array" ref="D178:J178">_xlfn.TEXTSPLIT(C178,"|")</f>
+        <v>[UV8] Une zone de protection périphérique concerne :</v>
+      </c>
+      <c r="E178" t="str">
+        <v>Un objet précis</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="G178" t="str">
+        <v>Un local</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Une vitrine</v>
+      </c>
+      <c r="I178" t="str">
+        <v>Une clôture</v>
+      </c>
+      <c r="J178" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="18" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B179" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C179" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Une zone de protection ponctuelle concerne :|Un local|Aucune des autres réponses|Une vitrine|Une clôture|Un objet précis|E</v>
+      </c>
+      <c r="D179" t="str" cm="1">
+        <f t="array" ref="D179:J179">_xlfn.TEXTSPLIT(C179,"|")</f>
+        <v>[UV8] Une zone de protection ponctuelle concerne :</v>
+      </c>
+      <c r="E179" t="str">
+        <v>Un local</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="G179" t="str">
+        <v>Une vitrine</v>
+      </c>
+      <c r="H179" t="str">
+        <v>Une clôture</v>
+      </c>
+      <c r="I179" t="str">
+        <v>Un objet précis</v>
+      </c>
+      <c r="J179" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="18" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B180" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C180" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Les convoyeurs de fonds peuvent-ils être armés lorsqu’ils effectuent en véhicule banalisé un transport de fonds, bijoux ou métaux précieux ?|Oui, avec l’autorisation du Préfet|Non, ils ne peuvent pas être armés|Oui, si la valeur des biens est supérieure à 1,3 millions d’euros|Aucune des autres réponses|Oui sur ordre de la société|B</v>
+      </c>
+      <c r="D180" t="str" cm="1">
+        <f t="array" ref="D180:J180">_xlfn.TEXTSPLIT(C180,"|")</f>
+        <v>[UV8] Les convoyeurs de fonds peuvent-ils être armés lorsqu’ils effectuent en véhicule banalisé un transport de fonds, bijoux ou métaux précieux ?</v>
+      </c>
+      <c r="E180" t="str">
+        <v>Oui, avec l’autorisation du Préfet</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Non, ils ne peuvent pas être armés</v>
+      </c>
+      <c r="G180" t="str">
+        <v>Oui, si la valeur des biens est supérieure à 1,3 millions d’euros</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I180" t="str">
+        <v>Oui sur ordre de la société</v>
+      </c>
+      <c r="J180" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="18" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B181" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C181" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Que signifie NRBC-E ?|Nationaliste-Radiologique-Bactériologique-Cyberterrorisme et Explosive|Nucléaire-Radiologique-Biologique-Chimique et Explosive|Nucléaire-Radiotechnologique-Bactériologique-Catastrophique et Explosive|Nationaliste-Régionaliste-Bracage-Contrôle et Enlèvement|Aucune des autres réponses|B</v>
+      </c>
+      <c r="D181" t="str" cm="1">
+        <f t="array" ref="D181:J181">_xlfn.TEXTSPLIT(C181,"|")</f>
+        <v>[UV7] Que signifie NRBC-E ?</v>
+      </c>
+      <c r="E181" t="str">
+        <v>Nationaliste-Radiologique-Bactériologique-Cyberterrorisme et Explosive</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Nucléaire-Radiologique-Biologique-Chimique et Explosive</v>
+      </c>
+      <c r="G181" t="str">
+        <v>Nucléaire-Radiotechnologique-Bactériologique-Catastrophique et Explosive</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Nationaliste-Régionaliste-Bracage-Contrôle et Enlèvement</v>
+      </c>
+      <c r="I181" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J181" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="18" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B182" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C182" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] En cas de plan Vigipirate, l’accès à n’importe quel établissement peut être soumis à une palpation de sécurité : qui peut en décider ?|Le Préfet par un arrêté spécifique|L’agent de sécurité si les consignes spéciales le prévoyants|Le chef d’établissement dans son règlement intérieur|Le CNAPS par une circulaire ministérielle|Aucune des autres réponses|A</v>
+      </c>
+      <c r="D182" t="str" cm="1">
+        <f t="array" ref="D182:J182">_xlfn.TEXTSPLIT(C182,"|")</f>
+        <v>[UV7] En cas de plan Vigipirate, l’accès à n’importe quel établissement peut être soumis à une palpation de sécurité : qui peut en décider ?</v>
+      </c>
+      <c r="E182" t="str">
+        <v>Le Préfet par un arrêté spécifique</v>
+      </c>
+      <c r="F182" t="str">
+        <v>L’agent de sécurité si les consignes spéciales le prévoyants</v>
+      </c>
+      <c r="G182" t="str">
+        <v>Le chef d’établissement dans son règlement intérieur</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Le CNAPS par une circulaire ministérielle</v>
+      </c>
+      <c r="I182" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J182" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="18" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B183" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C183" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Qu’est-ce que l’état d’urgence ?|Un régime exceptionnel qui permet à l’Etat français de gérer une crise|Un régime qui donne des pouvoirs supplémentaires aux agents de prévention et de sécurité|Un régime continu servant à instaurer un climat de sécurité au peuple|Un régime totalitaire qui octroie les pleins pouvoirs au Président de la République|Aucune des autres réponses|A</v>
+      </c>
+      <c r="D183" t="str" cm="1">
+        <f t="array" ref="D183:J183">_xlfn.TEXTSPLIT(C183,"|")</f>
+        <v>[UV7] Qu’est-ce que l’état d’urgence ?</v>
+      </c>
+      <c r="E183" t="str">
+        <v>Un régime exceptionnel qui permet à l’Etat français de gérer une crise</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Un régime qui donne des pouvoirs supplémentaires aux agents de prévention et de sécurité</v>
+      </c>
+      <c r="G183" t="str">
+        <v>Un régime continu servant à instaurer un climat de sécurité au peuple</v>
+      </c>
+      <c r="H183" t="str">
+        <v>Un régime totalitaire qui octroie les pleins pouvoirs au Président de la République</v>
+      </c>
+      <c r="I183" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J183" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="18" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B184" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C184" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Suite à une blessure par balle sur le torse d’une victime, comment puis-je la secourir sans provoquer un pneumothorax ?|Aucune des autres réponses|En posant dès que possible un garrot|En réalisant un pansement 3 côtés|En bouchant le trou formé par l’impact avec ma main|En mettant en place la réanimation cardio-pulmonaire|C</v>
+      </c>
+      <c r="D184" t="str" cm="1">
+        <f t="array" ref="D184:J184">_xlfn.TEXTSPLIT(C184,"|")</f>
+        <v>[UV7] Suite à une blessure par balle sur le torse d’une victime, comment puis-je la secourir sans provoquer un pneumothorax ?</v>
+      </c>
+      <c r="E184" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F184" t="str">
+        <v>En posant dès que possible un garrot</v>
+      </c>
+      <c r="G184" t="str">
+        <v>En réalisant un pansement 3 côtés</v>
+      </c>
+      <c r="H184" t="str">
+        <v>En bouchant le trou formé par l’impact avec ma main</v>
+      </c>
+      <c r="I184" t="str">
+        <v>En mettant en place la réanimation cardio-pulmonaire</v>
+      </c>
+      <c r="J184" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="18" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B185" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C185" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Quelles sont les grandes priorités de réaction que je dois adopter face à une attaque terroriste ?|Courir, m'enfermer, appeler, attaquer si nécessaire|M’échapper, me cacher, secourir, combattre systématiquement|Alerter, éteindre, méloigner, boxer|Aucune des autres réponses|A</v>
+      </c>
+      <c r="D185" t="str" cm="1">
+        <f t="array" ref="D185:I185">_xlfn.TEXTSPLIT(C185,"|")</f>
+        <v>[UV7] Quelles sont les grandes priorités de réaction que je dois adopter face à une attaque terroriste ?</v>
+      </c>
+      <c r="E185" t="str">
+        <v>Courir, m'enfermer, appeler, attaquer si nécessaire</v>
+      </c>
+      <c r="F185" t="str">
+        <v>M’échapper, me cacher, secourir, combattre systématiquement</v>
+      </c>
+      <c r="G185" t="str">
+        <v>Alerter, éteindre, méloigner, boxer</v>
+      </c>
+      <c r="H185" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I185" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="18" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B186" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C186" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Qu’est-ce que le terrorisme d’Etat ?|Aucune des autres réponses|Lorsqu’un peuple terrorise son gouvernement|Lorsqu’un Etat terrorise son peuple|Lorsqu’un Etat combat de le terrorisme à l’intérieur de ses frontières|Lorsqu’une organisation terroriste veut prendre le pouvoir d’un Etat|C</v>
+      </c>
+      <c r="D186" t="str" cm="1">
+        <f t="array" ref="D186:J186">_xlfn.TEXTSPLIT(C186,"|")</f>
+        <v>[UV7] Qu’est-ce que le terrorisme d’Etat ?</v>
+      </c>
+      <c r="E186" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Lorsqu’un peuple terrorise son gouvernement</v>
+      </c>
+      <c r="G186" t="str">
+        <v>Lorsqu’un Etat terrorise son peuple</v>
+      </c>
+      <c r="H186" t="str">
+        <v>Lorsqu’un Etat combat de le terrorisme à l’intérieur de ses frontières</v>
+      </c>
+      <c r="I186" t="str">
+        <v>Lorsqu’une organisation terroriste veut prendre le pouvoir d’un Etat</v>
+      </c>
+      <c r="J186" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="18" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B187" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C187" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Un agent de sécurité exerçant ses fonctions dans un parc d’attraction peut-il appréhender un individu qui y entre avec une matraque et tente d’agresser un salarié du parc ?|Il peut juste l’aborder mais il ne peut pas l’appréhender en vertu de l’art. 73 du CPP|Aucune des autres réponses|Oui, car il sera dans le cadre de l’état de nécessité prévu dans l’art. 121-2 du Code Pénal|Non, car il n’y a pas d’infraction prévue pour ce type de fait|Le port d’une matraque constituant un délit, il peut appréhender l’individu au titre de l’art. 73 du CPP|E</v>
+      </c>
+      <c r="D187" t="str" cm="1">
+        <f t="array" ref="D187:J187">_xlfn.TEXTSPLIT(C187,"|")</f>
+        <v>[UV2] Un agent de sécurité exerçant ses fonctions dans un parc d’attraction peut-il appréhender un individu qui y entre avec une matraque et tente d’agresser un salarié du parc ?</v>
+      </c>
+      <c r="E187" t="str">
+        <v>Il peut juste l’aborder mais il ne peut pas l’appréhender en vertu de l’art. 73 du CPP</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="G187" t="str">
+        <v>Oui, car il sera dans le cadre de l’état de nécessité prévu dans l’art. 121-2 du Code Pénal</v>
+      </c>
+      <c r="H187" t="str">
+        <v>Non, car il n’y a pas d’infraction prévue pour ce type de fait</v>
+      </c>
+      <c r="I187" t="str">
+        <v>Le port d’une matraque constituant un délit, il peut appréhender l’individu au titre de l’art. 73 du CPP</v>
+      </c>
+      <c r="J187" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="18" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B188" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C188" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Un agent de sécurité privé peut être sanctionné par le CNAPS :|À une pénalité financière mais sans limite prise en charge par l’entreprise|À aucune pénalité financière|À une pénalité financière allant jusqu’à 10 000 euros|À une pénalité financière allant jusqu’à 7 500 euros|À une pénalité financière inférieure à 1 500 euros|D</v>
+      </c>
+      <c r="D188" t="str" cm="1">
+        <f t="array" ref="D188:J188">_xlfn.TEXTSPLIT(C188,"|")</f>
+        <v>[UV2] Un agent de sécurité privé peut être sanctionné par le CNAPS :</v>
+      </c>
+      <c r="E188" t="str">
+        <v>À une pénalité financière mais sans limite prise en charge par l’entreprise</v>
+      </c>
+      <c r="F188" t="str">
+        <v>À aucune pénalité financière</v>
+      </c>
+      <c r="G188" t="str">
+        <v>À une pénalité financière allant jusqu’à 10 000 euros</v>
+      </c>
+      <c r="H188" t="str">
+        <v>À une pénalité financière allant jusqu’à 7 500 euros</v>
+      </c>
+      <c r="I188" t="str">
+        <v>À une pénalité financière inférieure à 1 500 euros</v>
+      </c>
+      <c r="J188" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="18" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B189" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C189" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] À quoi peut servir un PPI/POI/PER ?|Aucune des autres réponses|À coordonner les moyens internes des installations classées|À prévoir la mobilisation des services de secours publics|À protéger les installations recevant du public|À planifier les opérations de maintien de l’ordre|C</v>
+      </c>
+      <c r="D189" t="str" cm="1">
+        <f t="array" ref="D189:J189">_xlfn.TEXTSPLIT(C189,"|")</f>
+        <v>[UV12] À quoi peut servir un PPI/POI/PER ?</v>
+      </c>
+      <c r="E189" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F189" t="str">
+        <v>À coordonner les moyens internes des installations classées</v>
+      </c>
+      <c r="G189" t="str">
+        <v>À prévoir la mobilisation des services de secours publics</v>
+      </c>
+      <c r="H189" t="str">
+        <v>À protéger les installations recevant du public</v>
+      </c>
+      <c r="I189" t="str">
+        <v>À planifier les opérations de maintien de l’ordre</v>
+      </c>
+      <c r="J189" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="18" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B190" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C190" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Il est puni par le code du sport (L332-3) dans une enceinte sportive, lors du déroulement ou de la retransmission en public d’une manifestation sportive :|Le fait d’introduire ou de tenter d’introduire, par force ou par fraude, des boissons alcoolisées|Toutes les réponses sont exactes|Le fait d’avoir, en état d’ivresse, pénétré ou tenté de pénétrer par force ou par fraude|D’un an d’emprisonnement ou d’amende|Le fait d’accéder en état d’ivresse|A</v>
+      </c>
+      <c r="D190" t="str" cm="1">
+        <f t="array" ref="D190:J190">_xlfn.TEXTSPLIT(C190,"|")</f>
+        <v>[UV12] Il est puni par le code du sport (L332-3) dans une enceinte sportive, lors du déroulement ou de la retransmission en public d’une manifestation sportive :</v>
+      </c>
+      <c r="E190" t="str">
+        <v>Le fait d’introduire ou de tenter d’introduire, par force ou par fraude, des boissons alcoolisées</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Toutes les réponses sont exactes</v>
+      </c>
+      <c r="G190" t="str">
+        <v>Le fait d’avoir, en état d’ivresse, pénétré ou tenté de pénétrer par force ou par fraude</v>
+      </c>
+      <c r="H190" t="str">
+        <v>D’un an d’emprisonnement ou d’amende</v>
+      </c>
+      <c r="I190" t="str">
+        <v>Le fait d’accéder en état d’ivresse</v>
+      </c>
+      <c r="J190" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B191" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C191" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Les organisateurs de manifestations sportives, récréatives ou culturelles sont tenus (R211-22 du CSI) :|D’en faire la déclaration uniquement si elles sont sur la liste des événements exposés|D’en faire la déclaration au Préfet de région au moins un an avant l’événement|D’en faire la déclaration aux maires ou aux Préfets de police, si la manifestation peut atteindre plus de 1500 personnes|Aucune des autres réponses|D’en faire la déclaration aux maires si la manifestation peut atteindre plus de 300 personnes et aux Préfets si elle dépasse plus de 1500 personnes|C</v>
+      </c>
+      <c r="D191" t="str" cm="1">
+        <f t="array" ref="D191:J191">_xlfn.TEXTSPLIT(C191,"|")</f>
+        <v>[UV12] Les organisateurs de manifestations sportives, récréatives ou culturelles sont tenus (R211-22 du CSI) :</v>
+      </c>
+      <c r="E191" t="str">
+        <v>D’en faire la déclaration uniquement si elles sont sur la liste des événements exposés</v>
+      </c>
+      <c r="F191" t="str">
+        <v>D’en faire la déclaration au Préfet de région au moins un an avant l’événement</v>
+      </c>
+      <c r="G191" t="str">
+        <v>D’en faire la déclaration aux maires ou aux Préfets de police, si la manifestation peut atteindre plus de 1500 personnes</v>
+      </c>
+      <c r="H191" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I191" t="str">
+        <v>D’en faire la déclaration aux maires si la manifestation peut atteindre plus de 300 personnes et aux Préfets si elle dépasse plus de 1500 personnes</v>
+      </c>
+      <c r="J191" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="18" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B192" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C192" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV9] Je suis agent dans un magasin : sous quelles conditions ai-je le droit d’inspecter des sacs ?|Je peux faire une inspection visuelle, dès lors que j’ai un doute|Je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaire|Aucune des autres réponses|J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille|Si c’est prévu dans les consignes, je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaires|D</v>
+      </c>
+      <c r="D192" t="str" cm="1">
+        <f t="array" ref="D192:J192">_xlfn.TEXTSPLIT(C192,"|")</f>
+        <v>[UV9] Je suis agent dans un magasin : sous quelles conditions ai-je le droit d’inspecter des sacs ?</v>
+      </c>
+      <c r="E192" t="str">
+        <v>Je peux faire une inspection visuelle, dès lors que j’ai un doute</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaire</v>
+      </c>
+      <c r="G192" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H192" t="str">
+        <v>J’ai le droit de faire une inspection visuelle des bagages et, avec le consentement de leur propriétaire, à leur fouille</v>
+      </c>
+      <c r="I192" t="str">
+        <v>Si c’est prévu dans les consignes, je peux vérifier visuellement et fouiller les sacs sans avoir besoin du consentement du propriétaires</v>
+      </c>
+      <c r="J192" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="18" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B193" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C193" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Qu’est-ce qu’une zone de protection ?|Lieu protégé par des filets empêchant l’introduction de pigeons dans le site|Lieu protégé par des paroies possédant une isolation phonique|Aucune des autres réponses|Lieu protégé contre les intempéries|Lieu protégé par un obstacle s’opposant à pénétration d’intrus dans le site|E</v>
+      </c>
+      <c r="D193" t="str" cm="1">
+        <f t="array" ref="D193:J193">_xlfn.TEXTSPLIT(C193,"|")</f>
+        <v>[UV8] Qu’est-ce qu’une zone de protection ?</v>
+      </c>
+      <c r="E193" t="str">
+        <v>Lieu protégé par des filets empêchant l’introduction de pigeons dans le site</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Lieu protégé par des paroies possédant une isolation phonique</v>
+      </c>
+      <c r="G193" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Lieu protégé contre les intempéries</v>
+      </c>
+      <c r="I193" t="str">
+        <v>Lieu protégé par un obstacle s’opposant à pénétration d’intrus dans le site</v>
+      </c>
+      <c r="J193" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="18" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B194" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C194" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Un point dit vulnérable lors d’une ronde est :|Un point comportant un danger permanent|Un point qui en cas d’atteinte pourrait handicaper le bon fonctionnement de l’entreprise|Un point régulièrement mis en défaut|Aucune des autres réponses|Un point sensible convoité par les voleurs|B</v>
+      </c>
+      <c r="D194" t="str" cm="1">
+        <f t="array" ref="D194:J194">_xlfn.TEXTSPLIT(C194,"|")</f>
+        <v>[UV8] Un point dit vulnérable lors d’une ronde est :</v>
+      </c>
+      <c r="E194" t="str">
+        <v>Un point comportant un danger permanent</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Un point qui en cas d’atteinte pourrait handicaper le bon fonctionnement de l’entreprise</v>
+      </c>
+      <c r="G194" t="str">
+        <v>Un point régulièrement mis en défaut</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I194" t="str">
+        <v>Un point sensible convoité par les voleurs</v>
+      </c>
+      <c r="J194" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="18" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B195" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C195" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Pendant votre ronde, vous découvrez un local en désordre avec un pied de biche au sol. Que faites-vous ?|Vous ramassez le pied de biche afin d’avoir un objet pour vous défendre|Vous prévenez immédiatement le PCS et inspecter prudemment les locaux voisins|Aucune des autres réponses|Vous ne faites rien et continuez votre rondre, c’est sûrement le bureau d’un salarié désordonné|Vous refermez la porte et prévenez le PCS|B</v>
+      </c>
+      <c r="D195" t="str" cm="1">
+        <f t="array" ref="D195:J195">_xlfn.TEXTSPLIT(C195,"|")</f>
+        <v>[UV8] Pendant votre ronde, vous découvrez un local en désordre avec un pied de biche au sol. Que faites-vous ?</v>
+      </c>
+      <c r="E195" t="str">
+        <v>Vous ramassez le pied de biche afin d’avoir un objet pour vous défendre</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Vous prévenez immédiatement le PCS et inspecter prudemment les locaux voisins</v>
+      </c>
+      <c r="G195" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Vous ne faites rien et continuez votre rondre, c’est sûrement le bureau d’un salarié désordonné</v>
+      </c>
+      <c r="I195" t="str">
+        <v>Vous refermez la porte et prévenez le PCS</v>
+      </c>
+      <c r="J195" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="18" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B196" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C196" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV6] Un agent de sécurité privé masculin doit appréhender un voleur en sortie de caisse, mais il s’agit d’une femme :|Il doit appeler une collègue du même sexe|Il agit normalement, néanmoins il est conseillé d’appeler un témoin féminin|Aucune des autres réponses|Il doit demander l’autorisation de la personne|Il ne peut rien faire sur une personne de sexe opposé|B</v>
+      </c>
+      <c r="D196" t="str" cm="1">
+        <f t="array" ref="D196:J196">_xlfn.TEXTSPLIT(C196,"|")</f>
+        <v>[UV6] Un agent de sécurité privé masculin doit appréhender un voleur en sortie de caisse, mais il s’agit d’une femme :</v>
+      </c>
+      <c r="E196" t="str">
+        <v>Il doit appeler une collègue du même sexe</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Il agit normalement, néanmoins il est conseillé d’appeler un témoin féminin</v>
+      </c>
+      <c r="G196" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Il doit demander l’autorisation de la personne</v>
+      </c>
+      <c r="I196" t="str">
+        <v>Il ne peut rien faire sur une personne de sexe opposé</v>
+      </c>
+      <c r="J196" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B197" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C197" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Les agents de sécurité employés par un bailleur d’immeuble à usage d’habitations peuvent être armés :|D’un bâton de défense de type TONFA|D’un fusil à pompe|D’une grenade lacrymogène ayant une capacité inférieure à 100 ml|Aucune des autres réponses|D’un pistolet mitrailleur|A</v>
+      </c>
+      <c r="D197" t="str" cm="1">
+        <f t="array" ref="D197:J197">_xlfn.TEXTSPLIT(C197,"|")</f>
+        <v>[UV2] Les agents de sécurité employés par un bailleur d’immeuble à usage d’habitations peuvent être armés :</v>
+      </c>
+      <c r="E197" t="str">
+        <v>D’un bâton de défense de type TONFA</v>
+      </c>
+      <c r="F197" t="str">
+        <v>D’un fusil à pompe</v>
+      </c>
+      <c r="G197" t="str">
+        <v>D’une grenade lacrymogène ayant une capacité inférieure à 100 ml</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I197" t="str">
+        <v>D’un pistolet mitrailleur</v>
+      </c>
+      <c r="J197" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="18" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B198" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C198" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Le schéma d’installation de la vidéoprotection permet :|D’installer, de maintenir et de mettre à disposition des prestataires des images|De capter, de transmettre, de stocker, de visionner les images|Aucune des autres réponses|De garantir aux forces de l’ordre la bonne réalisation de la mission de sûreté|De compléter le système de surveillance incendie|B</v>
+      </c>
+      <c r="D198" t="str" cm="1">
+        <f t="array" ref="D198:J198">_xlfn.TEXTSPLIT(C198,"|")</f>
+        <v>[UV12] Le schéma d’installation de la vidéoprotection permet :</v>
+      </c>
+      <c r="E198" t="str">
+        <v>D’installer, de maintenir et de mettre à disposition des prestataires des images</v>
+      </c>
+      <c r="F198" t="str">
+        <v>De capter, de transmettre, de stocker, de visionner les images</v>
+      </c>
+      <c r="G198" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H198" t="str">
+        <v>De garantir aux forces de l’ordre la bonne réalisation de la mission de sûreté</v>
+      </c>
+      <c r="I198" t="str">
+        <v>De compléter le système de surveillance incendie</v>
+      </c>
+      <c r="J198" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="18" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B199" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C199" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] À quoi correspond une crash barrière ?|Aucune des autres réponses|Un système de barrière type passage à niveau pour bloquer les accès|Des barrières de sécurité équipés de pieds empêchant le renversement|Un test en laboratoire de la résistance des barrières|L’action de lancer des barrières sur des véhicules voulant forcer l’accès|C</v>
+      </c>
+      <c r="D199" t="str" cm="1">
+        <f t="array" ref="D199:J199">_xlfn.TEXTSPLIT(C199,"|")</f>
+        <v>[UV12] À quoi correspond une crash barrière ?</v>
+      </c>
+      <c r="E199" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Un système de barrière type passage à niveau pour bloquer les accès</v>
+      </c>
+      <c r="G199" t="str">
+        <v>Des barrières de sécurité équipés de pieds empêchant le renversement</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Un test en laboratoire de la résistance des barrières</v>
+      </c>
+      <c r="I199" t="str">
+        <v>L’action de lancer des barrières sur des véhicules voulant forcer l’accès</v>
+      </c>
+      <c r="J199" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="18" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B200" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C200" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV12] Un APS effectue une ronde dans la chaufferie gaz, il peut y entrer si :|Il dispose d’une radio fabriquée après le 1er juillet 2017|Il dispose d’un matériel anti-déflagrant|Il dispose d’un émetteur multi-fréquences|Il dispose d’une pastille de détection de gaz homologuée|Aucune des autres réponses|B</v>
+      </c>
+      <c r="D200" t="str" cm="1">
+        <f t="array" ref="D200:J200">_xlfn.TEXTSPLIT(C200,"|")</f>
+        <v>[UV12] Un APS effectue une ronde dans la chaufferie gaz, il peut y entrer si :</v>
+      </c>
+      <c r="E200" t="str">
+        <v>Il dispose d’une radio fabriquée après le 1er juillet 2017</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Il dispose d’un matériel anti-déflagrant</v>
+      </c>
+      <c r="G200" t="str">
+        <v>Il dispose d’un émetteur multi-fréquences</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Il dispose d’une pastille de détection de gaz homologuée</v>
+      </c>
+      <c r="I200" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J200" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B201" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C201" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] Sur votre GTB/GTC vous recevez une alarme SURCHAUFF au niveau de la chaufferie. Que devez-vous faire en premier ?|Aucune des autres réponses|Arrêter le signal sonore de l’alarme|Appeler les services de secours|Couper la chaudière|Appeler le technicien compétent|B</v>
+      </c>
+      <c r="D201" t="str" cm="1">
+        <f t="array" ref="D201:J201">_xlfn.TEXTSPLIT(C201,"|")</f>
+        <v>[UV11] Sur votre GTB/GTC vous recevez une alarme SURCHAUFF au niveau de la chaufferie. Que devez-vous faire en premier ?</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Arrêter le signal sonore de l’alarme</v>
+      </c>
+      <c r="G201" t="str">
+        <v>Appeler les services de secours</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Couper la chaudière</v>
+      </c>
+      <c r="I201" t="str">
+        <v>Appeler le technicien compétent</v>
+      </c>
+      <c r="J201" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="18" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B202" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C202" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] En vous rendant sur une levée de doute intrusion, votre PC vous appelle car une détection incendie vient d’avoir lieu. Que faites-vous ?|Je termine la levée de doute intrusion sans effectuer les contrôles de rigueur pour aller sur la levée de doute incendie|Je fais demi-tour et priorise la détection incendie dont la gravité peut être supérieure|Aucune des autres réponses|Je poursuis la levée de doute intrusion, étant presque arrivé|Je demande au chef de poste d’effectuer lui-même la levée de doute incendie|B</v>
+      </c>
+      <c r="D202" t="str" cm="1">
+        <f t="array" ref="D202:J202">_xlfn.TEXTSPLIT(C202,"|")</f>
+        <v>[UV11] En vous rendant sur une levée de doute intrusion, votre PC vous appelle car une détection incendie vient d’avoir lieu. Que faites-vous ?</v>
+      </c>
+      <c r="E202" t="str">
+        <v>Je termine la levée de doute intrusion sans effectuer les contrôles de rigueur pour aller sur la levée de doute incendie</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Je fais demi-tour et priorise la détection incendie dont la gravité peut être supérieure</v>
+      </c>
+      <c r="G202" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Je poursuis la levée de doute intrusion, étant presque arrivé</v>
+      </c>
+      <c r="I202" t="str">
+        <v>Je demande au chef de poste d’effectuer lui-même la levée de doute incendie</v>
+      </c>
+      <c r="J202" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="18" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B203" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C203" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] En cas d’alarme observée sur la centrale incendie, quelle est généralement la procédure à suivre ?|Appel de l’astreinte incendie, attente des secours, intervention éventuelle sur le feu|Acquittement du signal sonore, lecture de l’information, levée de doute, plan d’action conforme aux consignes du site|Aucune des autres réponses|Levée de doute, appel des secours, retour au PCS|Intervention immédiate sur feu, appel des secours, réinitialisation central incendie|B</v>
+      </c>
+      <c r="D203" t="str" cm="1">
+        <f t="array" ref="D203:J203">_xlfn.TEXTSPLIT(C203,"|")</f>
+        <v>[UV11] En cas d’alarme observée sur la centrale incendie, quelle est généralement la procédure à suivre ?</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Appel de l’astreinte incendie, attente des secours, intervention éventuelle sur le feu</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Acquittement du signal sonore, lecture de l’information, levée de doute, plan d’action conforme aux consignes du site</v>
+      </c>
+      <c r="G203" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Levée de doute, appel des secours, retour au PCS</v>
+      </c>
+      <c r="I203" t="str">
+        <v>Intervention immédiate sur feu, appel des secours, réinitialisation central incendie</v>
+      </c>
+      <c r="J203" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="18" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B204" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C204" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV9] Quelles sont les méthodes pour les agents masculins pour effectuer des vérifications de sécurité sur des femmes qui sont au contrôle d’accès :|Les palpations de sécurité|La fouille à corps uniquement avec le consentement de la personne|La fouille au corps|Aucune des autres réponses|Le contrôle visuel des bagages|E</v>
+      </c>
+      <c r="D204" t="str" cm="1">
+        <f t="array" ref="D204:J204">_xlfn.TEXTSPLIT(C204,"|")</f>
+        <v>[UV9] Quelles sont les méthodes pour les agents masculins pour effectuer des vérifications de sécurité sur des femmes qui sont au contrôle d’accès :</v>
+      </c>
+      <c r="E204" t="str">
+        <v>Les palpations de sécurité</v>
+      </c>
+      <c r="F204" t="str">
+        <v>La fouille à corps uniquement avec le consentement de la personne</v>
+      </c>
+      <c r="G204" t="str">
+        <v>La fouille au corps</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I204" t="str">
+        <v>Le contrôle visuel des bagages</v>
+      </c>
+      <c r="J204" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="18" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B205" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C205" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV9] Dans quelle situation puis-je effectuer des palpations de sécurité ?|Dans tout le magasin sur des personnes soupçonnées de vouloir fumer|À l’intérieur d’une salle de concert à la demande du chef de poste|Dans tout lieu visé par un arrêté préfectoral|À la sortie du magasin sur un individu connu pour des actes de vol|Aucune des autres réponses|C</v>
+      </c>
+      <c r="D205" t="str" cm="1">
+        <f t="array" ref="D205:J205">_xlfn.TEXTSPLIT(C205,"|")</f>
+        <v>[UV9] Dans quelle situation puis-je effectuer des palpations de sécurité ?</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Dans tout le magasin sur des personnes soupçonnées de vouloir fumer</v>
+      </c>
+      <c r="F205" t="str">
+        <v>À l’intérieur d’une salle de concert à la demande du chef de poste</v>
+      </c>
+      <c r="G205" t="str">
+        <v>Dans tout lieu visé par un arrêté préfectoral</v>
+      </c>
+      <c r="H205" t="str">
+        <v>À la sortie du magasin sur un individu connu pour des actes de vol</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J205" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="18" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B206" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C206" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV8] Certaines circonstances peuvent aggraver le vol. Par exemple quand le vol est commis :|Par plusieurs personnes|Chez une personne dépositaire de l’autorité publique|Sur une personne dans la journée|Aucune des autres réponses|Dans un local sous surveillance électronique|A</v>
+      </c>
+      <c r="D206" t="str" cm="1">
+        <f t="array" ref="D206:J206">_xlfn.TEXTSPLIT(C206,"|")</f>
+        <v>[UV8] Certaines circonstances peuvent aggraver le vol. Par exemple quand le vol est commis :</v>
+      </c>
+      <c r="E206" t="str">
+        <v>Par plusieurs personnes</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Chez une personne dépositaire de l’autorité publique</v>
+      </c>
+      <c r="G206" t="str">
+        <v>Sur une personne dans la journée</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Dans un local sous surveillance électronique</v>
+      </c>
+      <c r="J206" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="18" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B207" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C207" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Dès l’arrivée des forces de l’ordre, dans une zone d’attentat, vous devez en premier :|Leur parler de la situation|Courir vers eux|Leur indiquer l’emplacement des victimes|Suivre leurs instructions|Aucune des autres réponses|D</v>
+      </c>
+      <c r="D207" t="str" cm="1">
+        <f t="array" ref="D207:J207">_xlfn.TEXTSPLIT(C207,"|")</f>
+        <v>[UV7] Dès l’arrivée des forces de l’ordre, dans une zone d’attentat, vous devez en premier :</v>
+      </c>
+      <c r="E207" t="str">
+        <v>Leur parler de la situation</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Courir vers eux</v>
+      </c>
+      <c r="G207" t="str">
+        <v>Leur indiquer l’emplacement des victimes</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Suivre leurs instructions</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J207" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="18" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B208" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C208" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV7] Parmi les types de “BLAST” suivants, lequel ou lesquels existent ?|BLAST primaire|BLAST tertiaire|BLAST quaternaire|Toutes les réponses précédentes sont exactes|BLAST secondaire|D</v>
+      </c>
+      <c r="D208" t="str" cm="1">
+        <f t="array" ref="D208:J208">_xlfn.TEXTSPLIT(C208,"|")</f>
+        <v>[UV7] Parmi les types de “BLAST” suivants, lequel ou lesquels existent ?</v>
+      </c>
+      <c r="E208" t="str">
+        <v>BLAST primaire</v>
+      </c>
+      <c r="F208" t="str">
+        <v>BLAST tertiaire</v>
+      </c>
+      <c r="G208" t="str">
+        <v>BLAST quaternaire</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Toutes les réponses précédentes sont exactes</v>
+      </c>
+      <c r="I208" t="str">
+        <v>BLAST secondaire</v>
+      </c>
+      <c r="J208" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="18" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B209" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C209" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Agent de sécurité, je dispose d’un véhicule d’entreprise équipé d’un gyrophare orange :|Aucune des autres réponses|C’est absolument interdit|C’est autorisé uniquement à l’intérieur des sites surveillés, si les consignes le prévoient|Seuls les gyrophares bleus sont autorisés pour les agents de sécurité|C’est interdit, sauf en situation d’urgence attentat|C</v>
+      </c>
+      <c r="D209" t="str" cm="1">
+        <f t="array" ref="D209:J209">_xlfn.TEXTSPLIT(C209,"|")</f>
+        <v>[UV2] Agent de sécurité, je dispose d’un véhicule d’entreprise équipé d’un gyrophare orange :</v>
+      </c>
+      <c r="E209" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="F209" t="str">
+        <v>C’est absolument interdit</v>
+      </c>
+      <c r="G209" t="str">
+        <v>C’est autorisé uniquement à l’intérieur des sites surveillés, si les consignes le prévoient</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Seuls les gyrophares bleus sont autorisés pour les agents de sécurité</v>
+      </c>
+      <c r="I209" t="str">
+        <v>C’est interdit, sauf en situation d’urgence attentat</v>
+      </c>
+      <c r="J209" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B210" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C210" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV2] Selon la loi, est une arme par destination :|Tout objet conçu pour usage professionnel|Tout objet conçu pour tuer ou blesser|Aucune des autres réponses|Tout objet susceptible de présenter un danger pour des personnes, dès lors qu’il est utilisé pour menacer|Tout objet pouvant causer des dommages|D</v>
+      </c>
+      <c r="D210" t="str" cm="1">
+        <f t="array" ref="D210:J210">_xlfn.TEXTSPLIT(C210,"|")</f>
+        <v>[UV2] Selon la loi, est une arme par destination :</v>
+      </c>
+      <c r="E210" t="str">
+        <v>Tout objet conçu pour usage professionnel</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Tout objet conçu pour tuer ou blesser</v>
+      </c>
+      <c r="G210" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Tout objet susceptible de présenter un danger pour des personnes, dès lors qu’il est utilisé pour menacer</v>
+      </c>
+      <c r="I210" t="str">
+        <v>Tout objet pouvant causer des dommages</v>
+      </c>
+      <c r="J210" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="18" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B211" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C211" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV11] Le report d’alarme d’une centrale intrusion est un dispositif :|Uniquement destiné aux équipes de sûreté en cas d’intrusion|De secours en cas de défaillance du clavier principal|Qui permet aux agents d’accéder à certaines informations hors du PCS|De cloisonnement anti-intrusion indépendant du système central|Aucune des autres réponses|C</v>
+      </c>
+      <c r="D211" t="str" cm="1">
+        <f t="array" ref="D211:J211">_xlfn.TEXTSPLIT(C211,"|")</f>
+        <v>[UV11] Le report d’alarme d’une centrale intrusion est un dispositif :</v>
+      </c>
+      <c r="E211" t="str">
+        <v>Uniquement destiné aux équipes de sûreté en cas d’intrusion</v>
+      </c>
+      <c r="F211" t="str">
+        <v>De secours en cas de défaillance du clavier principal</v>
+      </c>
+      <c r="G211" t="str">
+        <v>Qui permet aux agents d’accéder à certaines informations hors du PCS</v>
+      </c>
+      <c r="H211" t="str">
+        <v>De cloisonnement anti-intrusion indépendant du système central</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J211" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="18" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B212" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C212" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV14] Dans quel document l’APS peut trouver les mesures opératoires des secours extérieurs lors d’un sinistre majeur ?|Le Plan des Opérations Externes (P.O.E.)|Le Plan Particulier d’Intervention (P.P.I. ou équivalent)|Le Plan de Secours Extérieurs (P.S.E.)|Le Plan Particulier des Risques Majeurs (P.P.R.M.)|Aucune des autres réponses|B</v>
+      </c>
+      <c r="D212" t="str" cm="1">
+        <f t="array" ref="D212:J212">_xlfn.TEXTSPLIT(C212,"|")</f>
+        <v>[UV14] Dans quel document l’APS peut trouver les mesures opératoires des secours extérieurs lors d’un sinistre majeur ?</v>
+      </c>
+      <c r="E212" t="str">
+        <v>Le Plan des Opérations Externes (P.O.E.)</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Le Plan Particulier d’Intervention (P.P.I. ou équivalent)</v>
+      </c>
+      <c r="G212" t="str">
+        <v>Le Plan de Secours Extérieurs (P.S.E.)</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Le Plan Particulier des Risques Majeurs (P.P.R.M.)</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J212" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="18" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B213" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C213" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV14] Quand doit-on rédiger notamment impérativement un Plan de Prévention ?|En cas de travaux dangereux listés dans l’arrêté du 19 mars 1993|Uniquement lorsque les consignes de sûreté le prévoient|Si vous estimez que l’importance des travaux le nécessitent|Uniquement sur demande explicite du client|Aucune des autres réponses|A</v>
+      </c>
+      <c r="D213" t="str" cm="1">
+        <f t="array" ref="D213:J213">_xlfn.TEXTSPLIT(C213,"|")</f>
+        <v>[UV14] Quand doit-on rédiger notamment impérativement un Plan de Prévention ?</v>
+      </c>
+      <c r="E213" t="str">
+        <v>En cas de travaux dangereux listés dans l’arrêté du 19 mars 1993</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Uniquement lorsque les consignes de sûreté le prévoient</v>
+      </c>
+      <c r="G213" t="str">
+        <v>Si vous estimez que l’importance des travaux le nécessitent</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Uniquement sur demande explicite du client</v>
+      </c>
+      <c r="I213" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J213" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="18" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B214" s="17">
+        <f t="shared" si="22"/>
+        <v>3</v>
+      </c>
+      <c r="C214" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v>[UV14] Quel est l’objectif général de la prévention ?|Définir les mesures de sûreté|Protéger l’employeur du risque pénal|Améliorer les statistiques concernant les taux d’accidents|Éviter ou limiter les dommages|Aucune des autres réponses|D</v>
+      </c>
+      <c r="D214" t="str" cm="1">
+        <f t="array" ref="D214:J214">_xlfn.TEXTSPLIT(C214,"|")</f>
+        <v>[UV14] Quel est l’objectif général de la prévention ?</v>
+      </c>
+      <c r="E214" t="str">
+        <v>Définir les mesures de sûreté</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Protéger l’employeur du risque pénal</v>
+      </c>
+      <c r="G214" t="str">
+        <v>Améliorer les statistiques concernant les taux d’accidents</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Éviter ou limiter les dommages</v>
+      </c>
+      <c r="I214" t="str">
+        <v>Aucune des autres réponses</v>
+      </c>
+      <c r="J214" t="str">
+        <v>D</v>
       </c>
     </row>
   </sheetData>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CBEB89E-8F5C-4FAC-96A6-1B70A9A4549D}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2938AC39-D197-41FD-8413-7FB52ABEEA15}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14051,7 +14051,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>11</v>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2938AC39-D197-41FD-8413-7FB52ABEEA15}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E86F174-DF7C-40B3-BCBC-E4A6A300888D}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6390" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste_Questions" sheetId="1" r:id="rId1"/>
@@ -5839,9 +5839,6 @@
     <t>La zone de commandement des forces de l’ordre</t>
   </si>
   <si>
-    <t>La zone d’accueil des force de l’ordre et des secours</t>
-  </si>
-  <si>
     <t>[UV2] Un revolver chambré pour le calibre 38 spécial est une arme de catégorie :</t>
   </si>
   <si>
@@ -5860,9 +5857,6 @@
     <t>Crime</t>
   </si>
   <si>
-    <t>[UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein de périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :</t>
-  </si>
-  <si>
     <t>Avec le consentement de son conducteur, par un agent de prévention et de sécurité placé sous l’autorité d’un OPJ</t>
   </si>
   <si>
@@ -5899,9 +5893,6 @@
     <t>Un plan de limitation des déplacements dans le cadre du plan Vigipirates “Urgence Attentat”</t>
   </si>
   <si>
-    <t>Un plan d’Organisation de la Réponses de la Sécurité Civile</t>
-  </si>
-  <si>
     <t>Un plan de circulation des riverains lors des événement culturels ou festifs</t>
   </si>
   <si>
@@ -6431,6 +6422,15 @@
   </si>
   <si>
     <t>[UV7] Que signifie le R de NRBC-E ?</t>
+  </si>
+  <si>
+    <t>Un plan d’Organisation de la Réponse de la Sécurité Civile</t>
+  </si>
+  <si>
+    <t>[UV12] Lorsque des véhicules sont susceptibles de pénétrer au sein d'un périmètre de protection (L266-1 du CSI), la loi peut également en subordonner l’accès à l’inspection visuelle du contenu du véhicule :</t>
+  </si>
+  <si>
+    <t>La zone d’accueil des forces de l’ordre et des secours</t>
   </si>
 </sst>
 </file>
@@ -13471,13 +13471,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>1255</v>
@@ -13500,7 +13500,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>13</v>
@@ -13529,7 +13529,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>15</v>
@@ -13558,7 +13558,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>16</v>
@@ -13587,7 +13587,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>17</v>
@@ -13616,7 +13616,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>19</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>20</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>22</v>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>24</v>
@@ -13732,7 +13732,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>25</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>26</v>
@@ -13782,7 +13782,7 @@
         <v>90</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>1309</v>
+        <v>1506</v>
       </c>
       <c r="J216" s="10" t="s">
         <v>21</v>
@@ -13790,13 +13790,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>18</v>
@@ -13814,33 +13814,33 @@
         <v>21</v>
       </c>
       <c r="J217" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B218" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C218" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D218" s="2" t="s">
         <v>1311</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>1312</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F218" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G218" s="2" t="s">
         <v>1313</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="H218" s="2" t="s">
         <v>1314</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>1315</v>
       </c>
       <c r="J218" s="10" t="s">
         <v>23</v>
@@ -13848,13 +13848,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1316</v>
+        <v>1505</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>896</v>
@@ -13866,7 +13866,7 @@
         <v>895</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>90</v>
@@ -13877,22 +13877,22 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="F220" s="2" t="s">
         <v>1319</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>1320</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1321</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>90</v>
@@ -13906,28 +13906,28 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>1322</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="F221" s="2" t="s">
         <v>1323</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>1325</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="J221" s="10" t="s">
         <v>14</v>
@@ -13935,28 +13935,28 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B222" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E222" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H222" s="2" t="s">
         <v>1328</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G222" s="2" t="s">
-        <v>1330</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>1331</v>
       </c>
       <c r="J222" s="10" t="s">
         <v>18</v>
@@ -13964,28 +13964,28 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B223" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="J223" s="10" t="s">
         <v>14</v>
@@ -13993,13 +13993,13 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B224" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>438</v>
@@ -14022,13 +14022,13 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B225" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>440</v>
@@ -14051,28 +14051,28 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F226" s="2" t="s">
         <v>1339</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>1340</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1341</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1342</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J226" s="10" t="s">
         <v>21</v>
@@ -14080,25 +14080,25 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B227" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>1344</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="G227" s="2" t="s">
         <v>1345</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>1348</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>90</v>
@@ -14109,25 +14109,25 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>1349</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="G228" s="2" t="s">
         <v>1350</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>1351</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1352</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>1353</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>90</v>
@@ -14138,25 +14138,25 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="G229" s="2" t="s">
         <v>1355</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>1356</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>1357</v>
-      </c>
-      <c r="G229" s="2" t="s">
-        <v>1358</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>90</v>
@@ -14167,28 +14167,28 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E230" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H230" s="2" t="s">
         <v>1360</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>1363</v>
       </c>
       <c r="J230" s="10" t="s">
         <v>18</v>
@@ -14196,22 +14196,22 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B231" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>1364</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>1367</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>90</v>
@@ -14222,28 +14222,28 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E232" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H232" s="2" t="s">
         <v>1369</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>1371</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>1372</v>
       </c>
       <c r="J232" s="10" t="s">
         <v>18</v>
@@ -14251,28 +14251,28 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="J233" s="10" t="s">
         <v>23</v>
@@ -14280,28 +14280,28 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="G234" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="E234" s="2" t="s">
+      <c r="H234" s="2" t="s">
         <v>1380</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>1382</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>1383</v>
       </c>
       <c r="J234" s="10" t="s">
         <v>12</v>
@@ -14309,28 +14309,28 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E235" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H235" s="2" t="s">
         <v>1385</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>1386</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>1388</v>
       </c>
       <c r="J235" s="10" t="s">
         <v>18</v>
@@ -14338,28 +14338,28 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B236" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="J236" s="10" t="s">
         <v>14</v>
@@ -14367,28 +14367,28 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B237" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>940</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="J237" s="10" t="s">
         <v>18</v>
@@ -14396,19 +14396,19 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>90</v>
@@ -14417,7 +14417,7 @@
         <v>1293</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="J238" s="10" t="s">
         <v>12</v>
@@ -14425,28 +14425,28 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B239" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="J239" s="10" t="s">
         <v>23</v>
@@ -14454,13 +14454,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B240" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>475</v>
@@ -14469,13 +14469,13 @@
         <v>473</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="J240" s="10" t="s">
         <v>21</v>
@@ -14483,28 +14483,28 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B241" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="J241" s="10" t="s">
         <v>21</v>
@@ -14512,28 +14512,28 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="J242" s="10" t="s">
         <v>21</v>
@@ -14541,28 +14541,28 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="J243" s="10" t="s">
         <v>14</v>
@@ -14570,13 +14570,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>881</v>
@@ -14599,28 +14599,28 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B245" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E245" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H245" s="2" t="s">
         <v>1426</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="G245" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>1429</v>
       </c>
       <c r="J245" s="10" t="s">
         <v>18</v>
@@ -14628,25 +14628,25 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B246" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="G246" s="2" t="s">
         <v>1431</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="G246" s="2" t="s">
-        <v>1434</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>90</v>
@@ -14657,28 +14657,28 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B247" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E247" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H247" s="2" t="s">
         <v>1436</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G247" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>1439</v>
       </c>
       <c r="J247" s="10" t="s">
         <v>21</v>
@@ -14686,28 +14686,28 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B248" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="J248" s="10" t="s">
         <v>21</v>
@@ -14715,28 +14715,28 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B249" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="J249" s="10" t="s">
         <v>21</v>
@@ -14744,13 +14744,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B250" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>732</v>
@@ -14765,7 +14765,7 @@
         <v>90</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="J250" s="10" t="s">
         <v>23</v>
@@ -14773,25 +14773,25 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B251" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>1452</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="G251" s="2" t="s">
         <v>1453</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="G251" s="2" t="s">
-        <v>1456</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>90</v>
@@ -14802,28 +14802,28 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B252" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>1457</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>1460</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="J252" s="10" t="s">
         <v>14</v>
@@ -14831,25 +14831,25 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>1462</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="G253" s="2" t="s">
         <v>1463</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G253" s="2" t="s">
-        <v>1466</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>90</v>
@@ -14860,28 +14860,28 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>1467</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>1470</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>377</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="J254" s="10" t="s">
         <v>12</v>
@@ -14889,28 +14889,28 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B255" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E255" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H255" s="2" t="s">
         <v>1473</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>1476</v>
       </c>
       <c r="J255" s="10" t="s">
         <v>18</v>
@@ -14918,28 +14918,28 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="J256" s="10" t="s">
         <v>12</v>
@@ -14947,25 +14947,25 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B257" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>1482</v>
       </c>
-      <c r="D257" s="2" t="s">
+      <c r="G257" s="2" t="s">
         <v>1483</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G257" s="2" t="s">
-        <v>1486</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>90</v>
@@ -14976,25 +14976,25 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B258" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="G258" s="2" t="s">
         <v>1488</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>1491</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>90</v>
@@ -15005,25 +15005,25 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B259" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="D259" s="2" t="s">
+      <c r="G259" s="2" t="s">
         <v>1493</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>1496</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>90</v>
@@ -15034,25 +15034,25 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="9" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B260" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="D260" s="2" t="s">
+      <c r="G260" s="2" t="s">
         <v>1498</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>1501</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>90</v>
@@ -15244,26 +15244,26 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>1502</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E86F174-DF7C-40B3-BCBC-E4A6A300888D}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B24B49B-FEB7-4C8A-A640-A64176F8F4C7}"/>
   <bookViews>
     <workbookView xWindow="6390" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6004,9 +6004,6 @@
     <t>M’échapper, me cacher, secourir, combattre systématiquement</t>
   </si>
   <si>
-    <t>Alerter, éteindre, méloigner, boxer</t>
-  </si>
-  <si>
     <t>[UV7] Qu’est-ce que le terrorisme d’Etat ?</t>
   </si>
   <si>
@@ -6139,12 +6136,6 @@
     <t>Vous ramassez le pied de biche afin d’avoir un objet pour vous défendre</t>
   </si>
   <si>
-    <t>Vous prévenez immédiatement le PCS et inspecter prudemment les locaux voisins</t>
-  </si>
-  <si>
-    <t>Vous ne faites rien et continuez votre rondre, c’est sûrement le bureau d’un salarié désordonné</t>
-  </si>
-  <si>
     <t>Vous refermez la porte et prévenez le PCS</t>
   </si>
   <si>
@@ -6184,9 +6175,6 @@
     <t>Un système de barrière type passage à niveau pour bloquer les accès</t>
   </si>
   <si>
-    <t>Des barrières de sécurité équipés de pieds empêchant le renversement</t>
-  </si>
-  <si>
     <t>Un test en laboratoire de la résistance des barrières</t>
   </si>
   <si>
@@ -6431,6 +6419,18 @@
   </si>
   <si>
     <t>La zone d’accueil des forces de l’ordre et des secours</t>
+  </si>
+  <si>
+    <t>Vous prévenez immédiatement le PCS et inspectez prudemment les locaux voisins</t>
+  </si>
+  <si>
+    <t>Vous ne faites rien et continuez votre ronde, c’est sûrement le bureau d’un salarié désordonné</t>
+  </si>
+  <si>
+    <t>Des barrières de sécurité équipées de pieds empêchant le renversement</t>
+  </si>
+  <si>
+    <t>Alerter, éteindre, m'éloigner, boxer</t>
   </si>
 </sst>
 </file>
@@ -13471,13 +13471,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>1255</v>
@@ -13500,7 +13500,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>13</v>
@@ -13529,7 +13529,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>15</v>
@@ -13558,7 +13558,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>16</v>
@@ -13587,7 +13587,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>17</v>
@@ -13616,7 +13616,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>19</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>20</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>22</v>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>24</v>
@@ -13732,7 +13732,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>25</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>26</v>
@@ -13782,7 +13782,7 @@
         <v>90</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="J216" s="10" t="s">
         <v>21</v>
@@ -13790,7 +13790,7 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>27</v>
@@ -13819,7 +13819,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B218" s="9" t="s">
         <v>28</v>
@@ -13848,13 +13848,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>896</v>
@@ -13877,7 +13877,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>31</v>
@@ -13935,7 +13935,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B222" s="9" t="s">
         <v>32</v>
@@ -13950,7 +13950,7 @@
         <v>1326</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>1327</v>
@@ -13964,7 +13964,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B223" s="9" t="s">
         <v>33</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B224" s="9" t="s">
         <v>34</v>
@@ -14022,7 +14022,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B225" s="9" t="s">
         <v>35</v>
@@ -14051,7 +14051,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>11</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B227" s="9" t="s">
         <v>13</v>
@@ -14109,7 +14109,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>15</v>
@@ -14138,7 +14138,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>16</v>
@@ -14167,7 +14167,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>17</v>
@@ -14196,7 +14196,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B231" s="9" t="s">
         <v>19</v>
@@ -14211,7 +14211,7 @@
         <v>1363</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1364</v>
+        <v>1506</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>90</v>
@@ -14222,28 +14222,28 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E232" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="F232" s="2" t="s">
+      <c r="G232" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="G232" s="2" t="s">
+      <c r="H232" s="2" t="s">
         <v>1368</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>1369</v>
       </c>
       <c r="J232" s="10" t="s">
         <v>18</v>
@@ -14251,28 +14251,28 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>1370</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>1371</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F233" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G233" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="G233" s="2" t="s">
+      <c r="H233" s="2" t="s">
         <v>1373</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>1374</v>
       </c>
       <c r="J233" s="10" t="s">
         <v>23</v>
@@ -14280,28 +14280,28 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="E234" s="2" t="s">
+      <c r="F234" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="F234" s="2" t="s">
+      <c r="G234" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="G234" s="2" t="s">
+      <c r="H234" s="2" t="s">
         <v>1379</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>1380</v>
       </c>
       <c r="J234" s="10" t="s">
         <v>12</v>
@@ -14309,28 +14309,28 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E235" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="F235" s="2" t="s">
+      <c r="G235" s="2" t="s">
         <v>1383</v>
       </c>
-      <c r="G235" s="2" t="s">
+      <c r="H235" s="2" t="s">
         <v>1384</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>1385</v>
       </c>
       <c r="J235" s="10" t="s">
         <v>18</v>
@@ -14338,28 +14338,28 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B236" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>1386</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>1387</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F236" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G236" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="H236" s="2" t="s">
         <v>1389</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>1390</v>
       </c>
       <c r="J236" s="10" t="s">
         <v>14</v>
@@ -14367,28 +14367,28 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B237" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>940</v>
       </c>
       <c r="E237" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>1392</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>1393</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J237" s="10" t="s">
         <v>18</v>
@@ -14396,19 +14396,19 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D238" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="E238" s="2" t="s">
         <v>1396</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>1397</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>90</v>
@@ -14417,7 +14417,7 @@
         <v>1293</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J238" s="10" t="s">
         <v>12</v>
@@ -14425,28 +14425,28 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B239" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="E239" s="2" t="s">
         <v>1400</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>1401</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G239" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H239" s="2" t="s">
         <v>1402</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>1403</v>
       </c>
       <c r="J239" s="10" t="s">
         <v>23</v>
@@ -14454,13 +14454,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B240" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>475</v>
@@ -14469,13 +14469,13 @@
         <v>473</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J240" s="10" t="s">
         <v>21</v>
@@ -14483,28 +14483,28 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B241" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>1408</v>
-      </c>
       <c r="E241" s="2" t="s">
-        <v>1409</v>
+        <v>1503</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>1410</v>
+        <v>1504</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="J241" s="10" t="s">
         <v>21</v>
@@ -14512,28 +14512,28 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="J242" s="10" t="s">
         <v>21</v>
@@ -14541,28 +14541,28 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="J243" s="10" t="s">
         <v>14</v>
@@ -14570,13 +14570,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>881</v>
@@ -14599,28 +14599,28 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B245" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1424</v>
+        <v>1505</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="J245" s="10" t="s">
         <v>18</v>
@@ -14628,25 +14628,25 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B246" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G246" s="2" t="s">
         <v>1427</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>1430</v>
-      </c>
-      <c r="G246" s="2" t="s">
-        <v>1431</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>90</v>
@@ -14657,28 +14657,28 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B247" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="J247" s="10" t="s">
         <v>21</v>
@@ -14686,28 +14686,28 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B248" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="J248" s="10" t="s">
         <v>21</v>
@@ -14715,28 +14715,28 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B249" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="J249" s="10" t="s">
         <v>21</v>
@@ -14744,13 +14744,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B250" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>732</v>
@@ -14765,7 +14765,7 @@
         <v>90</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="J250" s="10" t="s">
         <v>23</v>
@@ -14773,25 +14773,25 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B251" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G251" s="2" t="s">
         <v>1449</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="G251" s="2" t="s">
-        <v>1453</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>90</v>
@@ -14802,28 +14802,28 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B252" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="J252" s="10" t="s">
         <v>14</v>
@@ -14831,25 +14831,25 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G253" s="2" t="s">
         <v>1459</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G253" s="2" t="s">
-        <v>1463</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>90</v>
@@ -14860,28 +14860,28 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>377</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="J254" s="10" t="s">
         <v>12</v>
@@ -14889,28 +14889,28 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B255" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="J255" s="10" t="s">
         <v>18</v>
@@ -14918,28 +14918,28 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="J256" s="10" t="s">
         <v>12</v>
@@ -14947,25 +14947,25 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B257" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G257" s="2" t="s">
         <v>1479</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="G257" s="2" t="s">
-        <v>1483</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>90</v>
@@ -14976,25 +14976,25 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B258" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G258" s="2" t="s">
         <v>1484</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>1488</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>90</v>
@@ -15005,25 +15005,25 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B259" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G259" s="2" t="s">
         <v>1489</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>1493</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>90</v>
@@ -15034,25 +15034,25 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B260" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G260" s="2" t="s">
         <v>1494</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>1498</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>90</v>
@@ -15244,26 +15244,26 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCB96D6-331C-418F-9098-1FCF4AD87BEE}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{563156A6-C701-4544-B924-3AB98E28A67D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1530">
   <si>
     <t>UV</t>
   </si>
@@ -6437,6 +6437,69 @@
   </si>
   <si>
     <t>VRAC (4)</t>
+  </si>
+  <si>
+    <t>[UV2] La liberté d’aller et venir s’inscrit dans le respect :</t>
+  </si>
+  <si>
+    <t>[UV2] Les acteurs de la sécurité privée doivent respecter la confidentialité des informations dont ils ont eu connaissance dans le cadre de leur activité :</t>
+  </si>
+  <si>
+    <t>[UV2] Que risque un employeur qui a conclu un contrat de travail avec un agent de sécurité, non titulaire de la carte professionnelle ?</t>
+  </si>
+  <si>
+    <t>[UV2] Le port et transport d’armes sans agrément spécifique, de type générateurs aérosols (de catégorie D) et arme à impulsion électrique de contact :</t>
+  </si>
+  <si>
+    <t>[UV3] Quels sont les 4 comportements pouvant être adoptés théoriquement lors d’un conflit ?</t>
+  </si>
+  <si>
+    <t>[UV4] Une consigne qui vous explique la procédure pour pénétrer dans un local où des matières toxiques sont entreposées en permanence est :</t>
+  </si>
+  <si>
+    <t>[UV4] La consigne affichée à proximité des sorties concernant l’évacuation est :</t>
+  </si>
+  <si>
+    <t>[UV5] Lors de la mise en place d’un permis feu, quelles consignes sont importantes à confier à l’exécutant ?</t>
+  </si>
+  <si>
+    <t>[UV9] Quel est le seuil fixé par le Code de la Sécurité Intérieure, concernant l’obligation de palpation de sécurité des manifestations ?</t>
+  </si>
+  <si>
+    <t>[UV9] D’après le Code de la Sécurité Intérieure, quelles conditions devez-vous respecter pour effectuer une palpation de sécurité lorsqu’un périmètre de protection a été institué ?</t>
+  </si>
+  <si>
+    <t>[UV9] Suite à une appréhension en flagrant délit pour vol, je vois que l’individu possède un couteau dans sa poche de blouson. Que dois-je faire ?</t>
+  </si>
+  <si>
+    <t>[UV10] La CNIL est :</t>
+  </si>
+  <si>
+    <t>[UV10] Dans lequel de ces textes la vidéoprotection est-elle encadrée ?</t>
+  </si>
+  <si>
+    <t>[UV10] Agent de vidéosurveillance sur un site en journée, vous repérez un individu au visage dissimulé dans un local sensible à accès réglementé, que faites-vous ?</t>
+  </si>
+  <si>
+    <t>[UV10] Quelle est la composition de la chaîne de télésécurité ?</t>
+  </si>
+  <si>
+    <t>[UV11] Lors d’un appel du PC de télésurveillance pour une alarme intrusion sur votre site, vous devez en premier lieu :</t>
+  </si>
+  <si>
+    <t>[UV11] Vous êtes seul sur site lors d’une ronde, vous constatez un incendie, que faites-vous en premier ?</t>
+  </si>
+  <si>
+    <t>[UV14] Que signifie POI ?</t>
+  </si>
+  <si>
+    <t>[UV14] Quel est le rôle du Document Unique (DU) ?</t>
+  </si>
+  <si>
+    <t>[UV14] Que signifie l’abrégé P.P.I. ?</t>
+  </si>
+  <si>
+    <t>[UV14] La directive SEVESO est applicable pour ?</t>
   </si>
 </sst>
 </file>
@@ -6660,7 +6723,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{739EAF5D-6DEC-4933-BEAA-58326FF9FE6A}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6708,14 +6771,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCCFF66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -15100,7 +15155,7 @@
         <v>31</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>61</v>
+        <v>1509</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>124</v>
@@ -15132,7 +15187,7 @@
         <v>11</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>63</v>
+        <v>1510</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>133</v>
@@ -15164,7 +15219,7 @@
         <v>13</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>65</v>
+        <v>1511</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>141</v>
@@ -15196,7 +15251,7 @@
         <v>15</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>77</v>
+        <v>1512</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>185</v>
@@ -15228,7 +15283,7 @@
         <v>16</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>279</v>
+        <v>1513</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>280</v>
@@ -15257,7 +15312,7 @@
         <v>17</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>346</v>
+        <v>1514</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>347</v>
@@ -15286,7 +15341,7 @@
         <v>19</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>354</v>
+        <v>1515</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>352</v>
@@ -15315,7 +15370,7 @@
         <v>20</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>672</v>
+        <v>1516</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>673</v>
@@ -15344,7 +15399,7 @@
         <v>22</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>722</v>
+        <v>1517</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>723</v>
@@ -15373,7 +15428,7 @@
         <v>24</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>737</v>
+        <v>1518</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>738</v>
@@ -15402,7 +15457,7 @@
         <v>25</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>742</v>
+        <v>1519</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>743</v>
@@ -15431,7 +15486,7 @@
         <v>26</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>783</v>
+        <v>1520</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>784</v>
@@ -15460,7 +15515,7 @@
         <v>27</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>808</v>
+        <v>1521</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>809</v>
@@ -15489,7 +15544,7 @@
         <v>28</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>813</v>
+        <v>1522</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>814</v>
@@ -15518,7 +15573,7 @@
         <v>29</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>833</v>
+        <v>1523</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>834</v>
@@ -15547,7 +15602,7 @@
         <v>30</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>1074</v>
+        <v>1524</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>1075</v>
@@ -15573,7 +15628,7 @@
         <v>31</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>1100</v>
+        <v>1525</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>963</v>
@@ -15602,7 +15657,7 @@
         <v>32</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>1130</v>
+        <v>1526</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>1131</v>
@@ -15628,7 +15683,7 @@
         <v>33</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1140</v>
+        <v>1527</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>1141</v>
@@ -15657,7 +15712,7 @@
         <v>34</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>1155</v>
+        <v>1528</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>1156</v>
@@ -15683,7 +15738,7 @@
         <v>35</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>1159</v>
+        <v>1529</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>1160</v>

--- a/TFP_APS_Questions_QCU_Reel_2025.xlsx
+++ b/TFP_APS_Questions_QCU_Reel_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daher-my.sharepoint.com/personal/2104474_daher_com/Documents/Documents/WORK/PYTHON/apps/Questions_TFP_APS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="573" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27F6EF0E-C585-4508-8933-3A2DC3DE4906}"/>
+  <xr:revisionPtr revIDLastSave="574" documentId="13_ncr:1_{2ACE7C71-CCF8-48B7-AEC7-69C3CEDFEA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACD6475-A42A-4A97-8520-E75BB5588899}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6855" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste_Questions" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1790">
   <si>
     <t>UV</t>
   </si>
@@ -6485,9 +6485,6 @@
   </si>
   <si>
     <t>[UV09] Suite à une appréhension en flagrant délit pour vol, je vois que l’individu possède un couteau dans sa poche de blouson. Que dois-je faire ?</t>
-  </si>
-  <si>
-    <t>UV0</t>
   </si>
   <si>
     <t>UV02 (1)</t>
@@ -7522,15 +7519,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{739EAF5D-6DEC-4933-BEAA-58326FF9FE6A}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -8381,7 +8370,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>1525</v>
+        <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -8413,7 +8402,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>10</v>
@@ -8445,7 +8434,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>12</v>
@@ -8477,7 +8466,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>14</v>
@@ -8509,7 +8498,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>15</v>
@@ -8541,7 +8530,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>16</v>
@@ -8573,7 +8562,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -8605,7 +8594,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>19</v>
@@ -8637,7 +8626,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>21</v>
@@ -8669,7 +8658,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>23</v>
@@ -8701,7 +8690,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>24</v>
@@ -8733,7 +8722,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
@@ -8765,7 +8754,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>26</v>
@@ -8797,7 +8786,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>27</v>
@@ -8829,7 +8818,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>28</v>
@@ -8861,7 +8850,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>29</v>
@@ -8893,7 +8882,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>30</v>
@@ -8925,7 +8914,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>31</v>
@@ -8957,7 +8946,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>32</v>
@@ -8989,7 +8978,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>33</v>
@@ -9021,7 +9010,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>34</v>
@@ -9053,7 +9042,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>35</v>
@@ -9085,7 +9074,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>36</v>
@@ -9117,7 +9106,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>37</v>
@@ -9149,7 +9138,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>38</v>
@@ -9181,7 +9170,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>39</v>
@@ -9213,7 +9202,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>40</v>
@@ -9245,7 +9234,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>41</v>
@@ -9277,7 +9266,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>42</v>
@@ -9309,7 +9298,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
@@ -9341,7 +9330,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>44</v>
@@ -9373,7 +9362,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>45</v>
@@ -9405,7 +9394,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>47</v>
@@ -9437,7 +9426,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>49</v>
@@ -9469,7 +9458,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>51</v>
@@ -9501,7 +9490,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>53</v>
@@ -9533,7 +9522,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>55</v>
@@ -9565,7 +9554,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>57</v>
@@ -9597,7 +9586,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>10</v>
@@ -9626,7 +9615,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>12</v>
@@ -9655,7 +9644,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>14</v>
@@ -9684,7 +9673,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>15</v>
@@ -9713,7 +9702,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>16</v>
@@ -9742,7 +9731,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>18</v>
@@ -9771,7 +9760,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>19</v>
@@ -9800,7 +9789,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>21</v>
@@ -9829,7 +9818,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>23</v>
@@ -9858,7 +9847,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>24</v>
@@ -9887,7 +9876,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>10</v>
@@ -9916,7 +9905,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>12</v>
@@ -9945,7 +9934,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>14</v>
@@ -9974,7 +9963,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>15</v>
@@ -10003,7 +9992,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>16</v>
@@ -10032,7 +10021,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>18</v>
@@ -10061,7 +10050,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>19</v>
@@ -10090,7 +10079,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>21</v>
@@ -10119,7 +10108,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>23</v>
@@ -10148,7 +10137,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>24</v>
@@ -10177,7 +10166,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>25</v>
@@ -10206,7 +10195,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>26</v>
@@ -10235,7 +10224,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>27</v>
@@ -10264,7 +10253,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>28</v>
@@ -10293,7 +10282,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>29</v>
@@ -10322,7 +10311,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>30</v>
@@ -10351,7 +10340,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
@@ -10380,7 +10369,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>12</v>
@@ -10409,7 +10398,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>14</v>
@@ -10438,7 +10427,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>15</v>
@@ -10467,7 +10456,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>16</v>
@@ -10496,7 +10485,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>18</v>
@@ -10525,7 +10514,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>19</v>
@@ -10554,7 +10543,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>21</v>
@@ -10583,7 +10572,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>23</v>
@@ -10612,7 +10601,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>24</v>
@@ -10641,7 +10630,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>25</v>
@@ -10670,7 +10659,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>26</v>
@@ -10699,7 +10688,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>10</v>
@@ -10725,7 +10714,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>12</v>
@@ -10751,7 +10740,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>14</v>
@@ -10780,7 +10769,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>15</v>
@@ -10809,7 +10798,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>16</v>
@@ -10838,7 +10827,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>18</v>
@@ -10867,7 +10856,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>19</v>
@@ -10896,7 +10885,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>21</v>
@@ -10925,7 +10914,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>23</v>
@@ -10954,7 +10943,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>24</v>
@@ -10983,7 +10972,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>25</v>
@@ -11012,7 +11001,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>26</v>
@@ -11041,7 +11030,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>27</v>
@@ -11070,7 +11059,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>28</v>
@@ -11099,7 +11088,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>29</v>
@@ -11128,7 +11117,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>30</v>
@@ -11157,7 +11146,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>31</v>
@@ -11186,7 +11175,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>32</v>
@@ -11215,7 +11204,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>33</v>
@@ -11244,7 +11233,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>34</v>
@@ -11273,7 +11262,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>35</v>
@@ -11302,7 +11291,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>36</v>
@@ -11331,7 +11320,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>37</v>
@@ -11360,7 +11349,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>38</v>
@@ -11389,7 +11378,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>39</v>
@@ -11418,7 +11407,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>40</v>
@@ -11447,7 +11436,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>41</v>
@@ -11476,7 +11465,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>42</v>
@@ -11505,7 +11494,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>43</v>
@@ -11534,7 +11523,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>44</v>
@@ -11563,7 +11552,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>45</v>
@@ -11592,7 +11581,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B108" s="15" t="s">
         <v>47</v>
@@ -11621,7 +11610,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>49</v>
@@ -11650,7 +11639,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>51</v>
@@ -11679,7 +11668,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>53</v>
@@ -11708,7 +11697,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>55</v>
@@ -11737,7 +11726,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>57</v>
@@ -11766,7 +11755,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>703</v>
@@ -11795,7 +11784,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>704</v>
@@ -11824,7 +11813,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>705</v>
@@ -11853,7 +11842,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>983</v>
@@ -11882,7 +11871,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>984</v>
@@ -11911,7 +11900,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>985</v>
@@ -11937,7 +11926,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>986</v>
@@ -11963,7 +11952,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>987</v>
@@ -11989,7 +11978,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>988</v>
@@ -12015,7 +12004,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>989</v>
@@ -12044,7 +12033,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>990</v>
@@ -12073,7 +12062,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>991</v>
@@ -12099,7 +12088,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>992</v>
@@ -12128,7 +12117,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B127" s="15" t="s">
         <v>10</v>
@@ -12157,7 +12146,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>12</v>
@@ -12186,7 +12175,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>14</v>
@@ -12215,7 +12204,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B130" s="15" t="s">
         <v>15</v>
@@ -12244,7 +12233,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B131" s="15" t="s">
         <v>16</v>
@@ -12273,7 +12262,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>18</v>
@@ -12302,7 +12291,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>19</v>
@@ -12331,7 +12320,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>21</v>
@@ -16563,22 +16552,22 @@
         <v>31</v>
       </c>
       <c r="C282" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>1587</v>
       </c>
-      <c r="D282" s="2" t="s">
+      <c r="E282" s="2" t="s">
         <v>1588</v>
       </c>
-      <c r="E282" s="2" t="s">
+      <c r="F282" s="2" t="s">
         <v>1589</v>
       </c>
-      <c r="F282" s="2" t="s">
+      <c r="G282" s="2" t="s">
         <v>1590</v>
       </c>
-      <c r="G282" s="2" t="s">
+      <c r="H282" s="2" t="s">
         <v>1591</v>
-      </c>
-      <c r="H282" s="2" t="s">
-        <v>1592</v>
       </c>
       <c r="J282" s="7" t="s">
         <v>20</v>
@@ -16592,22 +16581,22 @@
         <v>32</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E283" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>1594</v>
       </c>
-      <c r="F283" s="2" t="s">
+      <c r="G283" s="2" t="s">
         <v>1595</v>
       </c>
-      <c r="G283" s="2" t="s">
+      <c r="H283" s="2" t="s">
         <v>1596</v>
-      </c>
-      <c r="H283" s="2" t="s">
-        <v>1597</v>
       </c>
       <c r="J283" s="7" t="s">
         <v>17</v>
@@ -16621,22 +16610,22 @@
         <v>33</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>1598</v>
       </c>
-      <c r="D284" s="2" t="s">
+      <c r="E284" s="2" t="s">
         <v>1599</v>
       </c>
-      <c r="E284" s="2" t="s">
+      <c r="F284" s="2" t="s">
         <v>1600</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>1601</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="J284" s="7" t="s">
         <v>22</v>
@@ -16650,22 +16639,22 @@
         <v>34</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="D285" s="2" t="s">
+      <c r="E285" s="2" t="s">
         <v>1604</v>
       </c>
-      <c r="E285" s="2" t="s">
+      <c r="F285" s="2" t="s">
         <v>1605</v>
       </c>
-      <c r="F285" s="2" t="s">
+      <c r="G285" s="2" t="s">
         <v>1606</v>
       </c>
-      <c r="G285" s="2" t="s">
+      <c r="H285" s="2" t="s">
         <v>1607</v>
-      </c>
-      <c r="H285" s="2" t="s">
-        <v>1608</v>
       </c>
       <c r="J285" s="7" t="s">
         <v>20</v>
@@ -16673,28 +16662,28 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D286" s="2" t="s">
         <v>1609</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>1610</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F286" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G286" s="2" t="s">
         <v>1611</v>
       </c>
-      <c r="G286" s="2" t="s">
+      <c r="H286" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="J286" s="7" t="s">
         <v>17</v>
@@ -16702,28 +16691,28 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C287" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D287" s="2" t="s">
         <v>1614</v>
       </c>
-      <c r="D287" s="2" t="s">
+      <c r="E287" s="2" t="s">
         <v>1615</v>
       </c>
-      <c r="E287" s="2" t="s">
+      <c r="F287" s="2" t="s">
         <v>1616</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>1617</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J287" s="7" t="s">
         <v>17</v>
@@ -16731,28 +16720,28 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E288" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>1620</v>
       </c>
-      <c r="F288" s="2" t="s">
+      <c r="G288" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="H288" s="2" t="s">
         <v>1622</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>1623</v>
       </c>
       <c r="J288" s="7" t="s">
         <v>13</v>
@@ -16760,28 +16749,28 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D289" s="2" t="s">
         <v>1624</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>1625</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F289" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G289" s="2" t="s">
         <v>1626</v>
       </c>
-      <c r="G289" s="2" t="s">
+      <c r="H289" s="2" t="s">
         <v>1627</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>1628</v>
       </c>
       <c r="J289" s="7" t="s">
         <v>11</v>
@@ -16789,28 +16778,28 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C290" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D290" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="D290" s="2" t="s">
+      <c r="E290" s="2" t="s">
         <v>1630</v>
       </c>
-      <c r="E290" s="2" t="s">
+      <c r="F290" s="2" t="s">
         <v>1631</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1632</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J290" s="7" t="s">
         <v>13</v>
@@ -16818,28 +16807,28 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E291" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>1635</v>
       </c>
-      <c r="F291" s="2" t="s">
+      <c r="G291" s="2" t="s">
         <v>1636</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="H291" s="2" t="s">
         <v>1637</v>
-      </c>
-      <c r="H291" s="2" t="s">
-        <v>1638</v>
       </c>
       <c r="J291" s="7" t="s">
         <v>22</v>
@@ -16847,25 +16836,25 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C292" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D292" s="2" t="s">
         <v>1639</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>1640</v>
       </c>
-      <c r="E292" s="2" t="s">
+      <c r="F292" s="2" t="s">
         <v>1641</v>
       </c>
-      <c r="F292" s="2" t="s">
+      <c r="G292" s="2" t="s">
         <v>1642</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>1643</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>89</v>
@@ -16876,25 +16865,25 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C293" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D293" s="2" t="s">
         <v>1644</v>
       </c>
-      <c r="D293" s="2" t="s">
+      <c r="E293" s="2" t="s">
         <v>1645</v>
       </c>
-      <c r="E293" s="2" t="s">
+      <c r="F293" s="2" t="s">
         <v>1646</v>
       </c>
-      <c r="F293" s="2" t="s">
+      <c r="G293" s="2" t="s">
         <v>1647</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>1648</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>89</v>
@@ -16905,28 +16894,28 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E294" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="F294" s="2" t="s">
+      <c r="G294" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="H294" s="2" t="s">
         <v>1652</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>1653</v>
       </c>
       <c r="J294" s="7" t="s">
         <v>20</v>
@@ -16934,13 +16923,13 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>469</v>
@@ -16949,10 +16938,10 @@
         <v>471</v>
       </c>
       <c r="F295" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G295" s="2" t="s">
         <v>1655</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>1656</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>89</v>
@@ -16963,16 +16952,16 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C296" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D296" s="2" t="s">
         <v>1657</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>1658</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>1134</v>
@@ -16981,10 +16970,10 @@
         <v>89</v>
       </c>
       <c r="G296" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H296" s="2" t="s">
         <v>1659</v>
-      </c>
-      <c r="H296" s="2" t="s">
-        <v>1660</v>
       </c>
       <c r="J296" s="7" t="s">
         <v>11</v>
@@ -16992,28 +16981,28 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C297" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D297" s="2" t="s">
         <v>1661</v>
       </c>
-      <c r="D297" s="2" t="s">
+      <c r="E297" s="2" t="s">
         <v>1662</v>
       </c>
-      <c r="E297" s="2" t="s">
+      <c r="F297" s="2" t="s">
         <v>1663</v>
       </c>
-      <c r="F297" s="2" t="s">
+      <c r="G297" s="2" t="s">
         <v>1664</v>
       </c>
-      <c r="G297" s="2" t="s">
+      <c r="H297" s="2" t="s">
         <v>1665</v>
-      </c>
-      <c r="H297" s="2" t="s">
-        <v>1666</v>
       </c>
       <c r="J297" s="7" t="s">
         <v>20</v>
@@ -17021,28 +17010,28 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C298" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D298" s="2" t="s">
         <v>1667</v>
       </c>
-      <c r="D298" s="2" t="s">
+      <c r="E298" s="2" t="s">
         <v>1668</v>
       </c>
-      <c r="E298" s="2" t="s">
+      <c r="F298" s="2" t="s">
         <v>1669</v>
       </c>
-      <c r="F298" s="2" t="s">
+      <c r="G298" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="H298" s="2" t="s">
         <v>1671</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1672</v>
       </c>
       <c r="J298" s="7" t="s">
         <v>13</v>
@@ -17050,28 +17039,28 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C299" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D299" s="2" t="s">
         <v>1673</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>1674</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F299" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G299" s="2" t="s">
         <v>1675</v>
       </c>
-      <c r="G299" s="2" t="s">
+      <c r="H299" s="2" t="s">
         <v>1676</v>
-      </c>
-      <c r="H299" s="2" t="s">
-        <v>1677</v>
       </c>
       <c r="J299" s="7" t="s">
         <v>13</v>
@@ -17079,28 +17068,28 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C300" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D300" s="2" t="s">
         <v>1678</v>
       </c>
-      <c r="D300" s="2" t="s">
+      <c r="E300" s="2" t="s">
         <v>1679</v>
       </c>
-      <c r="E300" s="2" t="s">
+      <c r="F300" s="2" t="s">
         <v>1680</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>1681</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J300" s="7" t="s">
         <v>20</v>
@@ -17108,28 +17097,28 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C301" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D301" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="D301" s="2" t="s">
+      <c r="E301" s="2" t="s">
         <v>1684</v>
       </c>
-      <c r="E301" s="2" t="s">
+      <c r="F301" s="2" t="s">
         <v>1685</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>1686</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="J301" s="7" t="s">
         <v>11</v>
@@ -17137,28 +17126,28 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B302" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C302" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D302" s="2" t="s">
         <v>1688</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>1689</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F302" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G302" s="2" t="s">
         <v>1690</v>
       </c>
-      <c r="G302" s="2" t="s">
+      <c r="H302" s="2" t="s">
         <v>1691</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1692</v>
       </c>
       <c r="J302" s="7" t="s">
         <v>13</v>
@@ -17166,28 +17155,28 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B303" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D303" s="2" t="s">
         <v>1693</v>
       </c>
-      <c r="D303" s="2" t="s">
+      <c r="E303" s="2" t="s">
         <v>1694</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>1695</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G303" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H303" s="2" t="s">
         <v>1696</v>
-      </c>
-      <c r="H303" s="2" t="s">
-        <v>1697</v>
       </c>
       <c r="J303" s="7" t="s">
         <v>22</v>
@@ -17195,25 +17184,25 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B304" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C304" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D304" s="2" t="s">
         <v>1698</v>
       </c>
-      <c r="D304" s="2" t="s">
+      <c r="E304" s="2" t="s">
         <v>1699</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>1700</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>424</v>
@@ -17224,28 +17213,28 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B305" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E305" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F305" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="F305" s="2" t="s">
+      <c r="G305" s="2" t="s">
         <v>1704</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="H305" s="2" t="s">
         <v>1705</v>
-      </c>
-      <c r="H305" s="2" t="s">
-        <v>1706</v>
       </c>
       <c r="J305" s="7" t="s">
         <v>22</v>
@@ -17253,25 +17242,25 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B306" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D306" s="2" t="s">
         <v>1707</v>
       </c>
-      <c r="D306" s="2" t="s">
+      <c r="E306" s="2" t="s">
         <v>1708</v>
       </c>
-      <c r="E306" s="2" t="s">
+      <c r="F306" s="2" t="s">
         <v>1709</v>
       </c>
-      <c r="F306" s="2" t="s">
+      <c r="G306" s="2" t="s">
         <v>1710</v>
-      </c>
-      <c r="G306" s="2" t="s">
-        <v>1711</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>89</v>
@@ -17282,28 +17271,28 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B307" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C307" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D307" s="2" t="s">
         <v>1712</v>
       </c>
-      <c r="D307" s="2" t="s">
+      <c r="E307" s="2" t="s">
         <v>1713</v>
       </c>
-      <c r="E307" s="2" t="s">
+      <c r="F307" s="2" t="s">
         <v>1714</v>
       </c>
-      <c r="F307" s="2" t="s">
+      <c r="G307" s="2" t="s">
         <v>1715</v>
       </c>
-      <c r="G307" s="2" t="s">
+      <c r="H307" s="2" t="s">
         <v>1716</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>1717</v>
       </c>
       <c r="J307" s="7" t="s">
         <v>11</v>
@@ -17311,28 +17300,28 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B308" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D308" s="2" t="s">
         <v>1718</v>
       </c>
-      <c r="D308" s="2" t="s">
+      <c r="E308" s="2" t="s">
         <v>1719</v>
       </c>
-      <c r="E308" s="2" t="s">
+      <c r="F308" s="2" t="s">
         <v>1720</v>
       </c>
-      <c r="F308" s="2" t="s">
+      <c r="G308" s="2" t="s">
         <v>1721</v>
       </c>
-      <c r="G308" s="2" t="s">
+      <c r="H308" s="2" t="s">
         <v>1722</v>
-      </c>
-      <c r="H308" s="2" t="s">
-        <v>1723</v>
       </c>
       <c r="J308" s="7" t="s">
         <v>17</v>
@@ -17340,28 +17329,28 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B309" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C309" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D309" s="2" t="s">
         <v>1724</v>
       </c>
-      <c r="D309" s="2" t="s">
+      <c r="E309" s="2" t="s">
         <v>1725</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>1726</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G309" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="H309" s="2" t="s">
         <v>1727</v>
-      </c>
-      <c r="H309" s="2" t="s">
-        <v>1728</v>
       </c>
       <c r="J309" s="7" t="s">
         <v>11</v>
@@ -17369,28 +17358,28 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B310" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C310" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D310" s="2" t="s">
         <v>1729</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>1730</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F310" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G310" s="2" t="s">
         <v>1731</v>
       </c>
-      <c r="G310" s="2" t="s">
+      <c r="H310" s="2" t="s">
         <v>1732</v>
-      </c>
-      <c r="H310" s="2" t="s">
-        <v>1733</v>
       </c>
       <c r="J310" s="7" t="s">
         <v>13</v>
@@ -17398,28 +17387,28 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B311" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>745</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G311" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H311" s="2" t="s">
         <v>1736</v>
-      </c>
-      <c r="H311" s="2" t="s">
-        <v>1737</v>
       </c>
       <c r="J311" s="7" t="s">
         <v>22</v>
@@ -17427,28 +17416,28 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B312" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C312" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D312" s="2" t="s">
         <v>1738</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>1739</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>140</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="J312" s="7" t="s">
         <v>22</v>
@@ -17456,13 +17445,13 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B313" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>1293</v>
@@ -17485,28 +17474,28 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B314" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C314" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D314" s="2" t="s">
         <v>1743</v>
       </c>
-      <c r="D314" s="2" t="s">
+      <c r="E314" s="2" t="s">
         <v>1744</v>
       </c>
-      <c r="E314" s="2" t="s">
+      <c r="F314" s="2" t="s">
         <v>1745</v>
       </c>
-      <c r="F314" s="2" t="s">
+      <c r="G314" s="2" t="s">
         <v>1746</v>
       </c>
-      <c r="G314" s="2" t="s">
+      <c r="H314" s="2" t="s">
         <v>1747</v>
-      </c>
-      <c r="H314" s="2" t="s">
-        <v>1748</v>
       </c>
       <c r="J314" s="7" t="s">
         <v>13</v>
@@ -17514,13 +17503,13 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B315" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>620</v>
@@ -17532,7 +17521,7 @@
         <v>89</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>619</v>
@@ -17543,28 +17532,28 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B316" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D316" s="2" t="s">
         <v>1751</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>1752</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F316" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="G316" s="2" t="s">
         <v>1753</v>
       </c>
-      <c r="G316" s="2" t="s">
+      <c r="H316" s="2" t="s">
         <v>1754</v>
-      </c>
-      <c r="H316" s="2" t="s">
-        <v>1755</v>
       </c>
       <c r="J316" s="7" t="s">
         <v>17</v>
@@ -17572,28 +17561,28 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B317" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C317" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D317" s="2" t="s">
         <v>1756</v>
-      </c>
-      <c r="D317" s="2" t="s">
-        <v>1757</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F317" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G317" s="2" t="s">
         <v>1758</v>
       </c>
-      <c r="G317" s="2" t="s">
+      <c r="H317" s="2" t="s">
         <v>1759</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>1760</v>
       </c>
       <c r="J317" s="7" t="s">
         <v>13</v>
@@ -17601,28 +17590,28 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B318" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C318" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D318" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="D318" s="2" t="s">
+      <c r="E318" s="2" t="s">
         <v>1762</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1763</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G318" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H318" s="2" t="s">
         <v>1764</v>
-      </c>
-      <c r="H318" s="2" t="s">
-        <v>1765</v>
       </c>
       <c r="J318" s="7" t="s">
         <v>13</v>
@@ -17630,28 +17619,28 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B319" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C319" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D319" s="2" t="s">
         <v>1766</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>1767</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F319" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G319" s="2" t="s">
         <v>1768</v>
       </c>
-      <c r="G319" s="2" t="s">
+      <c r="H319" s="2" t="s">
         <v>1769</v>
-      </c>
-      <c r="H319" s="2" t="s">
-        <v>1770</v>
       </c>
       <c r="J319" s="7" t="s">
         <v>22</v>
@@ -17659,25 +17648,25 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B320" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C320" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D320" s="2" t="s">
         <v>1771</v>
       </c>
-      <c r="D320" s="2" t="s">
+      <c r="E320" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="E320" s="2" t="s">
+      <c r="F320" s="2" t="s">
         <v>1773</v>
       </c>
-      <c r="F320" s="2" t="s">
+      <c r="G320" s="2" t="s">
         <v>1774</v>
-      </c>
-      <c r="G320" s="2" t="s">
-        <v>1775</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>89</v>
@@ -17688,13 +17677,13 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B321" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>859</v>
@@ -17709,7 +17698,7 @@
         <v>856</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="J321" s="7" t="s">
         <v>22</v>
@@ -17717,28 +17706,28 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B322" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C322" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D322" s="2" t="s">
         <v>1778</v>
       </c>
-      <c r="D322" s="2" t="s">
+      <c r="E322" s="2" t="s">
         <v>1779</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>1780</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G322" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H322" s="2" t="s">
         <v>1781</v>
-      </c>
-      <c r="H322" s="2" t="s">
-        <v>1782</v>
       </c>
       <c r="J322" s="7" t="s">
         <v>11</v>
@@ -17746,25 +17735,25 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B323" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C323" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D323" s="2" t="s">
         <v>1783</v>
       </c>
-      <c r="D323" s="2" t="s">
+      <c r="E323" s="2" t="s">
         <v>1784</v>
       </c>
-      <c r="E323" s="2" t="s">
+      <c r="F323" s="2" t="s">
         <v>1785</v>
       </c>
-      <c r="F323" s="2" t="s">
+      <c r="G323" s="2" t="s">
         <v>1786</v>
-      </c>
-      <c r="G323" s="2" t="s">
-        <v>1787</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>89</v>
@@ -17775,7 +17764,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B324" s="20" t="s">
         <v>33</v>
@@ -17801,7 +17790,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B325" s="20" t="s">
         <v>34</v>
@@ -17832,32 +17821,32 @@
   <autoFilter ref="A1:J325" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J1="A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J1="B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J1="C"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$J1="D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$J1="E"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$J1="F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17891,7 +17880,7 @@
         <v>239</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>1472</v>
@@ -17899,7 +17888,7 @@
     </row>
     <row r="2" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B2" s="16" t="str">
         <f>F2 &amp; " (" &amp; D2 &amp; " questions)"</f>
@@ -17919,7 +17908,7 @@
     </row>
     <row r="3" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B3" s="16" t="str">
         <f t="shared" ref="B3:B18" si="0">F3 &amp; " (" &amp; D3 &amp; " questions)"</f>
@@ -17942,7 +17931,7 @@
     </row>
     <row r="4" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B4" s="16" t="str">
         <f t="shared" si="0"/>
@@ -17965,7 +17954,7 @@
     </row>
     <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B5" s="16" t="str">
         <f t="shared" si="0"/>
@@ -17988,14 +17977,14 @@
     </row>
     <row r="6" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B6" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Module stratégique (16 questions)</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D6" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A6)</f>
@@ -18011,7 +18000,7 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B7" s="16" t="str">
         <f t="shared" si="0"/>
@@ -18034,7 +18023,7 @@
     </row>
     <row r="8" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B8" s="16" t="str">
         <f t="shared" si="0"/>
@@ -18057,14 +18046,14 @@
     </row>
     <row r="9" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Module d’appréhension au cours de l’exercice du métier (0 questions)</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D9" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A9)</f>
@@ -18080,7 +18069,7 @@
     </row>
     <row r="10" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B10" s="16" t="str">
         <f t="shared" si="0"/>
@@ -18103,7 +18092,7 @@
     </row>
     <row r="11" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B11" s="16" t="str">
         <f t="shared" si="0"/>
@@ -18126,14 +18115,14 @@
     </row>
     <row r="12" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B12" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Module palpation de sécurité et inspection des bagages (8 questions)</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D12" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A12)</f>
@@ -18156,7 +18145,7 @@
         <v>Module surveillance par moyens électroniques de sécurité (20 questions)</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D13" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A13)</f>
@@ -18179,7 +18168,7 @@
         <v>Module gestion des risques (23 questions)</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D14" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A14)</f>
@@ -18202,7 +18191,7 @@
         <v>Module événementiel spécifique (10 questions)</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D15" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A15)</f>
@@ -18245,7 +18234,7 @@
         <v>Module industriel spécifique (18 questions)</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D17" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A17)</f>
@@ -18284,7 +18273,7 @@
         <v>1458</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D19" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A19)</f>
@@ -18296,7 +18285,7 @@
         <v>1459</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D20" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A20)</f>
@@ -18308,7 +18297,7 @@
         <v>1460</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D21" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A21)</f>
@@ -18320,7 +18309,7 @@
         <v>1461</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A22)</f>
@@ -18329,10 +18318,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="D23" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A23)</f>
@@ -18341,10 +18330,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>1789</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>1790</v>
       </c>
       <c r="D24" s="16">
         <f>COUNTIF(Liste_Questions!$A:$A,$A24)</f>
@@ -26058,7 +26047,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="19" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B216" s="13">
         <f t="shared" ref="B216:B257" si="24">FIND(" – ",A216)</f>
@@ -26093,7 +26082,7 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="19" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B217" s="13">
         <f t="shared" si="24"/>
@@ -26128,7 +26117,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="19" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B218" s="13">
         <f t="shared" si="24"/>
@@ -26163,7 +26152,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="19" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B219" s="13">
         <f t="shared" si="24"/>
@@ -26198,7 +26187,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="19" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B220" s="13">
         <f t="shared" si="24"/>
@@ -26233,7 +26222,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="19" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B221" s="13">
         <f t="shared" si="24"/>
@@ -26268,7 +26257,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="19" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B222" s="13">
         <f t="shared" si="24"/>
@@ -26303,7 +26292,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="19" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B223" s="13">
         <f t="shared" si="24"/>
@@ -26338,7 +26327,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="19" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B224" s="13">
         <f t="shared" si="24"/>
@@ -26373,7 +26362,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="19" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B225" s="13">
         <f t="shared" si="24"/>
@@ -26408,7 +26397,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="19" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B226" s="13">
         <f t="shared" si="24"/>
@@ -26443,7 +26432,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="19" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B227" s="13">
         <f t="shared" si="24"/>
@@ -26478,7 +26467,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="19" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B228" s="13">
         <f t="shared" si="24"/>
@@ -26513,7 +26502,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="19" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B229" s="13">
         <f t="shared" si="24"/>
@@ -26548,7 +26537,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="19" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B230" s="13">
         <f t="shared" si="24"/>
@@ -26583,7 +26572,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="19" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B231" s="13">
         <f t="shared" si="24"/>
@@ -26618,7 +26607,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="19" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B232" s="13">
         <f t="shared" si="24"/>
@@ -26653,7 +26642,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="19" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B233" s="13">
         <f t="shared" si="24"/>
@@ -26688,7 +26677,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="19" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B234" s="13">
         <f t="shared" si="24"/>
@@ -26723,7 +26712,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="19" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B235" s="13">
         <f t="shared" si="24"/>
@@ -26758,7 +26747,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="19" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B236" s="13">
         <f t="shared" si="24"/>
@@ -26793,7 +26782,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="19" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B237" s="13">
         <f t="shared" si="24"/>
@@ -26828,7 +26817,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="19" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B238" s="13">
         <f t="shared" si="24"/>
@@ -26863,7 +26852,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="19" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B239" s="13">
         <f t="shared" si="24"/>
@@ -26898,7 +26887,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="19" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B240" s="13">
         <f t="shared" si="24"/>
@@ -26933,7 +26922,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="19" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B241" s="13">
         <f t="shared" si="24"/>
@@ -26968,7 +26957,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="19" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B242" s="13">
         <f t="shared" si="24"/>
@@ -27003,7 +26992,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="19" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B243" s="13">
         <f t="shared" si="24"/>
@@ -27038,7 +27027,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="19" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B244" s="13">
         <f t="shared" si="24"/>
@@ -27073,7 +27062,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="19" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B245" s="13">
         <f t="shared" si="24"/>
@@ -27108,7 +27097,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="19" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B246" s="13">
         <f t="shared" si="24"/>
@@ -27143,7 +27132,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="19" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B247" s="13">
         <f t="shared" si="24"/>
@@ -27178,7 +27167,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="19" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B248" s="13">
         <f t="shared" si="24"/>
@@ -27213,7 +27202,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="19" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B249" s="13">
         <f t="shared" si="24"/>
@@ -27248,7 +27237,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="19" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B250" s="13">
         <f t="shared" si="24"/>
@@ -27283,7 +27272,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="19" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B251" s="13">
         <f t="shared" si="24"/>
@@ -27318,7 +27307,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="19" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B252" s="13">
         <f t="shared" si="24"/>
@@ -27353,7 +27342,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="19" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B253" s="13">
         <f t="shared" si="24"/>
@@ -27388,7 +27377,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="19" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B254" s="13">
         <f t="shared" si="24"/>
@@ -27423,7 +27412,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="19" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B255" s="13">
         <f t="shared" si="24"/>
@@ -27458,7 +27447,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="19" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B256" s="13">
         <f t="shared" si="24"/>
@@ -27493,7 +27482,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="19" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B257" s="13">
         <f t="shared" si="24"/>
